--- a/noprofit/en/11255/inpag-template.xlsx
+++ b/noprofit/en/11255/inpag-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bananach-my.sharepoint.com/personal/patrick_pasquillo_banana_ch/Documents/Desktop/Associazioni Internazionale/Documentazione INPAG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3135" documentId="8_{07358736-E140-4CDF-B895-9B6DD3243961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6E8CD59-A80F-425C-838B-0BED8354BEBE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44820CC8-AE92-4FB9-82EA-52E5190E96B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" firstSheet="4" activeTab="4" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
   <sheets>
     <sheet name="General information" sheetId="7" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="287">
   <si>
     <t>Company name and legal form</t>
   </si>
@@ -907,6 +907,12 @@
   </si>
   <si>
     <t>General Information</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>2.1</t>
   </si>
 </sst>
 </file>
@@ -1154,9 +1160,6 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1190,17 +1193,11 @@
     <xf numFmtId="2" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1241,9 +1238,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1322,9 +1316,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1347,9 +1338,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1419,26 +1407,38 @@
     <xf numFmtId="2" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1452,15 +1452,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1470,13 +1461,22 @@
     <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1485,53 +1485,59 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1922,122 +1928,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="99" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="107" t="s">
+      <c r="A2" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="109">
+      <c r="B8" s="102">
         <v>45292</v>
       </c>
-      <c r="C8" s="109"/>
-      <c r="D8" s="109"/>
-      <c r="E8" s="109"/>
-      <c r="F8" s="109"/>
-      <c r="G8" s="109"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="109">
+      <c r="B9" s="102">
         <v>45657</v>
       </c>
-      <c r="C9" s="109"/>
-      <c r="D9" s="109"/>
-      <c r="E9" s="109"/>
-      <c r="F9" s="109"/>
-      <c r="G9" s="109"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="48" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="103" t="s">
@@ -2050,199 +2056,205 @@
       <c r="G10" s="103"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="52"/>
-      <c r="B11" s="104"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A12" s="52"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A13" s="52"/>
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="52"/>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="52"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A16" s="50"/>
-      <c r="B16" s="105"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="104"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A18" s="52"/>
-      <c r="B18" s="104" t="s">
+      <c r="A18" s="48"/>
+      <c r="B18" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A19" s="52"/>
-      <c r="B19" s="104" t="s">
+      <c r="A19" s="48"/>
+      <c r="B19" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A20" s="50"/>
-      <c r="B20" s="105" t="s">
+      <c r="A20" s="46"/>
+      <c r="B20" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="105" t="s">
+      <c r="B21" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="105"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="104" t="s">
+      <c r="B22" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="104"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="52"/>
-      <c r="B23" s="104" t="s">
+      <c r="A23" s="48"/>
+      <c r="B23" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98"/>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A24" s="52"/>
-      <c r="B24" s="104" t="s">
+      <c r="A24" s="48"/>
+      <c r="B24" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="104"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A25" s="52"/>
-      <c r="B25" s="104" t="s">
+      <c r="A25" s="48"/>
+      <c r="B25" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="104"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A26" s="52"/>
-      <c r="B26" s="104" t="s">
+      <c r="A26" s="48"/>
+      <c r="B26" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="104"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A27" s="52"/>
-      <c r="B27" s="104" t="s">
+      <c r="A27" s="48"/>
+      <c r="B27" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="104"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98"/>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A28" s="52"/>
-      <c r="B28" s="104" t="s">
+      <c r="A28" s="48"/>
+      <c r="B28" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2259,12 +2271,6 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2293,685 +2299,731 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="114" t="str">
+      <c r="B2" s="105" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="105" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="116">
+      <c r="B4" s="107">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="116">
+      <c r="B5" s="107">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>283</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="78" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="84">
+      <c r="D9" s="78">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49"/>
-      <c r="B10" s="113" t="s">
+      <c r="A10" s="45"/>
+      <c r="B10" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="15">
+      <c r="C11" s="136">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="15">
-        <v>0</v>
-      </c>
-      <c r="E12" s="15">
+      <c r="C12" s="136">
+        <v>2</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="15">
-        <v>0</v>
-      </c>
-      <c r="E13" s="15">
+      <c r="C13" s="136">
+        <v>3</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="15">
-        <v>0</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="C14" s="136">
+        <v>4</v>
+      </c>
+      <c r="D14" s="14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A15" s="49"/>
-      <c r="B15" s="62" t="s">
+      <c r="A15" s="45"/>
+      <c r="B15" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="71">
+      <c r="C15" s="45"/>
+      <c r="D15" s="66">
         <f>SUM(D11:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="66">
         <f>SUM(E11:E14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="49"/>
-      <c r="B17" s="113" t="s">
+      <c r="A17" s="45"/>
+      <c r="B17" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="113"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="15">
-        <v>0</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="C18" s="136">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="15">
-        <v>0</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="C19" s="136">
+        <v>6</v>
+      </c>
+      <c r="D19" s="14">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="15">
-        <v>0</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="C20" s="136">
+        <v>7</v>
+      </c>
+      <c r="D20" s="14">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="15">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="C21" s="136">
+        <v>8</v>
+      </c>
+      <c r="D21" s="14">
+        <v>0</v>
+      </c>
+      <c r="E21" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A22" s="49"/>
-      <c r="B22" s="62" t="s">
+      <c r="A22" s="45"/>
+      <c r="B22" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="72">
+      <c r="C22" s="45"/>
+      <c r="D22" s="67">
         <f>SUM(D18:D21)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="72">
+      <c r="E22" s="67">
         <f>SUM(E18:E21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49"/>
-      <c r="B23" s="62" t="s">
+      <c r="A23" s="45"/>
+      <c r="B23" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="72">
+      <c r="C23" s="49"/>
+      <c r="D23" s="67">
         <f>SUM(D15,D22)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="72">
+      <c r="E23" s="67">
         <f>SUM(E15,E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="49"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
+      <c r="A24" s="45"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="78" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="84">
+      <c r="D25" s="78">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E25" s="84">
+      <c r="E25" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="49"/>
-      <c r="B26" s="113" t="s">
+      <c r="A26" s="45"/>
+      <c r="B26" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="113"/>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="15">
-        <v>0</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="C27" s="136">
+        <v>9</v>
+      </c>
+      <c r="D27" s="14">
+        <v>0</v>
+      </c>
+      <c r="E27" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="15">
-        <v>0</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="C28" s="136">
+        <v>10</v>
+      </c>
+      <c r="D28" s="14">
+        <v>0</v>
+      </c>
+      <c r="E28" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="15">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15">
+      <c r="C29" s="136">
+        <v>11</v>
+      </c>
+      <c r="D29" s="14">
+        <v>0</v>
+      </c>
+      <c r="E29" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="49" t="s">
+      <c r="A30" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="15">
-        <v>0</v>
-      </c>
-      <c r="E30" s="15">
+      <c r="C30" s="136">
+        <v>12</v>
+      </c>
+      <c r="D30" s="14">
+        <v>0</v>
+      </c>
+      <c r="E30" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="15">
-        <v>0</v>
-      </c>
-      <c r="E31" s="15">
+      <c r="C31" s="136">
+        <v>13</v>
+      </c>
+      <c r="D31" s="14">
+        <v>0</v>
+      </c>
+      <c r="E31" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A32" s="49"/>
-      <c r="B32" s="62" t="s">
+      <c r="A32" s="45"/>
+      <c r="B32" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="49"/>
-      <c r="D32" s="71">
+      <c r="C32" s="45"/>
+      <c r="D32" s="66">
         <f>SUM(D27:D31)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="71">
+      <c r="E32" s="66">
         <f>SUM(E27:E31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A33" s="49"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
+      <c r="A33" s="45"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
     </row>
     <row r="34" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="49"/>
-      <c r="B34" s="113" t="s">
+      <c r="A34" s="45"/>
+      <c r="B34" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="113"/>
-      <c r="D34" s="113"/>
-      <c r="E34" s="113"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="27"/>
-      <c r="D35" s="15">
-        <v>0</v>
-      </c>
-      <c r="E35" s="15">
+      <c r="C35" s="136">
+        <v>14</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="15">
-        <v>0</v>
-      </c>
-      <c r="E36" s="15">
+      <c r="C36" s="136">
+        <v>15</v>
+      </c>
+      <c r="D36" s="14">
+        <v>0</v>
+      </c>
+      <c r="E36" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="15">
-        <v>0</v>
-      </c>
-      <c r="E37" s="15">
+      <c r="C37" s="136">
+        <v>16</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A38" s="49"/>
-      <c r="B38" s="62" t="s">
+      <c r="A38" s="45"/>
+      <c r="B38" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C38" s="49"/>
-      <c r="D38" s="71">
+      <c r="C38" s="45"/>
+      <c r="D38" s="66">
         <f>SUM(D35:D37)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="71">
+      <c r="E38" s="66">
         <f>SUM(E35:E37)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A39" s="49"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
+      <c r="A39" s="45"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="49"/>
-      <c r="B40" s="113" t="s">
+      <c r="A40" s="45"/>
+      <c r="B40" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
-      <c r="E40" s="113"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="111"/>
     </row>
     <row r="41" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="49" t="s">
+      <c r="A41" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="15">
-        <v>0</v>
-      </c>
-      <c r="E41" s="15">
+      <c r="C41" s="136">
+        <v>17</v>
+      </c>
+      <c r="D41" s="14">
+        <v>0</v>
+      </c>
+      <c r="E41" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="49" t="s">
+      <c r="A42" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="15">
-        <v>0</v>
-      </c>
-      <c r="E42" s="15">
+      <c r="C42" s="136">
+        <v>18</v>
+      </c>
+      <c r="D42" s="14">
+        <v>0</v>
+      </c>
+      <c r="E42" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="49" t="s">
+      <c r="A43" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="15">
-        <v>0</v>
-      </c>
-      <c r="E43" s="15">
+      <c r="C43" s="136">
+        <v>19</v>
+      </c>
+      <c r="D43" s="14">
+        <v>0</v>
+      </c>
+      <c r="E43" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="27"/>
-      <c r="D44" s="15">
-        <v>0</v>
-      </c>
-      <c r="E44" s="15">
+      <c r="C44" s="136">
+        <v>20</v>
+      </c>
+      <c r="D44" s="14">
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="B45" s="41" t="s">
+      <c r="B45" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="27"/>
-      <c r="D45" s="15">
-        <v>0</v>
-      </c>
-      <c r="E45" s="15">
+      <c r="C45" s="136">
+        <v>21</v>
+      </c>
+      <c r="D45" s="14">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="27"/>
-      <c r="D46" s="15">
-        <v>0</v>
-      </c>
-      <c r="E46" s="15">
+      <c r="C46" s="136">
+        <v>22</v>
+      </c>
+      <c r="D46" s="14">
+        <v>0</v>
+      </c>
+      <c r="E46" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C47" s="27"/>
-      <c r="D47" s="15">
-        <v>0</v>
-      </c>
-      <c r="E47" s="15">
+      <c r="C47" s="136">
+        <v>23</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="49"/>
-      <c r="B48" s="113" t="s">
+      <c r="A48" s="45"/>
+      <c r="B48" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="113"/>
-      <c r="D48" s="71">
+      <c r="C48" s="111"/>
+      <c r="D48" s="66">
         <f>SUM(D41:D47)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="71">
+      <c r="E48" s="66">
         <f>SUM(E41:E47)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="49"/>
-      <c r="B49" s="113" t="s">
+      <c r="A49" s="45"/>
+      <c r="B49" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="113"/>
-      <c r="D49" s="71">
+      <c r="C49" s="111"/>
+      <c r="D49" s="66">
         <f>SUM(D32,D38,D48)</f>
         <v>0</v>
       </c>
-      <c r="E49" s="71">
+      <c r="E49" s="66">
         <f>SUM(E32,E38,E48)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="49"/>
-      <c r="B50" s="66"/>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
+      <c r="A50" s="45"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
     </row>
     <row r="51" spans="1:5" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="54"/>
-      <c r="B51" s="67"/>
-      <c r="C51" s="67"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
+      <c r="A51" s="50"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="68" t="s">
+      <c r="A52" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="112" t="str">
+      <c r="B52" s="110" t="str">
         <f>IF((D15+D23+D32=D38+D48),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C52" s="112"/>
-      <c r="D52" s="61">
+      <c r="C52" s="110"/>
+      <c r="D52" s="57">
         <f>D49-D23</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A53" s="69" t="s">
+      <c r="A53" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="B53" s="111" t="str">
+      <c r="B53" s="109" t="str">
         <f>IF((E15+E23+E32=E38+E48),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="111"/>
-      <c r="D53" s="111"/>
-      <c r="E53" s="61">
+      <c r="C53" s="109"/>
+      <c r="D53" s="109"/>
+      <c r="E53" s="57">
         <f>E49-E23</f>
         <v>0</v>
       </c>
@@ -2984,11 +3036,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="B52:C52"/>
@@ -2999,6 +3046,11 @@
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B52">
@@ -3052,499 +3104,537 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="118" t="str">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="113" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="118" t="str">
+      <c r="B3" s="113" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="119">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="119">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>282</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="97">
+      <c r="D9" s="91">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E9" s="97">
+      <c r="E9" s="91">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="20">
-        <v>0</v>
-      </c>
-      <c r="E10" s="20">
+      <c r="C10" s="137">
+        <v>24</v>
+      </c>
+      <c r="D10" s="19">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="20">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20">
+      <c r="C11" s="137">
+        <v>25</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0</v>
+      </c>
+      <c r="E11" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="20">
-        <v>0</v>
-      </c>
-      <c r="E12" s="20">
+      <c r="C12" s="137">
+        <v>26</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="20">
-        <v>0</v>
-      </c>
-      <c r="E13" s="20">
+      <c r="C13" s="137">
+        <v>27</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0</v>
+      </c>
+      <c r="E13" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="20">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20">
+      <c r="C14" s="137">
+        <v>28</v>
+      </c>
+      <c r="D14" s="19">
+        <v>0</v>
+      </c>
+      <c r="E14" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55"/>
-      <c r="B15" s="73" t="s">
+      <c r="A15" s="51"/>
+      <c r="B15" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74">
+      <c r="C15" s="68"/>
+      <c r="D15" s="69">
         <f>SUM(D10:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="69">
         <f>SUM(E10:E14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
     </row>
     <row r="17" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="97">
+      <c r="D17" s="91">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E17" s="97">
+      <c r="E17" s="91">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="20">
-        <v>0</v>
-      </c>
-      <c r="E18" s="20">
+      <c r="C18" s="137">
+        <v>29</v>
+      </c>
+      <c r="D18" s="19">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="20">
-        <v>0</v>
-      </c>
-      <c r="E19" s="20">
+      <c r="C19" s="137">
+        <v>30</v>
+      </c>
+      <c r="D19" s="19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="20">
-        <v>0</v>
-      </c>
-      <c r="E20" s="20">
+      <c r="C20" s="137">
+        <v>31</v>
+      </c>
+      <c r="D20" s="19">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="20">
-        <v>0</v>
-      </c>
-      <c r="E21" s="20">
+      <c r="C21" s="137">
+        <v>32</v>
+      </c>
+      <c r="D21" s="19">
+        <v>0</v>
+      </c>
+      <c r="E21" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="43"/>
-      <c r="D22" s="20">
-        <v>0</v>
-      </c>
-      <c r="E22" s="20">
+      <c r="C22" s="137">
+        <v>33</v>
+      </c>
+      <c r="D22" s="19">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="20">
-        <v>0</v>
-      </c>
-      <c r="E23" s="20">
+      <c r="C23" s="137">
+        <v>34</v>
+      </c>
+      <c r="D23" s="19">
+        <v>0</v>
+      </c>
+      <c r="E23" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="20">
-        <v>0</v>
-      </c>
-      <c r="E24" s="20">
+      <c r="C24" s="137">
+        <v>35</v>
+      </c>
+      <c r="D24" s="19">
+        <v>0</v>
+      </c>
+      <c r="E24" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="43"/>
-      <c r="D25" s="20">
-        <v>0</v>
-      </c>
-      <c r="E25" s="20">
+      <c r="C25" s="137">
+        <v>36</v>
+      </c>
+      <c r="D25" s="19">
+        <v>0</v>
+      </c>
+      <c r="E25" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="55"/>
-      <c r="B26" s="73" t="s">
+      <c r="A26" s="51"/>
+      <c r="B26" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="74">
+      <c r="C26" s="68"/>
+      <c r="D26" s="69">
         <f>SUM(D18:D25)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="74">
+      <c r="E26" s="69">
         <f>SUM(E18:E25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="55"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="84" t="s">
+      <c r="A28" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="64" t="s">
+      <c r="B28" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="97">
+      <c r="D28" s="91">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E28" s="97">
+      <c r="E28" s="91">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="43"/>
-      <c r="D29" s="20">
-        <v>0</v>
-      </c>
-      <c r="E29" s="20">
+      <c r="C29" s="137">
+        <v>37</v>
+      </c>
+      <c r="D29" s="19">
+        <v>0</v>
+      </c>
+      <c r="E29" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="55" t="s">
+      <c r="A30" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="20">
-        <v>0</v>
-      </c>
-      <c r="E30" s="20">
+      <c r="C30" s="137">
+        <v>38</v>
+      </c>
+      <c r="D30" s="19">
+        <v>0</v>
+      </c>
+      <c r="E30" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="51" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="43"/>
-      <c r="D31" s="20">
-        <v>0</v>
-      </c>
-      <c r="E31" s="20">
+      <c r="C31" s="137">
+        <v>39</v>
+      </c>
+      <c r="D31" s="19">
+        <v>0</v>
+      </c>
+      <c r="E31" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="55" t="s">
+      <c r="A32" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="43"/>
-      <c r="D32" s="20">
-        <v>0</v>
-      </c>
-      <c r="E32" s="20">
+      <c r="C32" s="137">
+        <v>40</v>
+      </c>
+      <c r="D32" s="19">
+        <v>0</v>
+      </c>
+      <c r="E32" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="43"/>
-      <c r="D33" s="20">
-        <v>0</v>
-      </c>
-      <c r="E33" s="20">
+      <c r="C33" s="137">
+        <v>41</v>
+      </c>
+      <c r="D33" s="19">
+        <v>0</v>
+      </c>
+      <c r="E33" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="20">
-        <v>0</v>
-      </c>
-      <c r="E34" s="20">
+      <c r="C34" s="137">
+        <v>42</v>
+      </c>
+      <c r="D34" s="19">
+        <v>0</v>
+      </c>
+      <c r="E34" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
-      <c r="B35" s="99" t="s">
+      <c r="A35" s="51"/>
+      <c r="B35" s="93" t="s">
         <v>243</v>
       </c>
-      <c r="C35" s="99"/>
-      <c r="D35" s="100">
+      <c r="C35" s="93"/>
+      <c r="D35" s="94">
         <f>SUM($D29:$D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="100">
+      <c r="E35" s="94">
         <f>SUM($E29:$E34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="73" t="s">
+      <c r="A36" s="12"/>
+      <c r="B36" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="73"/>
-      <c r="D36" s="75">
+      <c r="C36" s="68"/>
+      <c r="D36" s="70">
         <f>SUM(D15+D26+D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E36" s="70">
         <f>SUM(E15+E26+E35)</f>
         <v>0</v>
       </c>
@@ -3588,13 +3678,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3603,282 +3693,277 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="114" t="str">
+      <c r="B2" s="105" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="105" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="116">
+      <c r="B4" s="107">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="116">
+      <c r="B5" s="107">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>281</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="84">
+      <c r="C9" s="79"/>
+      <c r="D9" s="78">
         <f>DATE(YEAR(B5),1,1)</f>
         <v>45292</v>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="115" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="15">
-        <v>0</v>
-      </c>
-      <c r="E10" s="14"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="49"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="34"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="31"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="84">
+      <c r="C12" s="79"/>
+      <c r="D12" s="78">
         <f>DATE(YEAR(B5),1,1)</f>
         <v>45292</v>
       </c>
-      <c r="E12" s="84">
+      <c r="E12" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="117" t="s">
         <v>245</v>
       </c>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="15">
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="121" t="s">
+      <c r="B14" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="15">
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="49"/>
-      <c r="B15" s="120" t="s">
+      <c r="A15" s="45"/>
+      <c r="B15" s="116" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="76">
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="71">
         <f>SUM(E13:E14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="49"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="59"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="55"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="86">
+      <c r="C17" s="20"/>
+      <c r="D17" s="80">
         <f>DATE(YEAR(B4),1,1)</f>
         <v>45292</v>
       </c>
-      <c r="E17" s="84">
+      <c r="E17" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="45" t="s">
         <v>246</v>
       </c>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="15">
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="B19" s="125" t="s">
+      <c r="B19" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="15">
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="118" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="15">
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="45" t="s">
         <v>249</v>
       </c>
-      <c r="B21" s="121" t="s">
+      <c r="B21" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="15">
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="49"/>
-      <c r="B22" s="120" t="s">
+      <c r="A22" s="45"/>
+      <c r="B22" s="116" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="120"/>
-      <c r="D22" s="120"/>
-      <c r="E22" s="76">
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="71">
         <f>SUM(E18:E21)</f>
         <v>0</v>
       </c>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="49"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="59"/>
+      <c r="A23" s="45"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="55"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="116" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="120"/>
-      <c r="D24" s="120"/>
-      <c r="E24" s="71">
+      <c r="C24" s="116"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="66">
         <f>SUM(D10,E15,E22)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B24:D24"/>
@@ -3890,6 +3975,11 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -3916,667 +4006,711 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="114" t="str">
+      <c r="B2" s="105" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="105" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="116">
+      <c r="B4" s="107">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="116">
+      <c r="B5" s="107">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>280</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="123" t="s">
+      <c r="B9" s="121" t="s">
         <v>244</v>
       </c>
-      <c r="C9" s="123"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="121"/>
+      <c r="D9" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="111" t="s">
         <v>245</v>
       </c>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="23">
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="124"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
+      <c r="A11" s="122"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
     </row>
     <row r="12" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="121" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="123"/>
-      <c r="D12" s="84" t="s">
+      <c r="C12" s="121"/>
+      <c r="D12" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="84">
+      <c r="E12" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="B13" s="125" t="s">
+      <c r="B13" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="125"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="23">
+      <c r="C13" s="118"/>
+      <c r="D13" s="136">
+        <v>26</v>
+      </c>
+      <c r="E13" s="22">
         <v>0</v>
       </c>
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="45" t="s">
         <v>261</v>
       </c>
-      <c r="B14" s="125" t="s">
+      <c r="B14" s="118" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="125"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="23">
+      <c r="C14" s="118"/>
+      <c r="D14" s="136">
+        <v>32</v>
+      </c>
+      <c r="E14" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="45" t="s">
         <v>265</v>
       </c>
-      <c r="B15" s="125" t="s">
+      <c r="B15" s="118" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="125"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="23">
+      <c r="C15" s="118"/>
+      <c r="D15" s="136">
+        <v>36</v>
+      </c>
+      <c r="E15" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="45" t="s">
         <v>250</v>
       </c>
-      <c r="B16" s="125" t="s">
+      <c r="B16" s="118" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="125"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="23">
+      <c r="C16" s="118"/>
+      <c r="D16" s="136">
+        <v>33</v>
+      </c>
+      <c r="E16" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="B17" s="125" t="s">
+      <c r="B17" s="118" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="125"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="23">
+      <c r="C17" s="118"/>
+      <c r="D17" s="136">
+        <v>34</v>
+      </c>
+      <c r="E17" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="118" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="23">
+      <c r="C18" s="118"/>
+      <c r="D18" s="136">
+        <v>35</v>
+      </c>
+      <c r="E18" s="22">
         <v>0</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="45" t="s">
         <v>266</v>
       </c>
-      <c r="B19" s="125" t="s">
+      <c r="B19" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="125"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="23">
+      <c r="C19" s="118"/>
+      <c r="D19" s="136">
+        <v>27</v>
+      </c>
+      <c r="E19" s="22">
         <v>0</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="118" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="23">
+      <c r="C20" s="118"/>
+      <c r="D20" s="136">
+        <v>28</v>
+      </c>
+      <c r="E20" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="45" t="s">
         <v>253</v>
       </c>
-      <c r="B21" s="125" t="s">
+      <c r="B21" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="125"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="23">
+      <c r="C21" s="118"/>
+      <c r="D21" s="136">
+        <v>37</v>
+      </c>
+      <c r="E21" s="22">
         <v>0</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="B22" s="125" t="s">
+      <c r="B22" s="118" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="125"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="23">
+      <c r="C22" s="118"/>
+      <c r="D22" s="136">
+        <v>38</v>
+      </c>
+      <c r="E22" s="22">
         <v>0</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="B23" s="125" t="s">
+      <c r="B23" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="125"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="23">
+      <c r="C23" s="118"/>
+      <c r="D23" s="136">
+        <v>39</v>
+      </c>
+      <c r="E23" s="22">
         <v>0</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="45" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="125" t="s">
+      <c r="B24" s="118" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="125"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="23">
+      <c r="C24" s="118"/>
+      <c r="D24" s="136">
+        <v>40</v>
+      </c>
+      <c r="E24" s="22">
         <v>0</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="B25" s="140" t="s">
+      <c r="B25" s="119" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="140"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="23">
+      <c r="C25" s="119"/>
+      <c r="D25" s="136">
+        <v>41</v>
+      </c>
+      <c r="E25" s="22">
         <v>0</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="B26" s="140" t="s">
+      <c r="B26" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="140"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="23">
+      <c r="C26" s="119"/>
+      <c r="D26" s="136">
+        <v>42</v>
+      </c>
+      <c r="E26" s="22">
         <v>0</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="B27" s="125" t="s">
+      <c r="B27" s="118" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="125"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="23">
+      <c r="C27" s="118"/>
+      <c r="D27" s="136">
+        <v>25</v>
+      </c>
+      <c r="E27" s="22">
         <v>0</v>
       </c>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="49"/>
-      <c r="B28" s="113" t="s">
+      <c r="A28" s="45"/>
+      <c r="B28" s="111" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="113"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="71">
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="66">
         <f>E10+SUM(E13:E27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="49"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="32"/>
+      <c r="A29" s="45"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="29"/>
     </row>
     <row r="30" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="123" t="s">
+      <c r="B30" s="121" t="s">
         <v>146</v>
       </c>
-      <c r="C30" s="123"/>
-      <c r="D30" s="84" t="s">
+      <c r="C30" s="121"/>
+      <c r="D30" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="84">
+      <c r="E30" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="45" t="s">
         <v>262</v>
       </c>
-      <c r="B31" s="140" t="s">
+      <c r="B31" s="119" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="140"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="23">
+      <c r="C31" s="119"/>
+      <c r="D31" s="136">
+        <v>29</v>
+      </c>
+      <c r="E31" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="45" t="s">
         <v>263</v>
       </c>
-      <c r="B32" s="140" t="s">
+      <c r="B32" s="119" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="140"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="23">
+      <c r="C32" s="119"/>
+      <c r="D32" s="136">
+        <v>30</v>
+      </c>
+      <c r="E32" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="49" t="s">
+      <c r="A33" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="B33" s="140" t="s">
+      <c r="B33" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="140"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="23">
+      <c r="C33" s="119"/>
+      <c r="D33" s="136">
+        <v>31</v>
+      </c>
+      <c r="E33" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="49"/>
-      <c r="B34" s="113" t="s">
+      <c r="A34" s="45"/>
+      <c r="B34" s="111" t="s">
         <v>147</v>
       </c>
-      <c r="C34" s="113"/>
-      <c r="D34" s="113"/>
-      <c r="E34" s="71">
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="66">
         <f>E10+E28+SUM(E31:E33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="49"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="77"/>
+      <c r="A35" s="45"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="72"/>
     </row>
     <row r="36" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="121" t="s">
         <v>148</v>
       </c>
-      <c r="C36" s="123"/>
-      <c r="D36" s="84" t="s">
+      <c r="C36" s="121"/>
+      <c r="D36" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="84">
+      <c r="E36" s="78">
         <f>$B$5</f>
         <v>45657</v>
       </c>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="45" t="s">
         <v>267</v>
       </c>
-      <c r="B37" s="140" t="s">
+      <c r="B37" s="119" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="140"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="23">
+      <c r="C37" s="119"/>
+      <c r="D37" s="136">
+        <v>24</v>
+      </c>
+      <c r="E37" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="49"/>
-      <c r="B38" s="113" t="s">
+      <c r="A38" s="45"/>
+      <c r="B38" s="111" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="71">
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="66">
         <f>E10+E28+E34+SUM(E37:E37)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="49"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="77"/>
+      <c r="A39" s="45"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="72"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="49"/>
-      <c r="B40" s="113" t="s">
+      <c r="A40" s="45"/>
+      <c r="B40" s="111" t="s">
         <v>150</v>
       </c>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
-      <c r="E40" s="71">
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="66">
         <f>SUM(E28,E34,E38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="49"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="77"/>
+      <c r="A41" s="45"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="72"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="49" t="s">
+      <c r="A42" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="126" t="s">
+      <c r="B42" s="120" t="s">
         <v>152</v>
       </c>
-      <c r="C42" s="126"/>
-      <c r="D42" s="126"/>
-      <c r="E42" s="23"/>
+      <c r="C42" s="120"/>
+      <c r="D42" s="120"/>
+      <c r="E42" s="22"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="49"/>
-      <c r="B43" s="113" t="s">
+      <c r="A43" s="45"/>
+      <c r="B43" s="111" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="113"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="78">
+      <c r="C43" s="111"/>
+      <c r="D43" s="139">
+        <v>43</v>
+      </c>
+      <c r="E43" s="73">
         <f>E40+E42</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="49"/>
-      <c r="B44" s="113" t="s">
+      <c r="A44" s="45"/>
+      <c r="B44" s="111" t="s">
         <v>154</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="113"/>
-      <c r="E44" s="78">
+      <c r="C44" s="111"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="73">
         <f>'Statement of financial position'!D22</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="49"/>
-      <c r="B45" s="113" t="s">
+      <c r="A45" s="45"/>
+      <c r="B45" s="111" t="s">
         <v>155</v>
       </c>
-      <c r="C45" s="113"/>
-      <c r="D45" s="113"/>
-      <c r="E45" s="78">
+      <c r="C45" s="111"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="73">
         <f>'Statement of financial position'!E22</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A46" s="49"/>
-      <c r="B46" s="113" t="s">
+      <c r="A46" s="45"/>
+      <c r="B46" s="111" t="s">
         <v>156</v>
       </c>
-      <c r="C46" s="113"/>
-      <c r="D46" s="113"/>
-      <c r="E46" s="78">
+      <c r="C46" s="111"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="73">
         <f>E45-E44</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A47" s="34"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A48" s="34"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
+      <c r="A48" s="31"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
     </row>
     <row r="49" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="34"/>
-      <c r="B49" s="65" t="s">
+      <c r="A49" s="31"/>
+      <c r="B49" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
     </row>
     <row r="50" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A50" s="34"/>
-      <c r="B50" s="33">
+      <c r="A50" s="31"/>
+      <c r="B50" s="30">
         <v>7.18</v>
       </c>
-      <c r="C50" s="49" t="s">
+      <c r="C50" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="34"/>
+      <c r="D50" s="136"/>
+      <c r="E50" s="31"/>
     </row>
     <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A51" s="34"/>
-      <c r="B51" s="33" t="s">
+      <c r="A51" s="31"/>
+      <c r="B51" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="C51" s="49" t="s">
+      <c r="C51" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="34"/>
+      <c r="D51" s="136"/>
+      <c r="E51" s="31"/>
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A52" s="34"/>
-      <c r="B52" s="33" t="s">
+      <c r="A52" s="31"/>
+      <c r="B52" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="49" t="s">
+      <c r="C52" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="D52" s="12"/>
-      <c r="E52" s="34"/>
+      <c r="D52" s="136"/>
+      <c r="E52" s="31"/>
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A53" s="34"/>
-      <c r="B53" s="33" t="s">
+      <c r="A53" s="31"/>
+      <c r="B53" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="C53" s="49" t="s">
+      <c r="C53" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="34"/>
+      <c r="D53" s="136"/>
+      <c r="E53" s="31"/>
     </row>
     <row r="54" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A54" s="34"/>
-      <c r="B54" s="33">
+      <c r="A54" s="31"/>
+      <c r="B54" s="30">
         <v>7.21</v>
       </c>
-      <c r="C54" s="49" t="s">
+      <c r="C54" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="D54" s="12"/>
-      <c r="E54" s="34"/>
+      <c r="D54" s="136"/>
+      <c r="E54" s="31"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="28"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
+      <c r="A55" s="25"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="28"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E3"/>
@@ -4590,23 +4724,19 @@
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B38:D38"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
@@ -4632,199 +4762,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="114" t="str">
+      <c r="B2" s="105" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="105" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="116">
+      <c r="B4" s="107">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="116">
+      <c r="B5" s="107">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="130" t="s">
+      <c r="A9" s="125" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="128"/>
-      <c r="B10" s="128"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="128"/>
+      <c r="A10" s="124"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="128"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="128"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="128"/>
+      <c r="A12" s="124"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="129"/>
-      <c r="B13" s="129"/>
-      <c r="C13" s="129"/>
-      <c r="D13" s="129"/>
+      <c r="A13" s="126"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="129"/>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
+      <c r="A14" s="126"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="129"/>
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
+      <c r="A15" s="126"/>
+      <c r="B15" s="126"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="129"/>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
+      <c r="A16" s="126"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="129"/>
-      <c r="B17" s="129"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
+      <c r="A17" s="126"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="128"/>
-      <c r="B18" s="128"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="128"/>
+      <c r="A18" s="124"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="128"/>
-      <c r="B19" s="128"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
+      <c r="A19" s="124"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="128"/>
-      <c r="B20" s="128"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
+      <c r="A20" s="124"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="128"/>
-      <c r="B21" s="128"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="128"/>
+      <c r="A21" s="124"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="128"/>
-      <c r="B22" s="128"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="128"/>
+      <c r="A22" s="124"/>
+      <c r="B22" s="124"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="124"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="128"/>
-      <c r="B23" s="128"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
+      <c r="A23" s="124"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="124"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="128"/>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
+      <c r="A24" s="124"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="124"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="128"/>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
+      <c r="A25" s="124"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="128"/>
-      <c r="B26" s="128"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="128"/>
+      <c r="A26" s="124"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="128"/>
-      <c r="B27" s="128"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="128"/>
+      <c r="A27" s="124"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="124"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="128"/>
-      <c r="B28" s="128"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
+      <c r="A28" s="124"/>
+      <c r="B28" s="124"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="124"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="127"/>
@@ -4833,621 +4963,633 @@
       <c r="D29" s="127"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="78" t="s">
         <v>167</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A31" s="44">
+      <c r="A31" s="40">
         <v>1</v>
       </c>
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="23">
-        <v>0</v>
-      </c>
-      <c r="D31" s="24"/>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
+      <c r="D31" s="97"/>
     </row>
     <row r="32" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A32" s="44">
+      <c r="A32" s="40">
         <v>2</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="80"/>
-      <c r="D32" s="24"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="97"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="36">
-        <v>2.1</v>
-      </c>
-      <c r="B33" s="41" t="s">
+      <c r="A33" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="B33" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="C33" s="23">
-        <v>0</v>
-      </c>
-      <c r="D33" s="26"/>
+      <c r="C33" s="22">
+        <v>0</v>
+      </c>
+      <c r="D33" s="24"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="36">
+      <c r="A34" s="33">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="23">
-        <v>0</v>
-      </c>
-      <c r="D34" s="26"/>
+      <c r="C34" s="22">
+        <v>0</v>
+      </c>
+      <c r="D34" s="24"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="36">
+      <c r="A35" s="33">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C35" s="25">
-        <v>0</v>
-      </c>
-      <c r="D35" s="26"/>
+      <c r="C35" s="23">
+        <v>0</v>
+      </c>
+      <c r="D35" s="24"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="36">
+      <c r="A36" s="33">
         <v>2.4</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="C36" s="23">
-        <v>0</v>
-      </c>
-      <c r="D36" s="26"/>
+      <c r="C36" s="22">
+        <v>0</v>
+      </c>
+      <c r="D36" s="24"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="36">
+      <c r="A37" s="33">
         <v>2.5</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="C37" s="23">
-        <v>0</v>
-      </c>
-      <c r="D37" s="26"/>
+      <c r="C37" s="22">
+        <v>0</v>
+      </c>
+      <c r="D37" s="24"/>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="36">
+      <c r="A38" s="33">
         <v>2.6</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="C38" s="23">
-        <v>0</v>
-      </c>
-      <c r="D38" s="26"/>
+      <c r="C38" s="22">
+        <v>0</v>
+      </c>
+      <c r="D38" s="24"/>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="36">
+      <c r="A39" s="33">
         <v>2.7</v>
       </c>
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="C39" s="23">
-        <v>0</v>
-      </c>
-      <c r="D39" s="26"/>
+      <c r="C39" s="22">
+        <v>0</v>
+      </c>
+      <c r="D39" s="24"/>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="36">
+      <c r="A40" s="33">
         <v>2.8</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="23">
-        <v>0</v>
-      </c>
-      <c r="D40" s="26"/>
+      <c r="C40" s="22">
+        <v>0</v>
+      </c>
+      <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="36">
+      <c r="A41" s="33">
         <v>2.9</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="23">
-        <v>0</v>
-      </c>
-      <c r="D41" s="26"/>
+      <c r="C41" s="22">
+        <v>0</v>
+      </c>
+      <c r="D41" s="24"/>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
+      <c r="A42" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="C42" s="23">
-        <v>0</v>
-      </c>
-      <c r="D42" s="26"/>
+      <c r="C42" s="22">
+        <v>0</v>
+      </c>
+      <c r="D42" s="24"/>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="36" t="s">
+      <c r="A43" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="C43" s="23">
-        <v>0</v>
-      </c>
-      <c r="D43" s="26"/>
+      <c r="C43" s="22">
+        <v>0</v>
+      </c>
+      <c r="D43" s="24"/>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="C44" s="23">
-        <v>0</v>
-      </c>
-      <c r="D44" s="26"/>
+      <c r="C44" s="22">
+        <v>0</v>
+      </c>
+      <c r="D44" s="24"/>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="B45" s="41" t="s">
+      <c r="B45" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="C45" s="23">
-        <v>0</v>
-      </c>
-      <c r="D45" s="26"/>
+      <c r="C45" s="22">
+        <v>0</v>
+      </c>
+      <c r="D45" s="24"/>
     </row>
     <row r="46" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="C46" s="23">
-        <v>0</v>
-      </c>
-      <c r="D46" s="26"/>
+      <c r="C46" s="22">
+        <v>0</v>
+      </c>
+      <c r="D46" s="24"/>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="C47" s="23">
-        <v>0</v>
-      </c>
-      <c r="D47" s="26"/>
+      <c r="C47" s="22">
+        <v>0</v>
+      </c>
+      <c r="D47" s="24"/>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="36"/>
-      <c r="B48" s="53" t="s">
+      <c r="A48" s="33"/>
+      <c r="B48" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="C48" s="71">
+      <c r="C48" s="66">
         <f>SUM(C33:C47)</f>
         <v>0</v>
       </c>
-      <c r="D48" s="26"/>
+      <c r="D48" s="24"/>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="44">
+      <c r="A49" s="40">
         <v>3</v>
       </c>
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="C49" s="25">
-        <v>0</v>
-      </c>
-      <c r="D49" s="26"/>
+      <c r="C49" s="23">
+        <v>0</v>
+      </c>
+      <c r="D49" s="24"/>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="44">
+      <c r="A50" s="40">
         <v>4</v>
       </c>
-      <c r="B50" s="49" t="s">
+      <c r="B50" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="25">
-        <v>0</v>
-      </c>
-      <c r="D50" s="27"/>
+      <c r="C50" s="23">
+        <v>0</v>
+      </c>
+      <c r="D50" s="24"/>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="45"/>
-      <c r="B51" s="53" t="s">
+      <c r="A51" s="140"/>
+      <c r="B51" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="71">
+      <c r="C51" s="66">
         <f>SUM($C31+$C48+$C49+$C50)</f>
         <v>0</v>
       </c>
-      <c r="D51" s="30"/>
+      <c r="D51" s="27"/>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="45"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="30"/>
+      <c r="A52" s="41"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="27"/>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="84" t="s">
+      <c r="A53" s="78" t="s">
         <v>167</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="C53" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="44">
+      <c r="A54" s="40">
         <v>5</v>
       </c>
-      <c r="B54" s="49" t="s">
+      <c r="B54" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C54" s="25">
-        <v>0</v>
-      </c>
-      <c r="D54" s="27"/>
+      <c r="C54" s="23">
+        <v>0</v>
+      </c>
+      <c r="D54" s="24"/>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="44" t="s">
+      <c r="A55" s="40" t="s">
         <v>269</v>
       </c>
-      <c r="B55" s="49" t="s">
+      <c r="B55" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="C55" s="25">
-        <v>0</v>
-      </c>
-      <c r="D55" s="27"/>
+      <c r="C55" s="23">
+        <v>0</v>
+      </c>
+      <c r="D55" s="24"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="44" t="s">
+      <c r="A56" s="40" t="s">
         <v>270</v>
       </c>
-      <c r="B56" s="49" t="s">
+      <c r="B56" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="25">
-        <v>0</v>
-      </c>
-      <c r="D56" s="24"/>
+      <c r="C56" s="23">
+        <v>0</v>
+      </c>
+      <c r="D56" s="97"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="46" t="s">
+      <c r="A57" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="B57" s="49" t="s">
+      <c r="B57" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="25">
-        <v>0</v>
-      </c>
-      <c r="D57" s="27"/>
+      <c r="C57" s="23">
+        <v>0</v>
+      </c>
+      <c r="D57" s="24"/>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="47"/>
-      <c r="B58" s="53" t="s">
+      <c r="A58" s="43"/>
+      <c r="B58" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="71">
+      <c r="C58" s="66">
         <f>SUM(C54:C57)</f>
         <v>0</v>
       </c>
-      <c r="D58" s="34"/>
+      <c r="D58" s="31"/>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="47"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="34"/>
+      <c r="A59" s="43"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="31"/>
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="78" t="s">
         <v>167</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="44" t="s">
+      <c r="A61" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="B61" s="41" t="s">
+      <c r="B61" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="25">
-        <v>0</v>
-      </c>
-      <c r="D61" s="27"/>
+      <c r="C61" s="23">
+        <v>0</v>
+      </c>
+      <c r="D61" s="24"/>
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="44" t="s">
+      <c r="A62" s="40" t="s">
         <v>273</v>
       </c>
-      <c r="B62" s="41" t="s">
+      <c r="B62" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="25">
-        <v>0</v>
-      </c>
-      <c r="D62" s="27"/>
+      <c r="C62" s="23">
+        <v>0</v>
+      </c>
+      <c r="D62" s="24"/>
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="44" t="s">
+      <c r="A63" s="40" t="s">
         <v>274</v>
       </c>
-      <c r="B63" s="41" t="s">
+      <c r="B63" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="25">
-        <v>0</v>
-      </c>
-      <c r="D63" s="27"/>
+      <c r="C63" s="23">
+        <v>0</v>
+      </c>
+      <c r="D63" s="24"/>
     </row>
     <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="44" t="s">
+      <c r="A64" s="40" t="s">
         <v>275</v>
       </c>
-      <c r="B64" s="41" t="s">
+      <c r="B64" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C64" s="25">
-        <v>0</v>
-      </c>
-      <c r="D64" s="27"/>
+      <c r="C64" s="23">
+        <v>0</v>
+      </c>
+      <c r="D64" s="24"/>
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="44" t="s">
+      <c r="A65" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="B65" s="41" t="s">
+      <c r="B65" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C65" s="25">
-        <v>0</v>
-      </c>
-      <c r="D65" s="27"/>
+      <c r="C65" s="23">
+        <v>0</v>
+      </c>
+      <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A66" s="35"/>
-      <c r="B66" s="62" t="s">
+      <c r="A66" s="32"/>
+      <c r="B66" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="C66" s="81">
+      <c r="C66" s="75">
         <f>SUM(C61:C65)</f>
         <v>0</v>
       </c>
-      <c r="D66" s="28"/>
+      <c r="D66" s="25"/>
     </row>
     <row r="67" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A67" s="35"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="28"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="34"/>
+      <c r="D67" s="25"/>
     </row>
     <row r="68" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A68" s="84" t="s">
+      <c r="A68" s="78" t="s">
         <v>167</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C68" s="22" t="s">
+      <c r="C68" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="D68" s="22" t="s">
+      <c r="D68" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A69" s="48" t="s">
+      <c r="A69" s="44" t="s">
         <v>277</v>
       </c>
-      <c r="B69" s="41" t="s">
+      <c r="B69" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="101">
-        <v>0</v>
-      </c>
-      <c r="D69" s="70"/>
+      <c r="C69" s="95">
+        <v>0</v>
+      </c>
+      <c r="D69" s="138"/>
     </row>
     <row r="70" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A70" s="48" t="s">
+      <c r="A70" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="B70" s="41" t="s">
+      <c r="B70" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C70" s="101">
-        <v>0</v>
-      </c>
-      <c r="D70" s="70"/>
+      <c r="C70" s="95">
+        <v>0</v>
+      </c>
+      <c r="D70" s="138"/>
     </row>
     <row r="71" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A71" s="48" t="s">
+      <c r="A71" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="B71" s="41" t="s">
+      <c r="B71" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C71" s="15">
-        <v>0</v>
-      </c>
-      <c r="D71" s="70"/>
+      <c r="C71" s="14">
+        <v>0</v>
+      </c>
+      <c r="D71" s="138"/>
     </row>
     <row r="72" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A72" s="35"/>
-      <c r="B72" s="62" t="s">
+      <c r="A72" s="32"/>
+      <c r="B72" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="72">
+      <c r="C72" s="67">
         <f>SUM($C69:$C71)</f>
         <v>0</v>
       </c>
-      <c r="D72" s="28"/>
+      <c r="D72" s="25"/>
     </row>
     <row r="73" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A73" s="35"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="31"/>
-      <c r="D73" s="28"/>
+      <c r="A73" s="32"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="28"/>
+      <c r="D73" s="25"/>
     </row>
     <row r="74" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A74" s="84" t="s">
+      <c r="A74" s="78" t="s">
         <v>167</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A75" s="48" t="s">
+      <c r="A75" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="B75" s="41" t="s">
+      <c r="B75" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="C75" s="15">
-        <v>0</v>
-      </c>
-      <c r="D75" s="70"/>
+      <c r="C75" s="14">
+        <v>0</v>
+      </c>
+      <c r="D75" s="138"/>
     </row>
     <row r="76" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A76" s="48" t="s">
+      <c r="A76" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="B76" s="41" t="s">
+      <c r="B76" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C76" s="15">
-        <v>0</v>
-      </c>
-      <c r="D76" s="70"/>
+      <c r="C76" s="14">
+        <v>0</v>
+      </c>
+      <c r="D76" s="138"/>
     </row>
     <row r="77" spans="1:4" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A77" s="48" t="s">
+      <c r="A77" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="B77" s="41" t="s">
+      <c r="B77" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="C77" s="15">
-        <v>0</v>
-      </c>
-      <c r="D77" s="70"/>
+      <c r="C77" s="14">
+        <v>0</v>
+      </c>
+      <c r="D77" s="138"/>
     </row>
     <row r="78" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A78" s="48" t="s">
+      <c r="A78" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="B78" s="41" t="s">
+      <c r="B78" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="15">
-        <v>0</v>
-      </c>
-      <c r="D78" s="70"/>
+      <c r="C78" s="14">
+        <v>0</v>
+      </c>
+      <c r="D78" s="138"/>
     </row>
     <row r="79" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A79" s="48" t="s">
+      <c r="A79" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="B79" s="41" t="s">
+      <c r="B79" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="15">
-        <v>0</v>
-      </c>
-      <c r="D79" s="70"/>
+      <c r="C79" s="14">
+        <v>0</v>
+      </c>
+      <c r="D79" s="138"/>
     </row>
     <row r="80" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A80" s="48" t="s">
+      <c r="A80" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="B80" s="41" t="s">
+      <c r="B80" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="C80" s="15">
-        <v>0</v>
-      </c>
-      <c r="D80" s="70"/>
+      <c r="C80" s="14">
+        <v>0</v>
+      </c>
+      <c r="D80" s="138"/>
     </row>
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A81" s="48" t="s">
+      <c r="A81" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="B81" s="41" t="s">
+      <c r="B81" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C81" s="15">
-        <v>0</v>
-      </c>
-      <c r="D81" s="70"/>
+      <c r="C81" s="14">
+        <v>0</v>
+      </c>
+      <c r="D81" s="138"/>
     </row>
     <row r="82" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A82" s="35"/>
-      <c r="B82" s="53" t="s">
+      <c r="A82" s="32"/>
+      <c r="B82" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="C82" s="72">
+      <c r="C82" s="67">
         <f>SUM($C75:$C81)</f>
         <v>0</v>
       </c>
-      <c r="D82" s="28"/>
+      <c r="D82" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5463,18 +5605,6 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5482,6 +5612,9 @@
   <headerFooter>
     <oddFooter>&amp;C© www.banana.ch/it/it&amp;R&amp;P</oddFooter>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A42 A43:A47 A55:A57 A61:A65 A69:A71 A75:A81 A33" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5501,77 +5634,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="114" t="str">
+      <c r="B2" s="105" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="114" t="str">
+      <c r="B3" s="105" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="116">
+      <c r="B4" s="107">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="116">
+      <c r="B5" s="107">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -5580,89 +5713,89 @@
       <c r="B9" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C9" s="98" t="s">
+      <c r="C9" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="41" t="s">
+      <c r="A10" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="25">
-        <v>0</v>
-      </c>
-      <c r="D10" s="24"/>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="97"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="B11" s="41" t="s">
+      <c r="A11" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="25">
-        <v>0</v>
-      </c>
-      <c r="D11" s="24"/>
+      <c r="C11" s="23">
+        <v>0</v>
+      </c>
+      <c r="D11" s="97"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="B12" s="41" t="s">
+      <c r="A12" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="25">
-        <v>0</v>
-      </c>
-      <c r="D12" s="26"/>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="41" t="s">
+      <c r="A13" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="25">
-        <v>0</v>
-      </c>
-      <c r="D13" s="26"/>
+      <c r="C13" s="23">
+        <v>0</v>
+      </c>
+      <c r="D13" s="24"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="B14" s="41" t="s">
+      <c r="A14" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="25">
-        <v>0</v>
-      </c>
-      <c r="D14" s="26"/>
+      <c r="C14" s="23">
+        <v>0</v>
+      </c>
+      <c r="D14" s="24"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45"/>
-      <c r="B15" s="62" t="s">
+      <c r="A15" s="41"/>
+      <c r="B15" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="C15" s="71">
+      <c r="C15" s="66">
         <f>SUM(C10:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="41"/>
+      <c r="D15" s="38"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="45"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="41"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="38"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
@@ -5671,191 +5804,191 @@
       <c r="B17" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="98" t="s">
+      <c r="C17" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="44" t="s">
-        <v>210</v>
-      </c>
-      <c r="B18" s="41" t="s">
+      <c r="A18" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="25">
-        <v>0</v>
-      </c>
-      <c r="D18" s="26"/>
+      <c r="C18" s="23">
+        <v>0</v>
+      </c>
+      <c r="D18" s="24"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
-        <v>211</v>
-      </c>
-      <c r="B19" s="41" t="s">
+      <c r="A19" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="25">
-        <v>0</v>
-      </c>
-      <c r="D19" s="26"/>
+      <c r="C19" s="23">
+        <v>0</v>
+      </c>
+      <c r="D19" s="24"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="B20" s="41" t="s">
+      <c r="A20" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="25">
-        <v>0</v>
-      </c>
-      <c r="D20" s="26"/>
+      <c r="C20" s="23">
+        <v>0</v>
+      </c>
+      <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="44" t="s">
-        <v>213</v>
-      </c>
-      <c r="B21" s="41" t="s">
+      <c r="A21" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="B21" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="25">
-        <v>0</v>
-      </c>
-      <c r="D21" s="26"/>
+      <c r="C21" s="23">
+        <v>0</v>
+      </c>
+      <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="44" t="s">
-        <v>214</v>
-      </c>
-      <c r="B22" s="41" t="s">
+      <c r="A22" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="B22" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="25">
-        <v>0</v>
-      </c>
-      <c r="D22" s="26"/>
+      <c r="C22" s="23">
+        <v>0</v>
+      </c>
+      <c r="D22" s="24"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="44" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" s="41" t="s">
+      <c r="A23" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="25">
-        <v>0</v>
-      </c>
-      <c r="D23" s="26"/>
+      <c r="C23" s="23">
+        <v>0</v>
+      </c>
+      <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" s="41" t="s">
+      <c r="A24" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="B24" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="25">
-        <v>0</v>
-      </c>
-      <c r="D24" s="26"/>
+      <c r="C24" s="23">
+        <v>0</v>
+      </c>
+      <c r="D24" s="24"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="B25" s="41" t="s">
+      <c r="A25" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="B25" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="25">
-        <v>0</v>
-      </c>
-      <c r="D25" s="26"/>
+      <c r="C25" s="23">
+        <v>0</v>
+      </c>
+      <c r="D25" s="24"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="44" t="s">
-        <v>218</v>
-      </c>
-      <c r="B26" s="41" t="s">
+      <c r="A26" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="25">
-        <v>0</v>
-      </c>
-      <c r="D26" s="26"/>
+      <c r="C26" s="23">
+        <v>0</v>
+      </c>
+      <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="44" t="s">
-        <v>219</v>
-      </c>
-      <c r="B27" s="41" t="s">
+      <c r="A27" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="C27" s="25">
-        <v>0</v>
-      </c>
-      <c r="D27" s="26"/>
+      <c r="C27" s="23">
+        <v>0</v>
+      </c>
+      <c r="D27" s="24"/>
     </row>
     <row r="28" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="44" t="s">
-        <v>220</v>
-      </c>
-      <c r="B28" s="41" t="s">
+      <c r="A28" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="25">
-        <v>0</v>
-      </c>
-      <c r="D28" s="26"/>
+      <c r="C28" s="23">
+        <v>0</v>
+      </c>
+      <c r="D28" s="24"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="44" t="s">
-        <v>221</v>
-      </c>
-      <c r="B29" s="41" t="s">
+      <c r="A29" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="25">
-        <v>0</v>
-      </c>
-      <c r="D29" s="26"/>
+      <c r="C29" s="23">
+        <v>0</v>
+      </c>
+      <c r="D29" s="24"/>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="44" t="s">
-        <v>222</v>
-      </c>
-      <c r="B30" s="41" t="s">
+      <c r="A30" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="25">
-        <v>0</v>
-      </c>
-      <c r="D30" s="26"/>
+      <c r="C30" s="23">
+        <v>0</v>
+      </c>
+      <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
-        <v>223</v>
-      </c>
-      <c r="B31" s="33" t="s">
+      <c r="A31" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="B31" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="25">
-        <v>0</v>
-      </c>
-      <c r="D31" s="26"/>
+      <c r="C31" s="23">
+        <v>0</v>
+      </c>
+      <c r="D31" s="24"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="42"/>
-      <c r="B32" s="82" t="s">
+      <c r="A32" s="39"/>
+      <c r="B32" s="76" t="s">
         <v>224</v>
       </c>
-      <c r="C32" s="83">
+      <c r="C32" s="77">
         <f>SUM(C18:C31)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="42"/>
+      <c r="D32" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5871,6 +6004,9 @@
   <headerFooter>
     <oddFooter>&amp;C© www.banana.ch/it/it&amp;R&amp;P</oddFooter>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A10:A14 A18:A31" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5885,997 +6021,1003 @@
     <col min="1" max="1" width="21.77734375" customWidth="1"/>
     <col min="2" max="2" width="58.44140625" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="4" max="8" width="8.88671875" style="63"/>
-    <col min="9" max="9" width="2" style="63" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="63" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="8.77734375" style="63" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="63" hidden="1" customWidth="1"/>
+    <col min="4" max="8" width="8.88671875" style="59"/>
+    <col min="9" max="9" width="2" style="59" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="59" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="8.77734375" style="59" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="59" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
     </row>
     <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="134" t="str">
+      <c r="B2" s="132" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="134"/>
-      <c r="L2" s="134"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="134" t="str">
+      <c r="B3" s="132" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="132"/>
+      <c r="L3" s="132"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="135">
+      <c r="B4" s="133">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="135"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="135">
+      <c r="B5" s="133">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="134" t="s">
         <v>279</v>
       </c>
-      <c r="B6" s="139"/>
-      <c r="C6" s="139"/>
-      <c r="D6" s="139"/>
-      <c r="E6" s="139"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="139"/>
-      <c r="I6" s="139"/>
-      <c r="J6" s="139"/>
-      <c r="K6" s="139"/>
-      <c r="L6" s="139"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="134"/>
+      <c r="D6" s="134"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="134"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="134"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="134"/>
+      <c r="K6" s="134"/>
+      <c r="L6" s="134"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="139"/>
-      <c r="B7" s="139"/>
-      <c r="C7" s="139"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="139"/>
-      <c r="I7" s="139"/>
-      <c r="J7" s="139"/>
-      <c r="K7" s="139"/>
-      <c r="L7" s="139"/>
+      <c r="A7" s="134"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="134"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139"/>
-      <c r="B8" s="139"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="139"/>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
+      <c r="A8" s="134"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="134"/>
+      <c r="J8" s="134"/>
+      <c r="K8" s="134"/>
+      <c r="L8" s="134"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="82" t="s">
         <v>167</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="D9" s="133" t="s">
+      <c r="D9" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="133"/>
-      <c r="L9" s="133"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="130"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="87"/>
-      <c r="B10" s="33" t="s">
+      <c r="A10" s="81"/>
+      <c r="B10" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="C10" s="89">
-        <v>0</v>
-      </c>
-      <c r="D10" s="137"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
+      <c r="C10" s="83">
+        <v>0</v>
+      </c>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="87"/>
-      <c r="B11" s="33" t="s">
+      <c r="A11" s="81"/>
+      <c r="B11" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="C11" s="89">
-        <v>0</v>
-      </c>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
+      <c r="C11" s="83">
+        <v>0</v>
+      </c>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
+      <c r="J11" s="129"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="87"/>
-      <c r="B12" s="33" t="s">
+      <c r="A12" s="81"/>
+      <c r="B12" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="C12" s="89">
-        <v>0</v>
-      </c>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="137"/>
-      <c r="H12" s="137"/>
-      <c r="I12" s="137"/>
-      <c r="J12" s="137"/>
-      <c r="K12" s="137"/>
-      <c r="L12" s="137"/>
+      <c r="C12" s="83">
+        <v>0</v>
+      </c>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="93">
+      <c r="C13" s="87">
         <f>SUM(C10:C12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="87"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="87"/>
-      <c r="L13" s="87"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="87"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
-    </row>
-    <row r="15" spans="1:12" s="96" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88" t="s">
+      <c r="A14" s="81"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+    </row>
+    <row r="15" spans="1:12" s="90" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="82" t="s">
         <v>167</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="D15" s="133" t="s">
+      <c r="D15" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="133"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="87"/>
-      <c r="B16" s="33" t="s">
+      <c r="A16" s="81"/>
+      <c r="B16" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="C16" s="89">
-        <v>0</v>
-      </c>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="137"/>
-      <c r="G16" s="137"/>
-      <c r="H16" s="137"/>
-      <c r="I16" s="137"/>
-      <c r="J16" s="137"/>
-      <c r="K16" s="137"/>
-      <c r="L16" s="137"/>
+      <c r="C16" s="83">
+        <v>0</v>
+      </c>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="129"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="129"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="87"/>
-      <c r="B17" s="33" t="s">
+      <c r="A17" s="81"/>
+      <c r="B17" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="C17" s="89">
-        <v>0</v>
-      </c>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="137"/>
-      <c r="I17" s="137"/>
-      <c r="J17" s="137"/>
-      <c r="K17" s="137"/>
-      <c r="L17" s="137"/>
+      <c r="C17" s="83">
+        <v>0</v>
+      </c>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="129"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="129"/>
     </row>
     <row r="18" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="87"/>
-      <c r="B18" s="33" t="s">
+      <c r="A18" s="81"/>
+      <c r="B18" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="C18" s="89">
-        <v>0</v>
-      </c>
-      <c r="D18" s="137"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="137"/>
-      <c r="H18" s="137"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="137"/>
-      <c r="K18" s="137"/>
-      <c r="L18" s="137"/>
+      <c r="C18" s="83">
+        <v>0</v>
+      </c>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="129"/>
+      <c r="K18" s="129"/>
+      <c r="L18" s="129"/>
     </row>
     <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="95">
+      <c r="A19" s="89">
         <v>7.2</v>
       </c>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="C19" s="93">
+      <c r="C19" s="87">
         <f>SUM(C16:C18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="87"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="87"/>
-      <c r="J20" s="87"/>
-      <c r="K20" s="87"/>
-      <c r="L20" s="87"/>
+      <c r="A20" s="81"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
     </row>
     <row r="21" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="88" t="s">
+      <c r="A21" s="82" t="s">
         <v>167</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="C21" s="94" t="s">
+      <c r="C21" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="133" t="s">
+      <c r="D21" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="133"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="130"/>
+      <c r="K21" s="130"/>
+      <c r="L21" s="130"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="102">
-        <v>0</v>
-      </c>
-      <c r="D22" s="136"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="136"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="136"/>
-      <c r="K22" s="136"/>
-      <c r="L22" s="136"/>
+      <c r="A22" s="81"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="96">
+        <v>0</v>
+      </c>
+      <c r="D22" s="135"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="102">
-        <v>0</v>
-      </c>
-      <c r="D23" s="136"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="136"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="136"/>
-      <c r="K23" s="136"/>
-      <c r="L23" s="136"/>
+      <c r="A23" s="81"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="96">
+        <v>0</v>
+      </c>
+      <c r="D23" s="135"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="135"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="135"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
+      <c r="L23" s="135"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="102">
-        <v>0</v>
-      </c>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="136"/>
-      <c r="G24" s="136"/>
-      <c r="H24" s="136"/>
-      <c r="I24" s="136"/>
-      <c r="J24" s="136"/>
-      <c r="K24" s="136"/>
-      <c r="L24" s="136"/>
+      <c r="A24" s="81"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="96">
+        <v>0</v>
+      </c>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="135"/>
+      <c r="L24" s="135"/>
     </row>
     <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="87">
+      <c r="A25" s="81">
         <v>7.21</v>
       </c>
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="58" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="93">
+      <c r="C25" s="87">
         <f>SUM(C22:C24)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="81"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="81"/>
     </row>
     <row r="27" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="82" t="s">
         <v>167</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C27" s="94" t="s">
+      <c r="C27" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="D27" s="133" t="s">
+      <c r="D27" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="133"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="133"/>
-      <c r="L27" s="133"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="130"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="130"/>
+      <c r="I27" s="130"/>
+      <c r="J27" s="130"/>
+      <c r="K27" s="130"/>
+      <c r="L27" s="130"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="92">
-        <v>0</v>
-      </c>
-      <c r="D28" s="137"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137"/>
-      <c r="H28" s="137"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="137"/>
-      <c r="K28" s="137"/>
-      <c r="L28" s="137"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="86">
+        <v>0</v>
+      </c>
+      <c r="D28" s="129"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="129"/>
+      <c r="I28" s="129"/>
+      <c r="J28" s="129"/>
+      <c r="K28" s="129"/>
+      <c r="L28" s="129"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="87"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="92">
-        <v>0</v>
-      </c>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="137"/>
-      <c r="I29" s="137"/>
-      <c r="J29" s="137"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="137"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="86">
+        <v>0</v>
+      </c>
+      <c r="D29" s="129"/>
+      <c r="E29" s="129"/>
+      <c r="F29" s="129"/>
+      <c r="G29" s="129"/>
+      <c r="H29" s="129"/>
+      <c r="I29" s="129"/>
+      <c r="J29" s="129"/>
+      <c r="K29" s="129"/>
+      <c r="L29" s="129"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="87"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="92">
-        <v>0</v>
-      </c>
-      <c r="D30" s="137"/>
-      <c r="E30" s="137"/>
-      <c r="F30" s="137"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="137"/>
-      <c r="I30" s="137"/>
-      <c r="J30" s="137"/>
-      <c r="K30" s="137"/>
-      <c r="L30" s="137"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="86">
+        <v>0</v>
+      </c>
+      <c r="D30" s="129"/>
+      <c r="E30" s="129"/>
+      <c r="F30" s="129"/>
+      <c r="G30" s="129"/>
+      <c r="H30" s="129"/>
+      <c r="I30" s="129"/>
+      <c r="J30" s="129"/>
+      <c r="K30" s="129"/>
+      <c r="L30" s="129"/>
     </row>
     <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="87">
+      <c r="A31" s="81">
         <v>7.18</v>
       </c>
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="58" t="s">
         <v>237</v>
       </c>
-      <c r="C31" s="93">
+      <c r="C31" s="87">
         <f>SUM(C28:C30)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="87"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="87"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="87"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="87"/>
-      <c r="H32" s="87"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
     </row>
     <row r="33" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="88" t="s">
+      <c r="A33" s="82" t="s">
         <v>167</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C33" s="94" t="s">
+      <c r="C33" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="D33" s="133" t="s">
+      <c r="D33" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="133"/>
-      <c r="H33" s="133"/>
-      <c r="I33" s="133"/>
-      <c r="J33" s="133"/>
-      <c r="K33" s="133"/>
-      <c r="L33" s="133"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="130"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="130"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="130"/>
+      <c r="L33" s="130"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="87"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="92">
-        <v>0</v>
-      </c>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="137"/>
-      <c r="H34" s="137"/>
-      <c r="I34" s="137"/>
-      <c r="J34" s="137"/>
-      <c r="K34" s="137"/>
-      <c r="L34" s="137"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="86">
+        <v>0</v>
+      </c>
+      <c r="D34" s="129"/>
+      <c r="E34" s="129"/>
+      <c r="F34" s="129"/>
+      <c r="G34" s="129"/>
+      <c r="H34" s="129"/>
+      <c r="I34" s="129"/>
+      <c r="J34" s="129"/>
+      <c r="K34" s="129"/>
+      <c r="L34" s="129"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="87"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="92">
-        <v>0</v>
-      </c>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
-      <c r="H35" s="137"/>
-      <c r="I35" s="137"/>
-      <c r="J35" s="137"/>
-      <c r="K35" s="137"/>
-      <c r="L35" s="137"/>
+      <c r="A35" s="81"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="86">
+        <v>0</v>
+      </c>
+      <c r="D35" s="129"/>
+      <c r="E35" s="129"/>
+      <c r="F35" s="129"/>
+      <c r="G35" s="129"/>
+      <c r="H35" s="129"/>
+      <c r="I35" s="129"/>
+      <c r="J35" s="129"/>
+      <c r="K35" s="129"/>
+      <c r="L35" s="129"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="87"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="92">
-        <v>0</v>
-      </c>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="137"/>
-      <c r="H36" s="137"/>
-      <c r="I36" s="137"/>
-      <c r="J36" s="137"/>
-      <c r="K36" s="137"/>
-      <c r="L36" s="137"/>
+      <c r="A36" s="81"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="86">
+        <v>0</v>
+      </c>
+      <c r="D36" s="129"/>
+      <c r="E36" s="129"/>
+      <c r="F36" s="129"/>
+      <c r="G36" s="129"/>
+      <c r="H36" s="129"/>
+      <c r="I36" s="129"/>
+      <c r="J36" s="129"/>
+      <c r="K36" s="129"/>
+      <c r="L36" s="129"/>
     </row>
     <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="87" t="s">
+      <c r="A37" s="81" t="s">
         <v>159</v>
       </c>
-      <c r="B37" s="62" t="s">
+      <c r="B37" s="58" t="s">
         <v>238</v>
       </c>
-      <c r="C37" s="93">
+      <c r="C37" s="87">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
-      <c r="D37" s="87"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="87"/>
-      <c r="G37" s="87"/>
-      <c r="H37" s="87"/>
-      <c r="I37" s="87"/>
-      <c r="J37" s="87"/>
-      <c r="K37" s="87"/>
-      <c r="L37" s="87"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="87"/>
-      <c r="B38" s="53"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="87"/>
+      <c r="A38" s="81"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="88" t="s">
+      <c r="A39" s="82" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="91" t="s">
+      <c r="B39" s="85" t="s">
         <v>162</v>
       </c>
-      <c r="C39" s="94" t="s">
+      <c r="C39" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="133" t="s">
+      <c r="D39" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="133"/>
-      <c r="F39" s="133"/>
-      <c r="G39" s="133"/>
-      <c r="H39" s="133"/>
-      <c r="I39" s="133"/>
-      <c r="J39" s="133"/>
-      <c r="K39" s="133"/>
-      <c r="L39" s="133"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="130"/>
+      <c r="H39" s="130"/>
+      <c r="I39" s="130"/>
+      <c r="J39" s="130"/>
+      <c r="K39" s="130"/>
+      <c r="L39" s="130"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="87"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="92">
-        <v>0</v>
-      </c>
-      <c r="D40" s="137"/>
-      <c r="E40" s="137"/>
-      <c r="F40" s="137"/>
-      <c r="G40" s="137"/>
-      <c r="H40" s="137"/>
-      <c r="I40" s="137"/>
-      <c r="J40" s="137"/>
-      <c r="K40" s="137"/>
-      <c r="L40" s="137"/>
+      <c r="A40" s="81"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="86">
+        <v>0</v>
+      </c>
+      <c r="D40" s="129"/>
+      <c r="E40" s="129"/>
+      <c r="F40" s="129"/>
+      <c r="G40" s="129"/>
+      <c r="H40" s="129"/>
+      <c r="I40" s="129"/>
+      <c r="J40" s="129"/>
+      <c r="K40" s="129"/>
+      <c r="L40" s="129"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="87"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="92">
-        <v>0</v>
-      </c>
-      <c r="D41" s="137"/>
-      <c r="E41" s="137"/>
-      <c r="F41" s="137"/>
-      <c r="G41" s="137"/>
-      <c r="H41" s="137"/>
-      <c r="I41" s="137"/>
-      <c r="J41" s="137"/>
-      <c r="K41" s="137"/>
-      <c r="L41" s="137"/>
+      <c r="A41" s="81"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="86">
+        <v>0</v>
+      </c>
+      <c r="D41" s="129"/>
+      <c r="E41" s="129"/>
+      <c r="F41" s="129"/>
+      <c r="G41" s="129"/>
+      <c r="H41" s="129"/>
+      <c r="I41" s="129"/>
+      <c r="J41" s="129"/>
+      <c r="K41" s="129"/>
+      <c r="L41" s="129"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="87"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="92">
-        <v>0</v>
-      </c>
-      <c r="D42" s="137"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="137"/>
-      <c r="I42" s="137"/>
-      <c r="J42" s="137"/>
-      <c r="K42" s="137"/>
-      <c r="L42" s="137"/>
+      <c r="A42" s="81"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="86">
+        <v>0</v>
+      </c>
+      <c r="D42" s="129"/>
+      <c r="E42" s="129"/>
+      <c r="F42" s="129"/>
+      <c r="G42" s="129"/>
+      <c r="H42" s="129"/>
+      <c r="I42" s="129"/>
+      <c r="J42" s="129"/>
+      <c r="K42" s="129"/>
+      <c r="L42" s="129"/>
     </row>
     <row r="43" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="87" t="s">
+      <c r="A43" s="81" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="62" t="s">
+      <c r="B43" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="C43" s="93">
+      <c r="C43" s="87">
         <f>SUM(C40:C42)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="87"/>
-      <c r="E43" s="87"/>
-      <c r="F43" s="87"/>
-      <c r="G43" s="87"/>
-      <c r="H43" s="87"/>
-      <c r="I43" s="87"/>
-      <c r="J43" s="87"/>
-      <c r="K43" s="87"/>
-      <c r="L43" s="87"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="81"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="87"/>
-      <c r="B44" s="53"/>
-      <c r="C44" s="90"/>
-      <c r="D44" s="87"/>
-      <c r="E44" s="87"/>
-      <c r="F44" s="87"/>
-      <c r="G44" s="87"/>
-      <c r="H44" s="87"/>
-      <c r="I44" s="87"/>
-      <c r="J44" s="87"/>
-      <c r="K44" s="87"/>
-      <c r="L44" s="87"/>
+      <c r="A44" s="81"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="84"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="88" t="s">
+      <c r="A45" s="82" t="s">
         <v>167</v>
       </c>
-      <c r="B45" s="91" t="s">
+      <c r="B45" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="C45" s="94" t="s">
+      <c r="C45" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="D45" s="133" t="s">
+      <c r="D45" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="133"/>
-      <c r="F45" s="133"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="133"/>
-      <c r="I45" s="133"/>
-      <c r="J45" s="133"/>
-      <c r="K45" s="133"/>
-      <c r="L45" s="133"/>
+      <c r="E45" s="130"/>
+      <c r="F45" s="130"/>
+      <c r="G45" s="130"/>
+      <c r="H45" s="130"/>
+      <c r="I45" s="130"/>
+      <c r="J45" s="130"/>
+      <c r="K45" s="130"/>
+      <c r="L45" s="130"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="87"/>
-      <c r="B46" s="33"/>
-      <c r="C46" s="92">
-        <v>0</v>
-      </c>
-      <c r="D46" s="137"/>
-      <c r="E46" s="137"/>
-      <c r="F46" s="137"/>
-      <c r="G46" s="137"/>
-      <c r="H46" s="137"/>
-      <c r="I46" s="137"/>
-      <c r="J46" s="137"/>
-      <c r="K46" s="137"/>
-      <c r="L46" s="137"/>
+      <c r="A46" s="81"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="86">
+        <v>0</v>
+      </c>
+      <c r="D46" s="129"/>
+      <c r="E46" s="129"/>
+      <c r="F46" s="129"/>
+      <c r="G46" s="129"/>
+      <c r="H46" s="129"/>
+      <c r="I46" s="129"/>
+      <c r="J46" s="129"/>
+      <c r="K46" s="129"/>
+      <c r="L46" s="129"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="87"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="92">
-        <v>0</v>
-      </c>
-      <c r="D47" s="137"/>
-      <c r="E47" s="137"/>
-      <c r="F47" s="137"/>
-      <c r="G47" s="137"/>
-      <c r="H47" s="137"/>
-      <c r="I47" s="137"/>
-      <c r="J47" s="137"/>
-      <c r="K47" s="137"/>
-      <c r="L47" s="137"/>
+      <c r="A47" s="81"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="86">
+        <v>0</v>
+      </c>
+      <c r="D47" s="129"/>
+      <c r="E47" s="129"/>
+      <c r="F47" s="129"/>
+      <c r="G47" s="129"/>
+      <c r="H47" s="129"/>
+      <c r="I47" s="129"/>
+      <c r="J47" s="129"/>
+      <c r="K47" s="129"/>
+      <c r="L47" s="129"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="87"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="92">
-        <v>0</v>
-      </c>
-      <c r="D48" s="137"/>
-      <c r="E48" s="137"/>
-      <c r="F48" s="137"/>
-      <c r="G48" s="137"/>
-      <c r="H48" s="137"/>
-      <c r="I48" s="137"/>
-      <c r="J48" s="137"/>
-      <c r="K48" s="137"/>
-      <c r="L48" s="137"/>
+      <c r="A48" s="81"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="86">
+        <v>0</v>
+      </c>
+      <c r="D48" s="129"/>
+      <c r="E48" s="129"/>
+      <c r="F48" s="129"/>
+      <c r="G48" s="129"/>
+      <c r="H48" s="129"/>
+      <c r="I48" s="129"/>
+      <c r="J48" s="129"/>
+      <c r="K48" s="129"/>
+      <c r="L48" s="129"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="87" t="s">
+      <c r="A49" s="81" t="s">
         <v>163</v>
       </c>
-      <c r="B49" s="62" t="s">
+      <c r="B49" s="58" t="s">
         <v>240</v>
       </c>
-      <c r="C49" s="93">
+      <c r="C49" s="87">
         <f>SUM(C46:C48)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="87"/>
-      <c r="E49" s="87"/>
-      <c r="F49" s="87"/>
-      <c r="G49" s="87"/>
-      <c r="H49" s="87"/>
-      <c r="I49" s="87"/>
-      <c r="J49" s="87"/>
-      <c r="K49" s="87"/>
-      <c r="L49" s="87"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="87"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="87"/>
-      <c r="E50" s="87"/>
-      <c r="F50" s="87"/>
-      <c r="G50" s="87"/>
-      <c r="H50" s="87"/>
-      <c r="I50" s="87"/>
-      <c r="J50" s="87"/>
-      <c r="K50" s="87"/>
-      <c r="L50" s="87"/>
+      <c r="A50" s="81"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
     </row>
     <row r="51" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="88" t="s">
+      <c r="A51" s="82" t="s">
         <v>167</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C51" s="94" t="s">
+      <c r="C51" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="133" t="s">
+      <c r="D51" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="E51" s="133"/>
-      <c r="F51" s="133"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="133"/>
-      <c r="I51" s="133"/>
-      <c r="J51" s="133"/>
-      <c r="K51" s="133"/>
-      <c r="L51" s="133"/>
+      <c r="E51" s="130"/>
+      <c r="F51" s="130"/>
+      <c r="G51" s="130"/>
+      <c r="H51" s="130"/>
+      <c r="I51" s="130"/>
+      <c r="J51" s="130"/>
+      <c r="K51" s="130"/>
+      <c r="L51" s="130"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="87"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="92">
-        <v>0</v>
-      </c>
-      <c r="D52" s="137"/>
-      <c r="E52" s="137"/>
-      <c r="F52" s="137"/>
-      <c r="G52" s="137"/>
-      <c r="H52" s="137"/>
-      <c r="I52" s="137"/>
-      <c r="J52" s="137"/>
-      <c r="K52" s="137"/>
-      <c r="L52" s="137"/>
+      <c r="A52" s="81"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="86">
+        <v>0</v>
+      </c>
+      <c r="D52" s="129"/>
+      <c r="E52" s="129"/>
+      <c r="F52" s="129"/>
+      <c r="G52" s="129"/>
+      <c r="H52" s="129"/>
+      <c r="I52" s="129"/>
+      <c r="J52" s="129"/>
+      <c r="K52" s="129"/>
+      <c r="L52" s="129"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="87"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="92">
-        <v>0</v>
-      </c>
-      <c r="D53" s="137"/>
-      <c r="E53" s="137"/>
-      <c r="F53" s="137"/>
-      <c r="G53" s="137"/>
-      <c r="H53" s="137"/>
-      <c r="I53" s="137"/>
-      <c r="J53" s="137"/>
-      <c r="K53" s="137"/>
-      <c r="L53" s="137"/>
+      <c r="A53" s="81"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="86">
+        <v>0</v>
+      </c>
+      <c r="D53" s="129"/>
+      <c r="E53" s="129"/>
+      <c r="F53" s="129"/>
+      <c r="G53" s="129"/>
+      <c r="H53" s="129"/>
+      <c r="I53" s="129"/>
+      <c r="J53" s="129"/>
+      <c r="K53" s="129"/>
+      <c r="L53" s="129"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="87"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="92">
-        <v>0</v>
-      </c>
-      <c r="D54" s="137"/>
-      <c r="E54" s="137"/>
-      <c r="F54" s="137"/>
-      <c r="G54" s="137"/>
-      <c r="H54" s="137"/>
-      <c r="I54" s="137"/>
-      <c r="J54" s="137"/>
-      <c r="K54" s="137"/>
-      <c r="L54" s="137"/>
+      <c r="A54" s="81"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="86">
+        <v>0</v>
+      </c>
+      <c r="D54" s="129"/>
+      <c r="E54" s="129"/>
+      <c r="F54" s="129"/>
+      <c r="G54" s="129"/>
+      <c r="H54" s="129"/>
+      <c r="I54" s="129"/>
+      <c r="J54" s="129"/>
+      <c r="K54" s="129"/>
+      <c r="L54" s="129"/>
     </row>
     <row r="55" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="42" t="s">
+      <c r="A55" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="B55" s="62" t="s">
+      <c r="B55" s="58" t="s">
         <v>241</v>
       </c>
-      <c r="C55" s="93">
+      <c r="C55" s="87">
         <f>SUM(C52:C54)</f>
         <v>0</v>
       </c>
-      <c r="D55" s="138"/>
-      <c r="E55" s="138"/>
-      <c r="F55" s="138"/>
-      <c r="G55" s="138"/>
-      <c r="H55" s="138"/>
-      <c r="I55" s="138"/>
-      <c r="J55" s="138"/>
-      <c r="K55" s="138"/>
-      <c r="L55" s="138"/>
+      <c r="D55" s="131"/>
+      <c r="E55" s="131"/>
+      <c r="F55" s="131"/>
+      <c r="G55" s="131"/>
+      <c r="H55" s="131"/>
+      <c r="I55" s="131"/>
+      <c r="J55" s="131"/>
+      <c r="K55" s="131"/>
+      <c r="L55" s="131"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="D54:L54"/>
-    <mergeCell ref="D52:L52"/>
-    <mergeCell ref="D53:L53"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="D48:L48"/>
-    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="D22:L22"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D40:L40"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D23:L23"/>
+    <mergeCell ref="D24:L24"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="D15:L15"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="A6:L8"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="D10:L10"/>
     <mergeCell ref="D11:L11"/>
@@ -6888,25 +7030,19 @@
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="D34:L34"/>
     <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D9:L9"/>
-    <mergeCell ref="D15:L15"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A6:L8"/>
     <mergeCell ref="D21:L21"/>
     <mergeCell ref="D27:L27"/>
     <mergeCell ref="D33:L33"/>
     <mergeCell ref="D39:L39"/>
+    <mergeCell ref="D54:L54"/>
+    <mergeCell ref="D52:L52"/>
+    <mergeCell ref="D53:L53"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D46:L46"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="D51:L51"/>
     <mergeCell ref="D45:L45"/>
-    <mergeCell ref="D22:L22"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D40:L40"/>
-    <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D23:L23"/>
-    <mergeCell ref="D24:L24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>

--- a/noprofit/en/11255/inpag-template.xlsx
+++ b/noprofit/en/11255/inpag-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44820CC8-AE92-4FB9-82EA-52E5190E96B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA30A08-D3BB-461A-8F2F-997CC750366D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" firstSheet="4" activeTab="4" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
   <sheets>
     <sheet name="General information" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash flow statement - indirect'!$A$1:$E$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'General information'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Notes of cash flow statement'!$A$1:$L$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Notes of cash flow statement'!$A$1:$L$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Notes of financial statement'!$A$1:$D$82</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Notes of income statement'!$A$1:$D$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Statement of changes in equity'!$A$1:$E$24</definedName>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="277">
   <si>
     <t>Company name and legal form</t>
   </si>
@@ -489,9 +489,6 @@
     <t>Net cash flows from operating activities</t>
   </si>
   <si>
-    <t>7.4e</t>
-  </si>
-  <si>
     <t>Cash flows from investing activities</t>
   </si>
   <si>
@@ -531,21 +528,12 @@
     <t>Explanation of investing and financing transactions not requiring use of cash or cash equivalents</t>
   </si>
   <si>
-    <t>7.19 a</t>
-  </si>
-  <si>
     <t>Description of acquisition of assets by assuming directly related liabilities or means of finance lease</t>
   </si>
   <si>
-    <t>7.19 b</t>
-  </si>
-  <si>
     <t xml:space="preserve">Description of acquisition of entity by means of equity issue </t>
   </si>
   <si>
-    <t>7.19 c</t>
-  </si>
-  <si>
     <t xml:space="preserve">Description of conversion of debt to equity </t>
   </si>
   <si>
@@ -729,21 +717,6 @@
     <t>Total expenses</t>
   </si>
   <si>
-    <t>Income taxes paid (refund)</t>
-  </si>
-  <si>
-    <t>Income taxes [-] paid [+] refund, classified as operating activities</t>
-  </si>
-  <si>
-    <t>Income taxes [-] paid [+] refund, classified as investing activities</t>
-  </si>
-  <si>
-    <t>Income taxes [-] paid [+] refund, classified as financing activities</t>
-  </si>
-  <si>
-    <t>Total income taxes paid (refund)</t>
-  </si>
-  <si>
     <t>Cash and cash equivalents if different from statement of financial position</t>
   </si>
   <si>
@@ -778,9 +751,6 @@
   </si>
   <si>
     <t>Total Commentary by management on significant cash and cash equivalent balances held by entity that are not available for use by group</t>
-  </si>
-  <si>
-    <t>7.19 d</t>
   </si>
   <si>
     <t>Total Surplus or deficit from operating activities</t>
@@ -1086,40 +1056,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1147,7 +1088,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1256,19 +1197,10 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1307,7 +1239,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1383,9 +1315,6 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1410,26 +1339,35 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1440,18 +1378,6 @@
     <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1476,67 +1402,82 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1929,7 +1870,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -1939,322 +1880,316 @@
       <c r="G1" s="99"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="100" t="s">
+      <c r="A2" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="132" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="101" t="s">
+      <c r="B7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="102">
+      <c r="B8" s="133">
         <v>45292</v>
       </c>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="131" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="102">
+      <c r="B9" s="133">
         <v>45657</v>
       </c>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="133" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="48"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
+      <c r="A11" s="131"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
+      <c r="A12" s="131"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
+      <c r="A13" s="131"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
+      <c r="A14" s="131"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
+      <c r="A15" s="131"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
+      <c r="A16" s="131"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="98" t="s">
+      <c r="B17" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="133"/>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
-      <c r="B18" s="98" t="s">
+      <c r="A18" s="131"/>
+      <c r="B18" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A19" s="48"/>
-      <c r="B19" s="98" t="s">
+      <c r="A19" s="131"/>
+      <c r="B19" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A20" s="46"/>
-      <c r="B20" s="104" t="s">
+      <c r="A20" s="131"/>
+      <c r="B20" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="98" t="s">
+      <c r="B22" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
-      <c r="B23" s="98" t="s">
+      <c r="A23" s="131"/>
+      <c r="B23" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
-      <c r="B24" s="98" t="s">
+      <c r="A24" s="131"/>
+      <c r="B24" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A25" s="48"/>
-      <c r="B25" s="98" t="s">
+      <c r="A25" s="131"/>
+      <c r="B25" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="98"/>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="98"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="133"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
-      <c r="B26" s="98" t="s">
+      <c r="A26" s="131"/>
+      <c r="B26" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="98"/>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="98"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="133"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="133"/>
+      <c r="G26" s="133"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A27" s="48"/>
-      <c r="B27" s="98" t="s">
+      <c r="A27" s="131"/>
+      <c r="B27" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="98"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="98"/>
+      <c r="C27" s="133"/>
+      <c r="D27" s="133"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A28" s="48"/>
-      <c r="B28" s="98" t="s">
+      <c r="A28" s="131"/>
+      <c r="B28" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="98"/>
-      <c r="D28" s="98"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="98"/>
-      <c r="G28" s="98"/>
+      <c r="C28" s="133"/>
+      <c r="D28" s="133"/>
+      <c r="E28" s="133"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2271,6 +2206,12 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2299,87 +2240,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="105" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="105" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="107">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="107">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
-        <v>283</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
+      <c r="A6" s="100" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
+      <c r="A7" s="100"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="108"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="75" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -2388,23 +2329,23 @@
       <c r="C9" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="78">
+      <c r="D9" s="75">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E9" s="78">
+      <c r="E9" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="45"/>
-      <c r="B10" s="111" t="s">
+      <c r="B10" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
@@ -2413,7 +2354,7 @@
       <c r="B11" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="136">
+      <c r="C11" s="94">
         <v>1</v>
       </c>
       <c r="D11" s="14">
@@ -2430,7 +2371,7 @@
       <c r="B12" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="136">
+      <c r="C12" s="94">
         <v>2</v>
       </c>
       <c r="D12" s="14">
@@ -2447,7 +2388,7 @@
       <c r="B13" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="136">
+      <c r="C13" s="94">
         <v>3</v>
       </c>
       <c r="D13" s="14">
@@ -2464,7 +2405,7 @@
       <c r="B14" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="136">
+      <c r="C14" s="94">
         <v>4</v>
       </c>
       <c r="D14" s="14">
@@ -2476,15 +2417,15 @@
     </row>
     <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="45"/>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="55" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="45"/>
-      <c r="D15" s="66">
+      <c r="D15" s="63">
         <f>SUM(D11:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="66">
+      <c r="E15" s="63">
         <f>SUM(E11:E14)</f>
         <v>0</v>
       </c>
@@ -2498,12 +2439,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45"/>
-      <c r="B17" s="111" t="s">
+      <c r="B17" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45" t="s">
@@ -2512,7 +2453,7 @@
       <c r="B18" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="136">
+      <c r="C18" s="94">
         <v>5</v>
       </c>
       <c r="D18" s="14">
@@ -2524,12 +2465,12 @@
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="C19" s="136">
+        <v>258</v>
+      </c>
+      <c r="C19" s="94">
         <v>6</v>
       </c>
       <c r="D19" s="14">
@@ -2546,7 +2487,7 @@
       <c r="B20" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="136">
+      <c r="C20" s="94">
         <v>7</v>
       </c>
       <c r="D20" s="14">
@@ -2563,7 +2504,7 @@
       <c r="B21" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="136">
+      <c r="C21" s="94">
         <v>8</v>
       </c>
       <c r="D21" s="14">
@@ -2575,30 +2516,30 @@
     </row>
     <row r="22" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A22" s="45"/>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="55" t="s">
         <v>49</v>
       </c>
       <c r="C22" s="45"/>
-      <c r="D22" s="67">
+      <c r="D22" s="64">
         <f>SUM(D18:D21)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E22" s="64">
         <f>SUM(E18:E21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45"/>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="67">
+      <c r="C23" s="46"/>
+      <c r="D23" s="64">
         <f>SUM(D15,D22)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="67">
+      <c r="E23" s="64">
         <f>SUM(E15,E22)</f>
         <v>0</v>
       </c>
@@ -2611,7 +2552,7 @@
       <c r="E24" s="31"/>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="75" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="10" t="s">
@@ -2620,23 +2561,23 @@
       <c r="C25" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="78">
+      <c r="D25" s="75">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E25" s="78">
+      <c r="E25" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
-      <c r="B26" s="111" t="s">
+      <c r="B26" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45" t="s">
@@ -2645,7 +2586,7 @@
       <c r="B27" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="136">
+      <c r="C27" s="94">
         <v>9</v>
       </c>
       <c r="D27" s="14">
@@ -2662,7 +2603,7 @@
       <c r="B28" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="136">
+      <c r="C28" s="94">
         <v>10</v>
       </c>
       <c r="D28" s="14">
@@ -2679,7 +2620,7 @@
       <c r="B29" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="136">
+      <c r="C29" s="94">
         <v>11</v>
       </c>
       <c r="D29" s="14">
@@ -2696,7 +2637,7 @@
       <c r="B30" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="136">
+      <c r="C30" s="94">
         <v>12</v>
       </c>
       <c r="D30" s="14">
@@ -2713,7 +2654,7 @@
       <c r="B31" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="136">
+      <c r="C31" s="94">
         <v>13</v>
       </c>
       <c r="D31" s="14">
@@ -2725,15 +2666,15 @@
     </row>
     <row r="32" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="45"/>
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="55" t="s">
         <v>62</v>
       </c>
       <c r="C32" s="45"/>
-      <c r="D32" s="66">
+      <c r="D32" s="63">
         <f>SUM(D27:D31)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="66">
+      <c r="E32" s="63">
         <f>SUM(E27:E31)</f>
         <v>0</v>
       </c>
@@ -2747,12 +2688,12 @@
     </row>
     <row r="34" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45"/>
-      <c r="B34" s="111" t="s">
+      <c r="B34" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="111"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45" t="s">
@@ -2761,7 +2702,7 @@
       <c r="B35" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="136">
+      <c r="C35" s="94">
         <v>14</v>
       </c>
       <c r="D35" s="14">
@@ -2778,7 +2719,7 @@
       <c r="B36" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="136">
+      <c r="C36" s="94">
         <v>15</v>
       </c>
       <c r="D36" s="14">
@@ -2795,7 +2736,7 @@
       <c r="B37" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="136">
+      <c r="C37" s="94">
         <v>16</v>
       </c>
       <c r="D37" s="14">
@@ -2807,15 +2748,15 @@
     </row>
     <row r="38" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A38" s="45"/>
-      <c r="B38" s="58" t="s">
+      <c r="B38" s="55" t="s">
         <v>69</v>
       </c>
       <c r="C38" s="45"/>
-      <c r="D38" s="66">
+      <c r="D38" s="63">
         <f>SUM(D35:D37)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="66">
+      <c r="E38" s="63">
         <f>SUM(E35:E37)</f>
         <v>0</v>
       </c>
@@ -2829,12 +2770,12 @@
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45"/>
-      <c r="B40" s="111" t="s">
+      <c r="B40" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="111"/>
-      <c r="D40" s="111"/>
-      <c r="E40" s="111"/>
+      <c r="C40" s="103"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="103"/>
     </row>
     <row r="41" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45" t="s">
@@ -2843,7 +2784,7 @@
       <c r="B41" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="C41" s="136">
+      <c r="C41" s="94">
         <v>17</v>
       </c>
       <c r="D41" s="14">
@@ -2860,7 +2801,7 @@
       <c r="B42" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="136">
+      <c r="C42" s="94">
         <v>18</v>
       </c>
       <c r="D42" s="14">
@@ -2877,7 +2818,7 @@
       <c r="B43" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="C43" s="136">
+      <c r="C43" s="94">
         <v>19</v>
       </c>
       <c r="D43" s="14">
@@ -2894,7 +2835,7 @@
       <c r="B44" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="136">
+      <c r="C44" s="94">
         <v>20</v>
       </c>
       <c r="D44" s="14">
@@ -2911,7 +2852,7 @@
       <c r="B45" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="136">
+      <c r="C45" s="94">
         <v>21</v>
       </c>
       <c r="D45" s="14">
@@ -2928,7 +2869,7 @@
       <c r="B46" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="136">
+      <c r="C46" s="94">
         <v>22</v>
       </c>
       <c r="D46" s="14">
@@ -2945,7 +2886,7 @@
       <c r="B47" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C47" s="136">
+      <c r="C47" s="94">
         <v>23</v>
       </c>
       <c r="D47" s="14">
@@ -2957,73 +2898,73 @@
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45"/>
-      <c r="B48" s="111" t="s">
+      <c r="B48" s="103" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="111"/>
-      <c r="D48" s="66">
+      <c r="C48" s="103"/>
+      <c r="D48" s="63">
         <f>SUM(D41:D47)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="66">
+      <c r="E48" s="63">
         <f>SUM(E41:E47)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45"/>
-      <c r="B49" s="111" t="s">
+      <c r="B49" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="111"/>
-      <c r="D49" s="66">
+      <c r="C49" s="103"/>
+      <c r="D49" s="63">
         <f>SUM(D32,D38,D48)</f>
         <v>0</v>
       </c>
-      <c r="E49" s="66">
+      <c r="E49" s="63">
         <f>SUM(E32,E38,E48)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="45"/>
-      <c r="B50" s="62"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="49"/>
     </row>
     <row r="51" spans="1:5" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="50"/>
-      <c r="B51" s="63"/>
-      <c r="C51" s="63"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="60"/>
+      <c r="C51" s="60"/>
+      <c r="D51" s="60"/>
+      <c r="E51" s="60"/>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="64" t="s">
+      <c r="A52" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="110" t="str">
+      <c r="B52" s="102" t="str">
         <f>IF((D15+D23+D32=D38+D48),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C52" s="110"/>
-      <c r="D52" s="57">
+      <c r="C52" s="102"/>
+      <c r="D52" s="54">
         <f>D49-D23</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A53" s="65" t="s">
+      <c r="A53" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="B53" s="109" t="str">
+      <c r="B53" s="101" t="str">
         <f>IF((E15+E23+E32=E38+E48),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="109"/>
-      <c r="D53" s="109"/>
-      <c r="E53" s="57">
+      <c r="C53" s="101"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="54">
         <f>E49-E23</f>
         <v>0</v>
       </c>
@@ -3036,6 +2977,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="B52:C52"/>
@@ -3046,11 +2992,6 @@
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B52">
@@ -3104,13 +3045,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
@@ -3118,75 +3059,75 @@
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="113" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="113" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="114">
+      <c r="B4" s="109">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="114">
+      <c r="B5" s="109">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
-        <v>282</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
+      <c r="A6" s="100" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
+      <c r="A7" s="100"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="108"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="75" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="17" t="s">
@@ -3195,23 +3136,23 @@
       <c r="C9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="91">
+      <c r="D9" s="87">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E9" s="91">
+      <c r="E9" s="87">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="48" t="s">
         <v>88</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="137">
+      <c r="C10" s="95">
         <v>24</v>
       </c>
       <c r="D10" s="19">
@@ -3222,13 +3163,13 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="48" t="s">
         <v>90</v>
       </c>
       <c r="B11" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="137">
+      <c r="C11" s="95">
         <v>25</v>
       </c>
       <c r="D11" s="19">
@@ -3239,13 +3180,13 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="48" t="s">
         <v>92</v>
       </c>
       <c r="B12" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="137">
+      <c r="C12" s="95">
         <v>26</v>
       </c>
       <c r="D12" s="19">
@@ -3256,13 +3197,13 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="48" t="s">
         <v>94</v>
       </c>
       <c r="B13" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="137">
+      <c r="C13" s="95">
         <v>27</v>
       </c>
       <c r="D13" s="19">
@@ -3273,13 +3214,13 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="48" t="s">
         <v>96</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="137">
+      <c r="C14" s="95">
         <v>28</v>
       </c>
       <c r="D14" s="19">
@@ -3290,29 +3231,29 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="51"/>
-      <c r="B15" s="68" t="s">
+      <c r="A15" s="48"/>
+      <c r="B15" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69">
+      <c r="C15" s="65"/>
+      <c r="D15" s="66">
         <f>SUM(D10:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="69">
+      <c r="E15" s="66">
         <f>SUM(E10:E14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="51"/>
+      <c r="A16" s="48"/>
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
     </row>
     <row r="17" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="75" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="17" t="s">
@@ -3321,23 +3262,23 @@
       <c r="C17" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="91">
+      <c r="D17" s="87">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E17" s="91">
+      <c r="E17" s="87">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="48" t="s">
         <v>98</v>
       </c>
       <c r="B18" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="137">
+      <c r="C18" s="95">
         <v>29</v>
       </c>
       <c r="D18" s="19">
@@ -3348,13 +3289,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="48" t="s">
         <v>100</v>
       </c>
       <c r="B19" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="137">
+      <c r="C19" s="95">
         <v>30</v>
       </c>
       <c r="D19" s="19">
@@ -3365,13 +3306,13 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="48" t="s">
         <v>102</v>
       </c>
       <c r="B20" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="137">
+      <c r="C20" s="95">
         <v>31</v>
       </c>
       <c r="D20" s="19">
@@ -3382,13 +3323,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="51" t="s">
+      <c r="A21" s="48" t="s">
         <v>106</v>
       </c>
       <c r="B21" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="137">
+      <c r="C21" s="95">
         <v>32</v>
       </c>
       <c r="D21" s="19">
@@ -3399,13 +3340,13 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="48" t="s">
         <v>108</v>
       </c>
       <c r="B22" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="137">
+      <c r="C22" s="95">
         <v>33</v>
       </c>
       <c r="D22" s="19">
@@ -3416,13 +3357,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="48" t="s">
         <v>110</v>
       </c>
       <c r="B23" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="137">
+      <c r="C23" s="95">
         <v>34</v>
       </c>
       <c r="D23" s="19">
@@ -3433,13 +3374,13 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="48" t="s">
         <v>112</v>
       </c>
       <c r="B24" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="137">
+      <c r="C24" s="95">
         <v>35</v>
       </c>
       <c r="D24" s="19">
@@ -3450,13 +3391,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="48" t="s">
         <v>114</v>
       </c>
       <c r="B25" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="137">
+      <c r="C25" s="95">
         <v>36</v>
       </c>
       <c r="D25" s="19">
@@ -3467,54 +3408,54 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="51"/>
-      <c r="B26" s="68" t="s">
+      <c r="A26" s="48"/>
+      <c r="B26" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="69">
+      <c r="C26" s="65"/>
+      <c r="D26" s="66">
         <f>SUM(D18:D25)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="69">
+      <c r="E26" s="66">
         <f>SUM(E18:E25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="51"/>
+      <c r="A27" s="48"/>
       <c r="B27" s="18"/>
       <c r="C27" s="36"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="60" t="s">
+      <c r="B28" s="57" t="s">
         <v>117</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="91">
+      <c r="D28" s="87">
         <f>$B$4</f>
         <v>45292</v>
       </c>
-      <c r="E28" s="91">
+      <c r="E28" s="87">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="48" t="s">
         <v>118</v>
       </c>
       <c r="B29" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="137">
+      <c r="C29" s="95">
         <v>37</v>
       </c>
       <c r="D29" s="19">
@@ -3525,13 +3466,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="48" t="s">
         <v>120</v>
       </c>
       <c r="B30" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="137">
+      <c r="C30" s="95">
         <v>38</v>
       </c>
       <c r="D30" s="19">
@@ -3542,13 +3483,13 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="48" t="s">
         <v>122</v>
       </c>
       <c r="B31" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="137">
+      <c r="C31" s="95">
         <v>39</v>
       </c>
       <c r="D31" s="19">
@@ -3559,13 +3500,13 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="48" t="s">
         <v>124</v>
       </c>
       <c r="B32" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="137">
+      <c r="C32" s="95">
         <v>40</v>
       </c>
       <c r="D32" s="19">
@@ -3576,13 +3517,13 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="48" t="s">
         <v>126</v>
       </c>
       <c r="B33" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="137">
+      <c r="C33" s="95">
         <v>41</v>
       </c>
       <c r="D33" s="19">
@@ -3593,13 +3534,13 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="51" t="s">
+      <c r="A34" s="48" t="s">
         <v>128</v>
       </c>
       <c r="B34" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="137">
+      <c r="C34" s="95">
         <v>42</v>
       </c>
       <c r="D34" s="19">
@@ -3610,31 +3551,31 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="51"/>
-      <c r="B35" s="93" t="s">
-        <v>243</v>
-      </c>
-      <c r="C35" s="93"/>
-      <c r="D35" s="94">
+      <c r="A35" s="48"/>
+      <c r="B35" s="89" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35" s="89"/>
+      <c r="D35" s="90">
         <f>SUM($D29:$D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="94">
+      <c r="E35" s="90">
         <f>SUM($E29:$E34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
-      <c r="B36" s="68" t="s">
+      <c r="B36" s="65" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="68"/>
-      <c r="D36" s="70">
+      <c r="C36" s="65"/>
+      <c r="D36" s="67">
         <f>SUM(D15+D26+D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="70">
+      <c r="E36" s="67">
         <f>SUM(E15+E26+E35)</f>
         <v>0</v>
       </c>
@@ -3678,13 +3619,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3693,86 +3634,86 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="105" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="105" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="107">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="107">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="108" t="s">
-        <v>281</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
+      <c r="A6" s="100" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
+      <c r="A7" s="100"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="108"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="78">
+      <c r="C9" s="76"/>
+      <c r="D9" s="75">
         <f>DATE(YEAR(B5),1,1)</f>
         <v>45292</v>
       </c>
-      <c r="E9" s="78">
+      <c r="E9" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
@@ -3781,10 +3722,10 @@
       <c r="A10" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="115"/>
+      <c r="C10" s="110"/>
       <c r="D10" s="14">
         <v>0</v>
       </c>
@@ -3792,24 +3733,24 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="45"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="57"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="54"/>
       <c r="E11" s="31"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="78">
+      <c r="C12" s="76"/>
+      <c r="D12" s="75">
         <f>DATE(YEAR(B5),1,1)</f>
         <v>45292</v>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
@@ -3818,11 +3759,11 @@
       <c r="A13" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="117" t="s">
-        <v>245</v>
-      </c>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
+      <c r="B13" s="112" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
       <c r="E13" s="14">
         <v>0</v>
       </c>
@@ -3831,111 +3772,111 @@
       <c r="A14" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="112" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
       <c r="E14" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="45"/>
-      <c r="B15" s="116" t="s">
+      <c r="B15" s="111" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="71">
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="68">
         <f>SUM(E13:E14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="45"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="55"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="52"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="75" t="s">
         <v>133</v>
       </c>
       <c r="B17" s="20" t="s">
         <v>139</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="80">
+      <c r="D17" s="77">
         <f>DATE(YEAR(B4),1,1)</f>
         <v>45292</v>
       </c>
-      <c r="E17" s="78">
+      <c r="E17" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="B18" s="118" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
       <c r="E18" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="B19" s="118" t="s">
+        <v>237</v>
+      </c>
+      <c r="B19" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="113"/>
       <c r="E19" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="B20" s="118" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="113"/>
       <c r="E20" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" s="117" t="s">
+        <v>239</v>
+      </c>
+      <c r="B21" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
       <c r="E21" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="45"/>
-      <c r="B22" s="116" t="s">
+      <c r="B22" s="111" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="71">
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="68">
         <f>SUM(E18:E21)</f>
         <v>0</v>
       </c>
@@ -3943,27 +3884,32 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="45"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="55"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="52"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="116" t="s">
+      <c r="B24" s="111" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="116"/>
-      <c r="D24" s="116"/>
-      <c r="E24" s="66">
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="63">
         <f>SUM(D10,E15,E22)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B24:D24"/>
@@ -3975,11 +3921,6 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -4006,98 +3947,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="105" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="105" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="107">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="107">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
+      <c r="A6" s="100" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
+      <c r="A7" s="100"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="108"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="121" t="s">
-        <v>244</v>
-      </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="78" t="s">
+      <c r="B9" s="115" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="115"/>
+      <c r="D9" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="78">
+      <c r="E9" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
@@ -4106,47 +4047,47 @@
       <c r="A10" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="111" t="s">
-        <v>245</v>
-      </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
+      <c r="B10" s="103" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
       <c r="E10" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
     </row>
     <row r="12" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="121" t="s">
+      <c r="B12" s="115" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="121"/>
-      <c r="D12" s="78" t="s">
+      <c r="C12" s="115"/>
+      <c r="D12" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45" t="s">
-        <v>260</v>
-      </c>
-      <c r="B13" s="118" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="113" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="136">
+      <c r="C13" s="113"/>
+      <c r="D13" s="94">
         <v>26</v>
       </c>
       <c r="E13" s="22">
@@ -4156,13 +4097,13 @@
     </row>
     <row r="14" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45" t="s">
-        <v>261</v>
-      </c>
-      <c r="B14" s="118" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="118"/>
-      <c r="D14" s="136">
+      <c r="C14" s="113"/>
+      <c r="D14" s="94">
         <v>32</v>
       </c>
       <c r="E14" s="22">
@@ -4171,13 +4112,13 @@
     </row>
     <row r="15" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45" t="s">
-        <v>265</v>
-      </c>
-      <c r="B15" s="118" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="113" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="136">
+      <c r="C15" s="113"/>
+      <c r="D15" s="94">
         <v>36</v>
       </c>
       <c r="E15" s="22">
@@ -4186,13 +4127,13 @@
     </row>
     <row r="16" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="118" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="118"/>
-      <c r="D16" s="136">
+      <c r="C16" s="113"/>
+      <c r="D16" s="94">
         <v>33</v>
       </c>
       <c r="E16" s="22">
@@ -4201,13 +4142,13 @@
     </row>
     <row r="17" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="B17" s="118" t="s">
+        <v>241</v>
+      </c>
+      <c r="B17" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="118"/>
-      <c r="D17" s="136">
+      <c r="C17" s="113"/>
+      <c r="D17" s="94">
         <v>34</v>
       </c>
       <c r="E17" s="22">
@@ -4216,13 +4157,13 @@
     </row>
     <row r="18" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="B18" s="118" t="s">
+        <v>241</v>
+      </c>
+      <c r="B18" s="113" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="136">
+      <c r="C18" s="113"/>
+      <c r="D18" s="94">
         <v>35</v>
       </c>
       <c r="E18" s="22">
@@ -4232,13 +4173,13 @@
     </row>
     <row r="19" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="B19" s="118" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="113" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="118"/>
-      <c r="D19" s="136">
+      <c r="C19" s="113"/>
+      <c r="D19" s="94">
         <v>27</v>
       </c>
       <c r="E19" s="22">
@@ -4248,13 +4189,13 @@
     </row>
     <row r="20" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="B20" s="118" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="136">
+      <c r="C20" s="113"/>
+      <c r="D20" s="94">
         <v>28</v>
       </c>
       <c r="E20" s="22">
@@ -4263,13 +4204,13 @@
     </row>
     <row r="21" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="B21" s="118" t="s">
+        <v>243</v>
+      </c>
+      <c r="B21" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="118"/>
-      <c r="D21" s="136">
+      <c r="C21" s="113"/>
+      <c r="D21" s="94">
         <v>37</v>
       </c>
       <c r="E21" s="22">
@@ -4279,13 +4220,13 @@
     </row>
     <row r="22" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="B22" s="118" t="s">
+        <v>244</v>
+      </c>
+      <c r="B22" s="113" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="136">
+      <c r="C22" s="113"/>
+      <c r="D22" s="94">
         <v>38</v>
       </c>
       <c r="E22" s="22">
@@ -4295,13 +4236,13 @@
     </row>
     <row r="23" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="B23" s="118" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="113" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="136">
+      <c r="C23" s="113"/>
+      <c r="D23" s="94">
         <v>39</v>
       </c>
       <c r="E23" s="22">
@@ -4311,13 +4252,13 @@
     </row>
     <row r="24" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45" t="s">
-        <v>256</v>
-      </c>
-      <c r="B24" s="118" t="s">
+        <v>246</v>
+      </c>
+      <c r="B24" s="113" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="136">
+      <c r="C24" s="113"/>
+      <c r="D24" s="94">
         <v>40</v>
       </c>
       <c r="E24" s="22">
@@ -4327,13 +4268,13 @@
     </row>
     <row r="25" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="45" t="s">
-        <v>257</v>
-      </c>
-      <c r="B25" s="119" t="s">
+        <v>247</v>
+      </c>
+      <c r="B25" s="114" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="136">
+      <c r="C25" s="114"/>
+      <c r="D25" s="94">
         <v>41</v>
       </c>
       <c r="E25" s="22">
@@ -4343,13 +4284,13 @@
     </row>
     <row r="26" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="45" t="s">
-        <v>258</v>
-      </c>
-      <c r="B26" s="119" t="s">
+        <v>248</v>
+      </c>
+      <c r="B26" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="136">
+      <c r="C26" s="114"/>
+      <c r="D26" s="94">
         <v>42</v>
       </c>
       <c r="E26" s="22">
@@ -4359,13 +4300,13 @@
     </row>
     <row r="27" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="B27" s="118" t="s">
+        <v>249</v>
+      </c>
+      <c r="B27" s="113" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="136">
+      <c r="C27" s="113"/>
+      <c r="D27" s="94">
         <v>25</v>
       </c>
       <c r="E27" s="22">
@@ -4375,12 +4316,12 @@
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="45"/>
-      <c r="B28" s="111" t="s">
+      <c r="B28" s="103" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="66">
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="63">
         <f>E10+SUM(E13:E27)</f>
         <v>0</v>
       </c>
@@ -4393,30 +4334,30 @@
       <c r="E29" s="29"/>
     </row>
     <row r="30" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="121" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" s="121"/>
-      <c r="D30" s="78" t="s">
+      <c r="B30" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" s="115"/>
+      <c r="D30" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="78">
+      <c r="E30" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="45" t="s">
-        <v>262</v>
-      </c>
-      <c r="B31" s="119" t="s">
+        <v>252</v>
+      </c>
+      <c r="B31" s="114" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="119"/>
-      <c r="D31" s="136">
+      <c r="C31" s="114"/>
+      <c r="D31" s="94">
         <v>29</v>
       </c>
       <c r="E31" s="22">
@@ -4425,13 +4366,13 @@
     </row>
     <row r="32" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="B32" s="119" t="s">
+        <v>253</v>
+      </c>
+      <c r="B32" s="114" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="119"/>
-      <c r="D32" s="136">
+      <c r="C32" s="114"/>
+      <c r="D32" s="94">
         <v>30</v>
       </c>
       <c r="E32" s="22">
@@ -4440,13 +4381,13 @@
     </row>
     <row r="33" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="B33" s="119" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" s="114" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="119"/>
-      <c r="D33" s="136">
+      <c r="C33" s="114"/>
+      <c r="D33" s="94">
         <v>31</v>
       </c>
       <c r="E33" s="22">
@@ -4455,12 +4396,12 @@
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45"/>
-      <c r="B34" s="111" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="111"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="66">
+      <c r="B34" s="103" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="63">
         <f>E10+E28+SUM(E31:E33)</f>
         <v>0</v>
       </c>
@@ -4470,20 +4411,20 @@
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
-      <c r="E35" s="72"/>
+      <c r="E35" s="69"/>
     </row>
     <row r="36" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="78" t="s">
+      <c r="A36" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B36" s="121" t="s">
-        <v>148</v>
-      </c>
-      <c r="C36" s="121"/>
-      <c r="D36" s="78" t="s">
+      <c r="B36" s="115" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" s="115"/>
+      <c r="D36" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="78">
+      <c r="E36" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
@@ -4491,13 +4432,13 @@
     </row>
     <row r="37" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45" t="s">
-        <v>267</v>
-      </c>
-      <c r="B37" s="119" t="s">
+        <v>257</v>
+      </c>
+      <c r="B37" s="114" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="119"/>
-      <c r="D37" s="136">
+      <c r="C37" s="114"/>
+      <c r="D37" s="94">
         <v>24</v>
       </c>
       <c r="E37" s="22">
@@ -4506,12 +4447,12 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45"/>
-      <c r="B38" s="111" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="111"/>
-      <c r="D38" s="111"/>
-      <c r="E38" s="66">
+      <c r="B38" s="103" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="63">
         <f>E10+E28+E34+SUM(E37:E37)</f>
         <v>0</v>
       </c>
@@ -4521,16 +4462,16 @@
       <c r="B39" s="26"/>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
-      <c r="E39" s="72"/>
+      <c r="E39" s="69"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45"/>
-      <c r="B40" s="111" t="s">
-        <v>150</v>
-      </c>
-      <c r="C40" s="111"/>
-      <c r="D40" s="111"/>
-      <c r="E40" s="66">
+      <c r="B40" s="103" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" s="103"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="63">
         <f>SUM(E28,E34,E38)</f>
         <v>0</v>
       </c>
@@ -4540,65 +4481,65 @@
       <c r="B41" s="26"/>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
-      <c r="E41" s="72"/>
+      <c r="E41" s="69"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="117" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="120" t="s">
-        <v>152</v>
-      </c>
-      <c r="C42" s="120"/>
-      <c r="D42" s="120"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
       <c r="E42" s="22"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="45"/>
-      <c r="B43" s="111" t="s">
-        <v>153</v>
-      </c>
-      <c r="C43" s="111"/>
-      <c r="D43" s="139">
+      <c r="B43" s="103" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" s="103"/>
+      <c r="D43" s="97">
         <v>43</v>
       </c>
-      <c r="E43" s="73">
+      <c r="E43" s="70">
         <f>E40+E42</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="45"/>
-      <c r="B44" s="111" t="s">
-        <v>154</v>
-      </c>
-      <c r="C44" s="111"/>
-      <c r="D44" s="111"/>
-      <c r="E44" s="73">
+      <c r="B44" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="70">
         <f>'Statement of financial position'!D22</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="45"/>
-      <c r="B45" s="111" t="s">
-        <v>155</v>
-      </c>
-      <c r="C45" s="111"/>
-      <c r="D45" s="111"/>
-      <c r="E45" s="73">
+      <c r="B45" s="103" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="103"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="70">
         <f>'Statement of financial position'!E22</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A46" s="45"/>
-      <c r="B46" s="111" t="s">
-        <v>156</v>
-      </c>
-      <c r="C46" s="111"/>
-      <c r="D46" s="111"/>
-      <c r="E46" s="73">
+      <c r="B46" s="103" t="s">
+        <v>155</v>
+      </c>
+      <c r="C46" s="103"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="70">
         <f>E45-E44</f>
         <v>0</v>
       </c>
@@ -4619,8 +4560,8 @@
     </row>
     <row r="49" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A49" s="31"/>
-      <c r="B49" s="61" t="s">
-        <v>157</v>
+      <c r="B49" s="58" t="s">
+        <v>156</v>
       </c>
       <c r="C49" s="31"/>
       <c r="D49" s="31"/>
@@ -4628,57 +4569,57 @@
     </row>
     <row r="50" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A50" s="31"/>
-      <c r="B50" s="30">
-        <v>7.18</v>
-      </c>
-      <c r="C50" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="D50" s="136"/>
+      <c r="B50" s="116" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" s="116"/>
+      <c r="D50" s="94">
+        <v>44</v>
+      </c>
       <c r="E50" s="31"/>
     </row>
     <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A51" s="31"/>
-      <c r="B51" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="C51" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="D51" s="136"/>
+      <c r="B51" s="116" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="116"/>
+      <c r="D51" s="94">
+        <v>45</v>
+      </c>
       <c r="E51" s="31"/>
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="31"/>
-      <c r="B52" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="C52" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="D52" s="136"/>
+      <c r="B52" s="116" t="s">
+        <v>159</v>
+      </c>
+      <c r="C52" s="116"/>
+      <c r="D52" s="94">
+        <v>46</v>
+      </c>
       <c r="E52" s="31"/>
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
-      <c r="B53" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C53" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="D53" s="136"/>
+      <c r="B53" s="116" t="s">
+        <v>160</v>
+      </c>
+      <c r="C53" s="116"/>
+      <c r="D53" s="94">
+        <v>47</v>
+      </c>
       <c r="E53" s="31"/>
     </row>
-    <row r="54" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
-      <c r="B54" s="30">
-        <v>7.21</v>
-      </c>
-      <c r="C54" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="D54" s="136"/>
+      <c r="B54" s="116" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" s="116"/>
+      <c r="D54" s="94">
+        <v>48</v>
+      </c>
       <c r="E54" s="31"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -4696,12 +4637,32 @@
       <c r="E56" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A11:E11"/>
+  <mergeCells count="45">
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B34:D34"/>
@@ -4712,31 +4673,16 @@
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
@@ -4762,215 +4708,215 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="105" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="105" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="107">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="107">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
+      <c r="A7" s="100"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="108"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="125" t="s">
-        <v>166</v>
-      </c>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
+      <c r="A9" s="122" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="122"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="124"/>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
+      <c r="A10" s="119"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="124"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
+      <c r="A11" s="119"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="124"/>
-      <c r="B12" s="124"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="124"/>
+      <c r="A12" s="119"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="126"/>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
+      <c r="A13" s="120"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="120"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="126"/>
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
+      <c r="A14" s="120"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="120"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="126"/>
-      <c r="B15" s="126"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
+      <c r="A15" s="120"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="120"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="126"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
+      <c r="A16" s="120"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="120"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="126"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
+      <c r="A17" s="120"/>
+      <c r="B17" s="120"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="120"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="124"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="124"/>
+      <c r="A18" s="119"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="124"/>
-      <c r="B19" s="124"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="124"/>
+      <c r="A19" s="119"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="124"/>
-      <c r="B20" s="124"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="124"/>
+      <c r="A20" s="119"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="124"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="124"/>
+      <c r="A21" s="119"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="124"/>
-      <c r="B22" s="124"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="124"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="124"/>
-      <c r="B23" s="124"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="124"/>
+      <c r="A23" s="119"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="124"/>
-      <c r="B24" s="124"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="124"/>
+      <c r="A24" s="119"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="124"/>
-      <c r="B25" s="124"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="124"/>
+      <c r="A25" s="119"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="124"/>
-      <c r="B26" s="124"/>
-      <c r="C26" s="124"/>
-      <c r="D26" s="124"/>
+      <c r="A26" s="119"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="124"/>
-      <c r="B27" s="124"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="124"/>
+      <c r="A27" s="119"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="124"/>
-      <c r="B28" s="124"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="124"/>
+      <c r="A28" s="119"/>
+      <c r="B28" s="119"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="119"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="127"/>
-      <c r="B29" s="127"/>
-      <c r="C29" s="127"/>
-      <c r="D29" s="127"/>
+      <c r="A29" s="118"/>
+      <c r="B29" s="118"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="118"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A30" s="78" t="s">
-        <v>167</v>
+      <c r="A30" s="75" t="s">
+        <v>163</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>34</v>
@@ -4986,24 +4932,24 @@
       <c r="C31" s="22">
         <v>0</v>
       </c>
-      <c r="D31" s="97"/>
+      <c r="D31" s="93"/>
     </row>
     <row r="32" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2</v>
       </c>
-      <c r="B32" s="49" t="s">
+      <c r="B32" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="74"/>
-      <c r="D32" s="97"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="93"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C33" s="22">
         <v>0</v>
@@ -5015,7 +4961,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C34" s="22">
         <v>0</v>
@@ -5027,7 +4973,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C35" s="23">
         <v>0</v>
@@ -5039,7 +4985,7 @@
         <v>2.4</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C36" s="22">
         <v>0</v>
@@ -5051,7 +4997,7 @@
         <v>2.5</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C37" s="22">
         <v>0</v>
@@ -5063,7 +5009,7 @@
         <v>2.6</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C38" s="22">
         <v>0</v>
@@ -5075,7 +5021,7 @@
         <v>2.7</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C39" s="22">
         <v>0</v>
@@ -5087,7 +5033,7 @@
         <v>2.8</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C40" s="22">
         <v>0</v>
@@ -5099,7 +5045,7 @@
         <v>2.9</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C41" s="22">
         <v>0</v>
@@ -5108,10 +5054,10 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C42" s="22">
         <v>0</v>
@@ -5120,10 +5066,10 @@
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C43" s="22">
         <v>0</v>
@@ -5132,10 +5078,10 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C44" s="22">
         <v>0</v>
@@ -5144,10 +5090,10 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="33" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C45" s="22">
         <v>0</v>
@@ -5156,10 +5102,10 @@
     </row>
     <row r="46" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C46" s="22">
         <v>0</v>
@@ -5168,10 +5114,10 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C47" s="22">
         <v>0</v>
@@ -5180,10 +5126,10 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33"/>
-      <c r="B48" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="C48" s="66">
+      <c r="B48" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="63">
         <f>SUM(C33:C47)</f>
         <v>0</v>
       </c>
@@ -5194,7 +5140,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C49" s="23">
         <v>0</v>
@@ -5214,11 +5160,11 @@
       <c r="D50" s="24"/>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="140"/>
-      <c r="B51" s="49" t="s">
+      <c r="A51" s="98"/>
+      <c r="B51" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="66">
+      <c r="C51" s="63">
         <f>SUM($C31+$C48+$C49+$C50)</f>
         <v>0</v>
       </c>
@@ -5231,14 +5177,14 @@
       <c r="D52" s="27"/>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="78" t="s">
-        <v>167</v>
+      <c r="A53" s="75" t="s">
+        <v>163</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D53" s="21" t="s">
         <v>34</v>
@@ -5258,10 +5204,10 @@
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="40" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C55" s="23">
         <v>0</v>
@@ -5270,7 +5216,7 @@
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="40" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B56" s="45" t="s">
         <v>47</v>
@@ -5278,11 +5224,11 @@
       <c r="C56" s="23">
         <v>0</v>
       </c>
-      <c r="D56" s="97"/>
+      <c r="D56" s="93"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="42" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B57" s="45" t="s">
         <v>48</v>
@@ -5294,10 +5240,10 @@
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="43"/>
-      <c r="B58" s="49" t="s">
+      <c r="B58" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="66">
+      <c r="C58" s="63">
         <f>SUM(C54:C57)</f>
         <v>0</v>
       </c>
@@ -5310,14 +5256,14 @@
       <c r="D59" s="31"/>
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="78" t="s">
-        <v>167</v>
+      <c r="A60" s="75" t="s">
+        <v>163</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>34</v>
@@ -5325,7 +5271,7 @@
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="40" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="B61" s="38" t="s">
         <v>54</v>
@@ -5337,7 +5283,7 @@
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="40" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B62" s="38" t="s">
         <v>56</v>
@@ -5349,7 +5295,7 @@
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="40" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B63" s="38" t="s">
         <v>58</v>
@@ -5361,7 +5307,7 @@
     </row>
     <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="40" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B64" s="38" t="s">
         <v>59</v>
@@ -5373,7 +5319,7 @@
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="40" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="B65" s="38" t="s">
         <v>61</v>
@@ -5385,10 +5331,10 @@
     </row>
     <row r="66" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A66" s="32"/>
-      <c r="B66" s="58" t="s">
-        <v>195</v>
-      </c>
-      <c r="C66" s="75">
+      <c r="B66" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="C66" s="72">
         <f>SUM(C61:C65)</f>
         <v>0</v>
       </c>
@@ -5401,14 +5347,14 @@
       <c r="D67" s="25"/>
     </row>
     <row r="68" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A68" s="78" t="s">
-        <v>167</v>
+      <c r="A68" s="75" t="s">
+        <v>163</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>34</v>
@@ -5416,31 +5362,31 @@
     </row>
     <row r="69" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A69" s="44" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B69" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="95">
-        <v>0</v>
-      </c>
-      <c r="D69" s="138"/>
+      <c r="C69" s="91">
+        <v>0</v>
+      </c>
+      <c r="D69" s="96"/>
     </row>
     <row r="70" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A70" s="44" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="B70" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C70" s="95">
-        <v>0</v>
-      </c>
-      <c r="D70" s="138"/>
+      <c r="C70" s="91">
+        <v>0</v>
+      </c>
+      <c r="D70" s="96"/>
     </row>
     <row r="71" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A71" s="44" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B71" s="38" t="s">
         <v>68</v>
@@ -5448,14 +5394,14 @@
       <c r="C71" s="14">
         <v>0</v>
       </c>
-      <c r="D71" s="138"/>
+      <c r="D71" s="96"/>
     </row>
     <row r="72" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A72" s="32"/>
-      <c r="B72" s="58" t="s">
+      <c r="B72" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="67">
+      <c r="C72" s="64">
         <f>SUM($C69:$C71)</f>
         <v>0</v>
       </c>
@@ -5468,14 +5414,14 @@
       <c r="D73" s="25"/>
     </row>
     <row r="74" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A74" s="78" t="s">
-        <v>167</v>
+      <c r="A74" s="75" t="s">
+        <v>163</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D74" s="21" t="s">
         <v>34</v>
@@ -5483,7 +5429,7 @@
     </row>
     <row r="75" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A75" s="44" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B75" s="38" t="s">
         <v>72</v>
@@ -5491,11 +5437,11 @@
       <c r="C75" s="14">
         <v>0</v>
       </c>
-      <c r="D75" s="138"/>
+      <c r="D75" s="96"/>
     </row>
     <row r="76" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A76" s="44" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B76" s="38" t="s">
         <v>73</v>
@@ -5503,11 +5449,11 @@
       <c r="C76" s="14">
         <v>0</v>
       </c>
-      <c r="D76" s="138"/>
+      <c r="D76" s="96"/>
     </row>
     <row r="77" spans="1:4" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A77" s="44" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>75</v>
@@ -5515,11 +5461,11 @@
       <c r="C77" s="14">
         <v>0</v>
       </c>
-      <c r="D77" s="138"/>
+      <c r="D77" s="96"/>
     </row>
     <row r="78" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A78" s="44" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B78" s="38" t="s">
         <v>77</v>
@@ -5527,11 +5473,11 @@
       <c r="C78" s="14">
         <v>0</v>
       </c>
-      <c r="D78" s="138"/>
+      <c r="D78" s="96"/>
     </row>
     <row r="79" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A79" s="44" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B79" s="38" t="s">
         <v>79</v>
@@ -5539,11 +5485,11 @@
       <c r="C79" s="14">
         <v>0</v>
       </c>
-      <c r="D79" s="138"/>
+      <c r="D79" s="96"/>
     </row>
     <row r="80" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A80" s="44" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B80" s="38" t="s">
         <v>81</v>
@@ -5551,11 +5497,11 @@
       <c r="C80" s="14">
         <v>0</v>
       </c>
-      <c r="D80" s="138"/>
+      <c r="D80" s="96"/>
     </row>
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A81" s="44" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B81" s="38" t="s">
         <v>83</v>
@@ -5563,14 +5509,14 @@
       <c r="C81" s="14">
         <v>0</v>
       </c>
-      <c r="D81" s="138"/>
+      <c r="D81" s="96"/>
     </row>
     <row r="82" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A82" s="32"/>
-      <c r="B82" s="49" t="s">
+      <c r="B82" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C82" s="67">
+      <c r="C82" s="64">
         <f>SUM($C75:$C81)</f>
         <v>0</v>
       </c>
@@ -5578,18 +5524,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5605,6 +5539,18 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5634,95 +5580,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="105" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="105" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="107">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="107">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
+      <c r="A7" s="100"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="108"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="92" t="s">
-        <v>169</v>
+        <v>199</v>
+      </c>
+      <c r="C9" s="88" t="s">
+        <v>165</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
-        <v>205</v>
+      <c r="A10" s="140" t="s">
+        <v>201</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>89</v>
@@ -5730,11 +5676,11 @@
       <c r="C10" s="23">
         <v>0</v>
       </c>
-      <c r="D10" s="97"/>
+      <c r="D10" s="93"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
-        <v>206</v>
+      <c r="A11" s="140" t="s">
+        <v>202</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>91</v>
@@ -5742,11 +5688,11 @@
       <c r="C11" s="23">
         <v>0</v>
       </c>
-      <c r="D11" s="97"/>
+      <c r="D11" s="93"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>207</v>
+      <c r="A12" s="140" t="s">
+        <v>203</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>93</v>
@@ -5757,8 +5703,8 @@
       <c r="D12" s="24"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
-        <v>208</v>
+      <c r="A13" s="140" t="s">
+        <v>204</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>95</v>
@@ -5769,8 +5715,8 @@
       <c r="D13" s="24"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
-        <v>210</v>
+      <c r="A14" s="140" t="s">
+        <v>206</v>
       </c>
       <c r="B14" s="38" t="s">
         <v>97</v>
@@ -5782,10 +5728,10 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="41"/>
-      <c r="B15" s="58" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" s="66">
+      <c r="B15" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="63">
         <f>SUM(C10:C14)</f>
         <v>0</v>
       </c>
@@ -5799,21 +5745,21 @@
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="92" t="s">
-        <v>169</v>
+      <c r="C17" s="88" t="s">
+        <v>165</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="40" t="s">
-        <v>211</v>
+      <c r="A18" s="140" t="s">
+        <v>207</v>
       </c>
       <c r="B18" s="38" t="s">
         <v>99</v>
@@ -5824,8 +5770,8 @@
       <c r="D18" s="24"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
-        <v>212</v>
+      <c r="A19" s="140" t="s">
+        <v>208</v>
       </c>
       <c r="B19" s="38" t="s">
         <v>101</v>
@@ -5836,8 +5782,8 @@
       <c r="D19" s="24"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
-        <v>213</v>
+      <c r="A20" s="140" t="s">
+        <v>209</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>103</v>
@@ -5848,8 +5794,8 @@
       <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
-        <v>214</v>
+      <c r="A21" s="140" t="s">
+        <v>210</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>107</v>
@@ -5860,8 +5806,8 @@
       <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
-        <v>215</v>
+      <c r="A22" s="140" t="s">
+        <v>211</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>109</v>
@@ -5872,8 +5818,8 @@
       <c r="D22" s="24"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="40" t="s">
-        <v>216</v>
+      <c r="A23" s="140" t="s">
+        <v>212</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>111</v>
@@ -5884,8 +5830,8 @@
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
-        <v>217</v>
+      <c r="A24" s="140" t="s">
+        <v>213</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>113</v>
@@ -5896,8 +5842,8 @@
       <c r="D24" s="24"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="40" t="s">
-        <v>218</v>
+      <c r="A25" s="140" t="s">
+        <v>214</v>
       </c>
       <c r="B25" s="38" t="s">
         <v>115</v>
@@ -5908,8 +5854,8 @@
       <c r="D25" s="24"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="40" t="s">
-        <v>219</v>
+      <c r="A26" s="140" t="s">
+        <v>215</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>119</v>
@@ -5920,8 +5866,8 @@
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="40" t="s">
-        <v>220</v>
+      <c r="A27" s="140" t="s">
+        <v>216</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>121</v>
@@ -5932,8 +5878,8 @@
       <c r="D27" s="24"/>
     </row>
     <row r="28" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
-        <v>221</v>
+      <c r="A28" s="140" t="s">
+        <v>217</v>
       </c>
       <c r="B28" s="38" t="s">
         <v>123</v>
@@ -5944,8 +5890,8 @@
       <c r="D28" s="24"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
-        <v>222</v>
+      <c r="A29" s="140" t="s">
+        <v>218</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>125</v>
@@ -5956,8 +5902,8 @@
       <c r="D29" s="24"/>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="40" t="s">
-        <v>223</v>
+      <c r="A30" s="140" t="s">
+        <v>219</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>127</v>
@@ -5968,8 +5914,8 @@
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="40" t="s">
-        <v>285</v>
+      <c r="A31" s="140" t="s">
+        <v>275</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>129</v>
@@ -5981,10 +5927,10 @@
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39"/>
-      <c r="B32" s="76" t="s">
-        <v>224</v>
-      </c>
-      <c r="C32" s="77">
+      <c r="B32" s="73" t="s">
+        <v>220</v>
+      </c>
+      <c r="C32" s="74">
         <f>SUM(C18:C31)</f>
         <v>0</v>
       </c>
@@ -6015,1034 +5961,919 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.77734375" customWidth="1"/>
     <col min="2" max="2" width="58.44140625" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="4" max="8" width="8.88671875" style="59"/>
-    <col min="9" max="9" width="2" style="59" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="59" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="8.77734375" style="59" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="59" hidden="1" customWidth="1"/>
+    <col min="4" max="8" width="8.88671875" style="56"/>
+    <col min="9" max="9" width="2" style="56" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="56" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="8.77734375" style="56" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="56" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
     </row>
     <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="132" t="str">
+      <c r="B2" s="127" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="132" t="str">
+      <c r="B3" s="127" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="132"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="133">
+      <c r="B4" s="128">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="133">
+      <c r="B5" s="128">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="134" t="s">
-        <v>279</v>
-      </c>
-      <c r="B6" s="134"/>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
+      <c r="A6" s="129" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" s="129"/>
+      <c r="C6" s="129"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="129"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="134"/>
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="134"/>
-      <c r="L7" s="134"/>
+      <c r="A7" s="129"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="134"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="134"/>
-      <c r="D8" s="134"/>
-      <c r="E8" s="134"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
-      <c r="J8" s="134"/>
-      <c r="K8" s="134"/>
-      <c r="L8" s="134"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="82" t="s">
-        <v>167</v>
+      <c r="A8" s="129"/>
+      <c r="B8" s="129"/>
+      <c r="C8" s="129"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+      <c r="G8" s="129"/>
+      <c r="H8" s="129"/>
+      <c r="I8" s="129"/>
+      <c r="J8" s="129"/>
+      <c r="K8" s="129"/>
+      <c r="L8" s="129"/>
+    </row>
+    <row r="9" spans="1:12" s="86" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="79" t="s">
+        <v>163</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="126" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="137"/>
+      <c r="B10" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="80">
+        <v>0</v>
+      </c>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="125"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="137"/>
+      <c r="B11" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="80">
+        <v>0</v>
+      </c>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="125"/>
+    </row>
+    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="137"/>
+      <c r="B12" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" s="80">
+        <v>0</v>
+      </c>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="125"/>
+      <c r="L12" s="125"/>
+    </row>
+    <row r="13" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="135">
+        <v>43</v>
+      </c>
+      <c r="B13" s="55" t="s">
         <v>225</v>
       </c>
-      <c r="C9" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="D9" s="130" t="s">
+      <c r="C13" s="84">
+        <f>SUM(C10:C12)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="78"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="78"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="78"/>
+    </row>
+    <row r="15" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="81"/>
-      <c r="B10" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="83">
-        <v>0</v>
-      </c>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="129"/>
-      <c r="J10" s="129"/>
-      <c r="K10" s="129"/>
-      <c r="L10" s="129"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="81"/>
-      <c r="B11" s="30" t="s">
+      <c r="E15" s="126"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="136"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="92">
+        <v>0</v>
+      </c>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="124"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="136"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="92">
+        <v>0</v>
+      </c>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="124"/>
+      <c r="J17" s="124"/>
+      <c r="K17" s="124"/>
+      <c r="L17" s="124"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="136"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="92">
+        <v>0</v>
+      </c>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+    </row>
+    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="138">
+        <v>48</v>
+      </c>
+      <c r="B19" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="C11" s="83">
-        <v>0</v>
-      </c>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-      <c r="J11" s="129"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="81"/>
-      <c r="B12" s="30" t="s">
+      <c r="C19" s="84">
+        <f>SUM(C16:C18)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="136"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
+    </row>
+    <row r="21" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" s="126" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="126"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="126"/>
+      <c r="H21" s="126"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="126"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="134"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="83">
+        <v>0</v>
+      </c>
+      <c r="D22" s="125"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="125"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="125"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="134"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="83">
+        <v>0</v>
+      </c>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="125"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="134"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="83">
+        <v>0</v>
+      </c>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="125"/>
+    </row>
+    <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="138">
+        <v>44</v>
+      </c>
+      <c r="B25" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="C12" s="83">
-        <v>0</v>
-      </c>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="81" t="s">
-        <v>145</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>229</v>
-      </c>
-      <c r="C13" s="87">
-        <f>SUM(C10:C12)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="81"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-    </row>
-    <row r="15" spans="1:12" s="90" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="D15" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="81"/>
-      <c r="B16" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="C16" s="83">
-        <v>0</v>
-      </c>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="129"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="81"/>
-      <c r="B17" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="C17" s="83">
-        <v>0</v>
-      </c>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="129"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="129"/>
-    </row>
-    <row r="18" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="81"/>
-      <c r="B18" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="83">
-        <v>0</v>
-      </c>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="129"/>
-      <c r="K18" s="129"/>
-      <c r="L18" s="129"/>
-    </row>
-    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="89">
-        <v>7.2</v>
-      </c>
-      <c r="B19" s="58" t="s">
-        <v>234</v>
-      </c>
-      <c r="C19" s="87">
-        <f>SUM(C16:C18)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="81"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-    </row>
-    <row r="21" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="D21" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="130"/>
-      <c r="F21" s="130"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="130"/>
-      <c r="J21" s="130"/>
-      <c r="K21" s="130"/>
-      <c r="L21" s="130"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="81"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="96">
-        <v>0</v>
-      </c>
-      <c r="D22" s="135"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="135"/>
-      <c r="G22" s="135"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="135"/>
-      <c r="J22" s="135"/>
-      <c r="K22" s="135"/>
-      <c r="L22" s="135"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="81"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="96">
-        <v>0</v>
-      </c>
-      <c r="D23" s="135"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="135"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="135"/>
-      <c r="I23" s="135"/>
-      <c r="J23" s="135"/>
-      <c r="K23" s="135"/>
-      <c r="L23" s="135"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="81"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="96">
-        <v>0</v>
-      </c>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="135"/>
-      <c r="I24" s="135"/>
-      <c r="J24" s="135"/>
-      <c r="K24" s="135"/>
-      <c r="L24" s="135"/>
-    </row>
-    <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="81">
-        <v>7.21</v>
-      </c>
-      <c r="B25" s="58" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="87">
+      <c r="C25" s="84">
         <f>SUM(C22:C24)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="81"/>
-      <c r="E25" s="81"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="81"/>
-      <c r="H25" s="81"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="81"/>
-      <c r="K25" s="81"/>
-      <c r="L25" s="81"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="78"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="78"/>
+      <c r="I25" s="78"/>
+      <c r="J25" s="78"/>
+      <c r="K25" s="78"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="81"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="81"/>
-      <c r="L26" s="81"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="82" t="s">
-        <v>167</v>
+      <c r="A27" s="79" t="s">
+        <v>163</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C27" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="D27" s="130" t="s">
+      <c r="C27" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="130"/>
-      <c r="F27" s="130"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="130"/>
-      <c r="I27" s="130"/>
-      <c r="J27" s="130"/>
-      <c r="K27" s="130"/>
-      <c r="L27" s="130"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="126"/>
+      <c r="K27" s="126"/>
+      <c r="L27" s="126"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="81"/>
+      <c r="A28" s="134"/>
       <c r="B28" s="30"/>
-      <c r="C28" s="86">
-        <v>0</v>
-      </c>
-      <c r="D28" s="129"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="129"/>
-      <c r="K28" s="129"/>
-      <c r="L28" s="129"/>
+      <c r="C28" s="83">
+        <v>0</v>
+      </c>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="125"/>
+      <c r="L28" s="125"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="81"/>
+      <c r="A29" s="134"/>
       <c r="B29" s="30"/>
-      <c r="C29" s="86">
-        <v>0</v>
-      </c>
-      <c r="D29" s="129"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="129"/>
-      <c r="I29" s="129"/>
-      <c r="J29" s="129"/>
-      <c r="K29" s="129"/>
-      <c r="L29" s="129"/>
+      <c r="C29" s="83">
+        <v>0</v>
+      </c>
+      <c r="D29" s="125"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
+      <c r="I29" s="125"/>
+      <c r="J29" s="125"/>
+      <c r="K29" s="125"/>
+      <c r="L29" s="125"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="81"/>
+      <c r="A30" s="134"/>
       <c r="B30" s="30"/>
-      <c r="C30" s="86">
-        <v>0</v>
-      </c>
-      <c r="D30" s="129"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="129"/>
-      <c r="I30" s="129"/>
-      <c r="J30" s="129"/>
-      <c r="K30" s="129"/>
-      <c r="L30" s="129"/>
+      <c r="C30" s="83">
+        <v>0</v>
+      </c>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="125"/>
+      <c r="J30" s="125"/>
+      <c r="K30" s="125"/>
+      <c r="L30" s="125"/>
     </row>
     <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="81">
-        <v>7.18</v>
-      </c>
-      <c r="B31" s="58" t="s">
-        <v>237</v>
-      </c>
-      <c r="C31" s="87">
+      <c r="A31" s="138">
+        <v>45</v>
+      </c>
+      <c r="B31" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="C31" s="84">
         <f>SUM(C28:C30)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="78"/>
+      <c r="K31" s="78"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="81"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
-    </row>
-    <row r="33" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="B33" s="10" t="s">
+      <c r="A32" s="134"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="78"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="78"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" s="82" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="126" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="126"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="126"/>
+      <c r="H33" s="126"/>
+      <c r="I33" s="126"/>
+      <c r="J33" s="126"/>
+      <c r="K33" s="126"/>
+      <c r="L33" s="126"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="134"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="83">
+        <v>0</v>
+      </c>
+      <c r="D34" s="125"/>
+      <c r="E34" s="125"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="125"/>
+      <c r="J34" s="125"/>
+      <c r="K34" s="125"/>
+      <c r="L34" s="125"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="134"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="83">
+        <v>0</v>
+      </c>
+      <c r="D35" s="125"/>
+      <c r="E35" s="125"/>
+      <c r="F35" s="125"/>
+      <c r="G35" s="125"/>
+      <c r="H35" s="125"/>
+      <c r="I35" s="125"/>
+      <c r="J35" s="125"/>
+      <c r="K35" s="125"/>
+      <c r="L35" s="125"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="134"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="83">
+        <v>0</v>
+      </c>
+      <c r="D36" s="125"/>
+      <c r="E36" s="125"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="125"/>
+      <c r="H36" s="125"/>
+      <c r="I36" s="125"/>
+      <c r="J36" s="125"/>
+      <c r="K36" s="125"/>
+      <c r="L36" s="125"/>
+    </row>
+    <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="138">
+        <v>46</v>
+      </c>
+      <c r="B37" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="84">
+        <f>SUM(C34:C36)</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="78"/>
+      <c r="E37" s="78"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="78"/>
+      <c r="I37" s="78"/>
+      <c r="J37" s="78"/>
+      <c r="K37" s="78"/>
+      <c r="L37" s="78"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="134"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="78"/>
+      <c r="I38" s="78"/>
+      <c r="J38" s="78"/>
+      <c r="K38" s="78"/>
+      <c r="L38" s="78"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="C33" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="D33" s="130" t="s">
+      <c r="C39" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="D39" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="130"/>
-      <c r="F33" s="130"/>
-      <c r="G33" s="130"/>
-      <c r="H33" s="130"/>
-      <c r="I33" s="130"/>
-      <c r="J33" s="130"/>
-      <c r="K33" s="130"/>
-      <c r="L33" s="130"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="81"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="86">
-        <v>0</v>
-      </c>
-      <c r="D34" s="129"/>
-      <c r="E34" s="129"/>
-      <c r="F34" s="129"/>
-      <c r="G34" s="129"/>
-      <c r="H34" s="129"/>
-      <c r="I34" s="129"/>
-      <c r="J34" s="129"/>
-      <c r="K34" s="129"/>
-      <c r="L34" s="129"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="81"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="86">
-        <v>0</v>
-      </c>
-      <c r="D35" s="129"/>
-      <c r="E35" s="129"/>
-      <c r="F35" s="129"/>
-      <c r="G35" s="129"/>
-      <c r="H35" s="129"/>
-      <c r="I35" s="129"/>
-      <c r="J35" s="129"/>
-      <c r="K35" s="129"/>
-      <c r="L35" s="129"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="81"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="86">
-        <v>0</v>
-      </c>
-      <c r="D36" s="129"/>
-      <c r="E36" s="129"/>
-      <c r="F36" s="129"/>
-      <c r="G36" s="129"/>
-      <c r="H36" s="129"/>
-      <c r="I36" s="129"/>
-      <c r="J36" s="129"/>
-      <c r="K36" s="129"/>
-      <c r="L36" s="129"/>
-    </row>
-    <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="81" t="s">
-        <v>159</v>
-      </c>
-      <c r="B37" s="58" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="87">
-        <f>SUM(C34:C36)</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="81"/>
-      <c r="K37" s="81"/>
-      <c r="L37" s="81"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="81"/>
-      <c r="B38" s="49"/>
-      <c r="C38" s="84"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="81"/>
-      <c r="K38" s="81"/>
-      <c r="L38" s="81"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="B39" s="85" t="s">
-        <v>162</v>
-      </c>
-      <c r="C39" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="D39" s="130" t="s">
+      <c r="E39" s="126"/>
+      <c r="F39" s="126"/>
+      <c r="G39" s="126"/>
+      <c r="H39" s="126"/>
+      <c r="I39" s="126"/>
+      <c r="J39" s="126"/>
+      <c r="K39" s="126"/>
+      <c r="L39" s="126"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="134"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="83">
+        <v>0</v>
+      </c>
+      <c r="D40" s="125"/>
+      <c r="E40" s="125"/>
+      <c r="F40" s="125"/>
+      <c r="G40" s="125"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="125"/>
+      <c r="J40" s="125"/>
+      <c r="K40" s="125"/>
+      <c r="L40" s="125"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="134"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="83">
+        <v>0</v>
+      </c>
+      <c r="D41" s="125"/>
+      <c r="E41" s="125"/>
+      <c r="F41" s="125"/>
+      <c r="G41" s="125"/>
+      <c r="H41" s="125"/>
+      <c r="I41" s="125"/>
+      <c r="J41" s="125"/>
+      <c r="K41" s="125"/>
+      <c r="L41" s="125"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="134"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="83">
+        <v>0</v>
+      </c>
+      <c r="D42" s="125"/>
+      <c r="E42" s="125"/>
+      <c r="F42" s="125"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="125"/>
+      <c r="L42" s="125"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="138">
+        <v>47</v>
+      </c>
+      <c r="B43" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="C43" s="84">
+        <f>SUM(C40:C42)</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="78"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="78"/>
+      <c r="L43" s="78"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="134"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="78"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="78"/>
+      <c r="L44" s="78"/>
+    </row>
+    <row r="45" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="130"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="130"/>
-      <c r="H39" s="130"/>
-      <c r="I39" s="130"/>
-      <c r="J39" s="130"/>
-      <c r="K39" s="130"/>
-      <c r="L39" s="130"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="81"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="86">
-        <v>0</v>
-      </c>
-      <c r="D40" s="129"/>
-      <c r="E40" s="129"/>
-      <c r="F40" s="129"/>
-      <c r="G40" s="129"/>
-      <c r="H40" s="129"/>
-      <c r="I40" s="129"/>
-      <c r="J40" s="129"/>
-      <c r="K40" s="129"/>
-      <c r="L40" s="129"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="81"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="86">
-        <v>0</v>
-      </c>
-      <c r="D41" s="129"/>
-      <c r="E41" s="129"/>
-      <c r="F41" s="129"/>
-      <c r="G41" s="129"/>
-      <c r="H41" s="129"/>
-      <c r="I41" s="129"/>
-      <c r="J41" s="129"/>
-      <c r="K41" s="129"/>
-      <c r="L41" s="129"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="81"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="86">
-        <v>0</v>
-      </c>
-      <c r="D42" s="129"/>
-      <c r="E42" s="129"/>
-      <c r="F42" s="129"/>
-      <c r="G42" s="129"/>
-      <c r="H42" s="129"/>
-      <c r="I42" s="129"/>
-      <c r="J42" s="129"/>
-      <c r="K42" s="129"/>
-      <c r="L42" s="129"/>
-    </row>
-    <row r="43" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="81" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="58" t="s">
-        <v>239</v>
-      </c>
-      <c r="C43" s="87">
-        <f>SUM(C40:C42)</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
-      <c r="H43" s="81"/>
-      <c r="I43" s="81"/>
-      <c r="J43" s="81"/>
-      <c r="K43" s="81"/>
-      <c r="L43" s="81"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="81"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="L44" s="81"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="B45" s="85" t="s">
-        <v>164</v>
-      </c>
-      <c r="C45" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="D45" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" s="130"/>
-      <c r="F45" s="130"/>
-      <c r="G45" s="130"/>
-      <c r="H45" s="130"/>
-      <c r="I45" s="130"/>
-      <c r="J45" s="130"/>
-      <c r="K45" s="130"/>
-      <c r="L45" s="130"/>
+      <c r="E45" s="126"/>
+      <c r="F45" s="126"/>
+      <c r="G45" s="126"/>
+      <c r="H45" s="126"/>
+      <c r="I45" s="126"/>
+      <c r="J45" s="126"/>
+      <c r="K45" s="126"/>
+      <c r="L45" s="126"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="81"/>
+      <c r="A46" s="134"/>
       <c r="B46" s="30"/>
-      <c r="C46" s="86">
-        <v>0</v>
-      </c>
-      <c r="D46" s="129"/>
-      <c r="E46" s="129"/>
-      <c r="F46" s="129"/>
-      <c r="G46" s="129"/>
-      <c r="H46" s="129"/>
-      <c r="I46" s="129"/>
-      <c r="J46" s="129"/>
-      <c r="K46" s="129"/>
-      <c r="L46" s="129"/>
+      <c r="C46" s="83">
+        <v>0</v>
+      </c>
+      <c r="D46" s="125"/>
+      <c r="E46" s="125"/>
+      <c r="F46" s="125"/>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="125"/>
+      <c r="J46" s="125"/>
+      <c r="K46" s="125"/>
+      <c r="L46" s="125"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="81"/>
+      <c r="A47" s="134"/>
       <c r="B47" s="30"/>
-      <c r="C47" s="86">
-        <v>0</v>
-      </c>
-      <c r="D47" s="129"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="129"/>
-      <c r="G47" s="129"/>
-      <c r="H47" s="129"/>
-      <c r="I47" s="129"/>
-      <c r="J47" s="129"/>
-      <c r="K47" s="129"/>
-      <c r="L47" s="129"/>
+      <c r="C47" s="83">
+        <v>0</v>
+      </c>
+      <c r="D47" s="125"/>
+      <c r="E47" s="125"/>
+      <c r="F47" s="125"/>
+      <c r="G47" s="125"/>
+      <c r="H47" s="125"/>
+      <c r="I47" s="125"/>
+      <c r="J47" s="125"/>
+      <c r="K47" s="125"/>
+      <c r="L47" s="125"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="81"/>
+      <c r="A48" s="134"/>
       <c r="B48" s="30"/>
-      <c r="C48" s="86">
-        <v>0</v>
-      </c>
-      <c r="D48" s="129"/>
-      <c r="E48" s="129"/>
-      <c r="F48" s="129"/>
-      <c r="G48" s="129"/>
-      <c r="H48" s="129"/>
-      <c r="I48" s="129"/>
-      <c r="J48" s="129"/>
-      <c r="K48" s="129"/>
-      <c r="L48" s="129"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="81" t="s">
-        <v>163</v>
-      </c>
-      <c r="B49" s="58" t="s">
-        <v>240</v>
-      </c>
-      <c r="C49" s="87">
+      <c r="C48" s="83">
+        <v>0</v>
+      </c>
+      <c r="D48" s="125"/>
+      <c r="E48" s="125"/>
+      <c r="F48" s="125"/>
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="125"/>
+      <c r="J48" s="125"/>
+      <c r="K48" s="125"/>
+      <c r="L48" s="125"/>
+    </row>
+    <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="139">
+        <v>48</v>
+      </c>
+      <c r="B49" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="C49" s="84">
         <f>SUM(C46:C48)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="81"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="81"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="81"/>
-      <c r="J49" s="81"/>
-      <c r="K49" s="81"/>
-      <c r="L49" s="81"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="81"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="84"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="81"/>
-      <c r="K50" s="81"/>
-      <c r="L50" s="81"/>
-    </row>
-    <row r="51" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="C51" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="D51" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="E51" s="130"/>
-      <c r="F51" s="130"/>
-      <c r="G51" s="130"/>
-      <c r="H51" s="130"/>
-      <c r="I51" s="130"/>
-      <c r="J51" s="130"/>
-      <c r="K51" s="130"/>
-      <c r="L51" s="130"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="81"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="86">
-        <v>0</v>
-      </c>
-      <c r="D52" s="129"/>
-      <c r="E52" s="129"/>
-      <c r="F52" s="129"/>
-      <c r="G52" s="129"/>
-      <c r="H52" s="129"/>
-      <c r="I52" s="129"/>
-      <c r="J52" s="129"/>
-      <c r="K52" s="129"/>
-      <c r="L52" s="129"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="81"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="86">
-        <v>0</v>
-      </c>
-      <c r="D53" s="129"/>
-      <c r="E53" s="129"/>
-      <c r="F53" s="129"/>
-      <c r="G53" s="129"/>
-      <c r="H53" s="129"/>
-      <c r="I53" s="129"/>
-      <c r="J53" s="129"/>
-      <c r="K53" s="129"/>
-      <c r="L53" s="129"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="81"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="86">
-        <v>0</v>
-      </c>
-      <c r="D54" s="129"/>
-      <c r="E54" s="129"/>
-      <c r="F54" s="129"/>
-      <c r="G54" s="129"/>
-      <c r="H54" s="129"/>
-      <c r="I54" s="129"/>
-      <c r="J54" s="129"/>
-      <c r="K54" s="129"/>
-      <c r="L54" s="129"/>
-    </row>
-    <row r="55" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="B55" s="58" t="s">
-        <v>241</v>
-      </c>
-      <c r="C55" s="87">
-        <f>SUM(C52:C54)</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="131"/>
-      <c r="E55" s="131"/>
-      <c r="F55" s="131"/>
-      <c r="G55" s="131"/>
-      <c r="H55" s="131"/>
-      <c r="I55" s="131"/>
-      <c r="J55" s="131"/>
-      <c r="K55" s="131"/>
-      <c r="L55" s="131"/>
+      <c r="D49" s="130"/>
+      <c r="E49" s="130"/>
+      <c r="F49" s="130"/>
+      <c r="G49" s="130"/>
+      <c r="H49" s="130"/>
+      <c r="I49" s="130"/>
+      <c r="J49" s="130"/>
+      <c r="K49" s="130"/>
+      <c r="L49" s="130"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="D22:L22"/>
+  <mergeCells count="35">
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="D46:L46"/>
+    <mergeCell ref="D47:L47"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="D49:L49"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D22:L22"/>
     <mergeCell ref="D23:L23"/>
     <mergeCell ref="D24:L24"/>
+    <mergeCell ref="D28:L28"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D15:L15"/>
+    <mergeCell ref="D21:L21"/>
+    <mergeCell ref="D27:L27"/>
+    <mergeCell ref="D33:L33"/>
     <mergeCell ref="D9:L9"/>
-    <mergeCell ref="D15:L15"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="A6:L8"/>
-    <mergeCell ref="D55:L55"/>
-    <mergeCell ref="D10:L10"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
     <mergeCell ref="D16:L16"/>
-    <mergeCell ref="D17:L17"/>
-    <mergeCell ref="D18:L18"/>
-    <mergeCell ref="D28:L28"/>
-    <mergeCell ref="D29:L29"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="D34:L34"/>
     <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D21:L21"/>
-    <mergeCell ref="D27:L27"/>
-    <mergeCell ref="D33:L33"/>
-    <mergeCell ref="D39:L39"/>
-    <mergeCell ref="D54:L54"/>
-    <mergeCell ref="D52:L52"/>
-    <mergeCell ref="D53:L53"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="D48:L48"/>
-    <mergeCell ref="D51:L51"/>
-    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="D17:L17"/>
+    <mergeCell ref="D18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>

--- a/noprofit/en/11255/inpag-template.xlsx
+++ b/noprofit/en/11255/inpag-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA30A08-D3BB-461A-8F2F-997CC750366D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8CE32C-3852-46A9-9168-4BB40A256DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" firstSheet="1" activeTab="4" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
   <sheets>
     <sheet name="General information" sheetId="7" r:id="rId1"/>
@@ -1080,7 +1080,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1354,9 +1354,42 @@
     <xf numFmtId="1" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1369,15 +1402,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1399,86 +1423,56 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1869,327 +1863,333 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="106" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="132" t="s">
+      <c r="A2" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="131" t="s">
+      <c r="A4" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="131" t="s">
+      <c r="A6" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="132" t="s">
+      <c r="B6" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132"/>
-      <c r="G6" s="132"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="131" t="s">
+      <c r="A7" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="132" t="s">
+      <c r="B7" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="131" t="s">
+      <c r="A8" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="133">
+      <c r="B8" s="105">
         <v>45292</v>
       </c>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="131" t="s">
+      <c r="A9" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="133">
+      <c r="B9" s="105">
         <v>45657</v>
       </c>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A10" s="131" t="s">
+      <c r="A10" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="133" t="s">
+      <c r="B10" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A12" s="131"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A13" s="131"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="131"/>
-      <c r="B14" s="133"/>
-      <c r="C14" s="133"/>
-      <c r="D14" s="133"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
+      <c r="A14" s="100"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="131"/>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
+      <c r="A15" s="100"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A16" s="131"/>
-      <c r="B16" s="133"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
+      <c r="A16" s="100"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A17" s="131" t="s">
+      <c r="A17" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="133" t="s">
+      <c r="B17" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="133"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A18" s="131"/>
-      <c r="B18" s="133" t="s">
+      <c r="A18" s="100"/>
+      <c r="B18" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="133"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A19" s="131"/>
-      <c r="B19" s="133" t="s">
+      <c r="A19" s="100"/>
+      <c r="B19" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A20" s="131"/>
-      <c r="B20" s="133" t="s">
+      <c r="A20" s="100"/>
+      <c r="B20" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="133"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="133"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A21" s="131" t="s">
+      <c r="A21" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="133" t="s">
+      <c r="B21" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="133"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A22" s="131" t="s">
+      <c r="A22" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="133" t="s">
+      <c r="B22" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="133"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="131"/>
-      <c r="B23" s="133" t="s">
+      <c r="A23" s="100"/>
+      <c r="B23" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="133"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A24" s="131"/>
-      <c r="B24" s="133" t="s">
+      <c r="A24" s="100"/>
+      <c r="B24" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A25" s="131"/>
-      <c r="B25" s="133" t="s">
+      <c r="A25" s="100"/>
+      <c r="B25" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A26" s="131"/>
-      <c r="B26" s="133" t="s">
+      <c r="A26" s="100"/>
+      <c r="B26" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="133"/>
-      <c r="D26" s="133"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A27" s="131"/>
-      <c r="B27" s="133" t="s">
+      <c r="A27" s="100"/>
+      <c r="B27" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="133"/>
-      <c r="D27" s="133"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="105"/>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A28" s="131"/>
-      <c r="B28" s="133" t="s">
+      <c r="A28" s="100"/>
+      <c r="B28" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="133"/>
-      <c r="D28" s="133"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2206,12 +2206,6 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2240,84 +2234,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="111"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="100"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75" t="s">
@@ -2340,12 +2334,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="45"/>
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
@@ -2439,12 +2433,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45"/>
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45" t="s">
@@ -2572,12 +2566,12 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
-      <c r="B26" s="103" t="s">
+      <c r="B26" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
+      <c r="C26" s="114"/>
+      <c r="D26" s="114"/>
+      <c r="E26" s="114"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45" t="s">
@@ -2688,12 +2682,12 @@
     </row>
     <row r="34" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45"/>
-      <c r="B34" s="103" t="s">
+      <c r="B34" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
+      <c r="C34" s="114"/>
+      <c r="D34" s="114"/>
+      <c r="E34" s="114"/>
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45" t="s">
@@ -2770,12 +2764,12 @@
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45"/>
-      <c r="B40" s="103" t="s">
+      <c r="B40" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="103"/>
-      <c r="D40" s="103"/>
-      <c r="E40" s="103"/>
+      <c r="C40" s="114"/>
+      <c r="D40" s="114"/>
+      <c r="E40" s="114"/>
     </row>
     <row r="41" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45" t="s">
@@ -2898,10 +2892,10 @@
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45"/>
-      <c r="B48" s="103" t="s">
+      <c r="B48" s="114" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="103"/>
+      <c r="C48" s="114"/>
       <c r="D48" s="63">
         <f>SUM(D41:D47)</f>
         <v>0</v>
@@ -2913,10 +2907,10 @@
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45"/>
-      <c r="B49" s="103" t="s">
+      <c r="B49" s="114" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="103"/>
+      <c r="C49" s="114"/>
       <c r="D49" s="63">
         <f>SUM(D32,D38,D48)</f>
         <v>0</v>
@@ -2944,11 +2938,11 @@
       <c r="A52" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="102" t="str">
+      <c r="B52" s="113" t="str">
         <f>IF((D15+D23+D32=D38+D48),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C52" s="102"/>
+      <c r="C52" s="113"/>
       <c r="D52" s="54">
         <f>D49-D23</f>
         <v>0</v>
@@ -2958,12 +2952,12 @@
       <c r="A53" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="B53" s="101" t="str">
+      <c r="B53" s="112" t="str">
         <f>IF((E15+E23+E32=E38+E48),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="101"/>
-      <c r="D53" s="101"/>
+      <c r="C53" s="112"/>
+      <c r="D53" s="112"/>
       <c r="E53" s="54">
         <f>E49-E23</f>
         <v>0</v>
@@ -2977,11 +2971,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="B52:C52"/>
@@ -2992,6 +2981,11 @@
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B52">
@@ -3045,13 +3039,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
@@ -3059,72 +3053,72 @@
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="116" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="116" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="109">
+      <c r="B4" s="117">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="117">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="111"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="100"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="75" t="s">
@@ -3619,13 +3613,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3634,72 +3628,72 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="100"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="111"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="100"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="75" t="s">
@@ -3722,10 +3716,10 @@
       <c r="A10" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="118" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="118"/>
       <c r="D10" s="14">
         <v>0</v>
       </c>
@@ -3759,11 +3753,11 @@
       <c r="A13" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="120" t="s">
         <v>235</v>
       </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="112"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="120"/>
       <c r="E13" s="14">
         <v>0</v>
       </c>
@@ -3772,22 +3766,22 @@
       <c r="A14" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="112"/>
-      <c r="D14" s="112"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="120"/>
       <c r="E14" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="45"/>
-      <c r="B15" s="111" t="s">
+      <c r="B15" s="119" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="119"/>
       <c r="E15" s="68">
         <f>SUM(E13:E14)</f>
         <v>0</v>
@@ -3821,11 +3815,11 @@
       <c r="A18" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
       <c r="E18" s="14">
         <v>0</v>
       </c>
@@ -3834,11 +3828,11 @@
       <c r="A19" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="121" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="113"/>
-      <c r="D19" s="113"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
       <c r="E19" s="14">
         <v>0</v>
       </c>
@@ -3847,11 +3841,11 @@
       <c r="A20" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="B20" s="113" t="s">
+      <c r="B20" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="113"/>
-      <c r="D20" s="113"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="121"/>
       <c r="E20" s="14">
         <v>0</v>
       </c>
@@ -3860,22 +3854,22 @@
       <c r="A21" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="B21" s="112" t="s">
+      <c r="B21" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="112"/>
-      <c r="D21" s="112"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="120"/>
       <c r="E21" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="45"/>
-      <c r="B22" s="111" t="s">
+      <c r="B22" s="119" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
       <c r="E22" s="68">
         <f>SUM(E18:E21)</f>
         <v>0</v>
@@ -3893,11 +3887,11 @@
       <c r="A24" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="111" t="s">
+      <c r="B24" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
       <c r="E24" s="63">
         <f>SUM(D10,E15,E22)</f>
         <v>0</v>
@@ -3905,11 +3899,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B24:D24"/>
@@ -3921,6 +3910,11 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -3947,94 +3941,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="111"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="100"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="115" t="s">
+      <c r="B9" s="124" t="s">
         <v>234</v>
       </c>
-      <c r="C9" s="115"/>
+      <c r="C9" s="124"/>
       <c r="D9" s="75" t="s">
         <v>34</v>
       </c>
@@ -4047,30 +4041,30 @@
       <c r="A10" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="114" t="s">
         <v>235</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
       <c r="E10" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
+      <c r="A11" s="122"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
     </row>
     <row r="12" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="115" t="s">
+      <c r="B12" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="115"/>
+      <c r="C12" s="124"/>
       <c r="D12" s="75" t="s">
         <v>34</v>
       </c>
@@ -4083,10 +4077,10 @@
       <c r="A13" s="45" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="113" t="s">
+      <c r="B13" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="121"/>
       <c r="D13" s="94">
         <v>26</v>
       </c>
@@ -4099,10 +4093,10 @@
       <c r="A14" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="B14" s="113" t="s">
+      <c r="B14" s="121" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="113"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="94">
         <v>32</v>
       </c>
@@ -4114,10 +4108,10 @@
       <c r="A15" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="B15" s="113" t="s">
+      <c r="B15" s="121" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="113"/>
+      <c r="C15" s="121"/>
       <c r="D15" s="94">
         <v>36</v>
       </c>
@@ -4129,10 +4123,10 @@
       <c r="A16" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="B16" s="113" t="s">
+      <c r="B16" s="121" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="113"/>
+      <c r="C16" s="121"/>
       <c r="D16" s="94">
         <v>33</v>
       </c>
@@ -4144,10 +4138,10 @@
       <c r="A17" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="B17" s="113" t="s">
+      <c r="B17" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="113"/>
+      <c r="C17" s="121"/>
       <c r="D17" s="94">
         <v>34</v>
       </c>
@@ -4159,10 +4153,10 @@
       <c r="A18" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="113"/>
+      <c r="C18" s="121"/>
       <c r="D18" s="94">
         <v>35</v>
       </c>
@@ -4175,10 +4169,10 @@
       <c r="A19" s="45" t="s">
         <v>256</v>
       </c>
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="113"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="94">
         <v>27</v>
       </c>
@@ -4191,10 +4185,10 @@
       <c r="A20" s="45" t="s">
         <v>242</v>
       </c>
-      <c r="B20" s="113" t="s">
+      <c r="B20" s="121" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="113"/>
+      <c r="C20" s="121"/>
       <c r="D20" s="94">
         <v>28</v>
       </c>
@@ -4206,10 +4200,10 @@
       <c r="A21" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="B21" s="113" t="s">
+      <c r="B21" s="121" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="113"/>
+      <c r="C21" s="121"/>
       <c r="D21" s="94">
         <v>37</v>
       </c>
@@ -4222,10 +4216,10 @@
       <c r="A22" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="B22" s="113" t="s">
+      <c r="B22" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="113"/>
+      <c r="C22" s="121"/>
       <c r="D22" s="94">
         <v>38</v>
       </c>
@@ -4238,10 +4232,10 @@
       <c r="A23" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="B23" s="113" t="s">
+      <c r="B23" s="121" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="113"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="94">
         <v>39</v>
       </c>
@@ -4254,10 +4248,10 @@
       <c r="A24" s="45" t="s">
         <v>246</v>
       </c>
-      <c r="B24" s="113" t="s">
+      <c r="B24" s="121" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="113"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="94">
         <v>40</v>
       </c>
@@ -4270,10 +4264,10 @@
       <c r="A25" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="123" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="114"/>
+      <c r="C25" s="123"/>
       <c r="D25" s="94">
         <v>41</v>
       </c>
@@ -4286,10 +4280,10 @@
       <c r="A26" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="B26" s="114" t="s">
+      <c r="B26" s="123" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="114"/>
+      <c r="C26" s="123"/>
       <c r="D26" s="94">
         <v>42</v>
       </c>
@@ -4302,10 +4296,10 @@
       <c r="A27" s="45" t="s">
         <v>249</v>
       </c>
-      <c r="B27" s="113" t="s">
+      <c r="B27" s="121" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="113"/>
+      <c r="C27" s="121"/>
       <c r="D27" s="94">
         <v>25</v>
       </c>
@@ -4316,11 +4310,11 @@
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="45"/>
-      <c r="B28" s="103" t="s">
+      <c r="B28" s="114" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="103"/>
-      <c r="D28" s="103"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
       <c r="E28" s="63">
         <f>E10+SUM(E13:E27)</f>
         <v>0</v>
@@ -4337,10 +4331,10 @@
       <c r="A30" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="115" t="s">
+      <c r="B30" s="124" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="115"/>
+      <c r="C30" s="124"/>
       <c r="D30" s="75" t="s">
         <v>34</v>
       </c>
@@ -4353,10 +4347,10 @@
       <c r="A31" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="B31" s="114" t="s">
+      <c r="B31" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="114"/>
+      <c r="C31" s="123"/>
       <c r="D31" s="94">
         <v>29</v>
       </c>
@@ -4368,10 +4362,10 @@
       <c r="A32" s="45" t="s">
         <v>253</v>
       </c>
-      <c r="B32" s="114" t="s">
+      <c r="B32" s="123" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="114"/>
+      <c r="C32" s="123"/>
       <c r="D32" s="94">
         <v>30</v>
       </c>
@@ -4383,10 +4377,10 @@
       <c r="A33" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="B33" s="114" t="s">
+      <c r="B33" s="123" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="114"/>
+      <c r="C33" s="123"/>
       <c r="D33" s="94">
         <v>31</v>
       </c>
@@ -4396,11 +4390,11 @@
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45"/>
-      <c r="B34" s="103" t="s">
+      <c r="B34" s="114" t="s">
         <v>146</v>
       </c>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
+      <c r="C34" s="114"/>
+      <c r="D34" s="114"/>
       <c r="E34" s="63">
         <f>E10+E28+SUM(E31:E33)</f>
         <v>0</v>
@@ -4417,10 +4411,10 @@
       <c r="A36" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B36" s="115" t="s">
+      <c r="B36" s="124" t="s">
         <v>147</v>
       </c>
-      <c r="C36" s="115"/>
+      <c r="C36" s="124"/>
       <c r="D36" s="75" t="s">
         <v>34</v>
       </c>
@@ -4434,10 +4428,10 @@
       <c r="A37" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="B37" s="114" t="s">
+      <c r="B37" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="114"/>
+      <c r="C37" s="123"/>
       <c r="D37" s="94">
         <v>24</v>
       </c>
@@ -4447,11 +4441,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45"/>
-      <c r="B38" s="103" t="s">
+      <c r="B38" s="114" t="s">
         <v>148</v>
       </c>
-      <c r="C38" s="103"/>
-      <c r="D38" s="103"/>
+      <c r="C38" s="114"/>
+      <c r="D38" s="114"/>
       <c r="E38" s="63">
         <f>E10+E28+E34+SUM(E37:E37)</f>
         <v>0</v>
@@ -4466,11 +4460,11 @@
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45"/>
-      <c r="B40" s="103" t="s">
+      <c r="B40" s="114" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="103"/>
-      <c r="D40" s="103"/>
+      <c r="C40" s="114"/>
+      <c r="D40" s="114"/>
       <c r="E40" s="63">
         <f>SUM(E28,E34,E38)</f>
         <v>0</v>
@@ -4487,19 +4481,19 @@
       <c r="A42" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="B42" s="117" t="s">
+      <c r="B42" s="125" t="s">
         <v>151</v>
       </c>
-      <c r="C42" s="117"/>
-      <c r="D42" s="117"/>
+      <c r="C42" s="125"/>
+      <c r="D42" s="125"/>
       <c r="E42" s="22"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="45"/>
-      <c r="B43" s="103" t="s">
+      <c r="B43" s="114" t="s">
         <v>152</v>
       </c>
-      <c r="C43" s="103"/>
+      <c r="C43" s="114"/>
       <c r="D43" s="97">
         <v>43</v>
       </c>
@@ -4510,11 +4504,11 @@
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="45"/>
-      <c r="B44" s="103" t="s">
+      <c r="B44" s="114" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="103"/>
-      <c r="D44" s="103"/>
+      <c r="C44" s="114"/>
+      <c r="D44" s="114"/>
       <c r="E44" s="70">
         <f>'Statement of financial position'!D22</f>
         <v>0</v>
@@ -4522,11 +4516,11 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="45"/>
-      <c r="B45" s="103" t="s">
+      <c r="B45" s="114" t="s">
         <v>154</v>
       </c>
-      <c r="C45" s="103"/>
-      <c r="D45" s="103"/>
+      <c r="C45" s="114"/>
+      <c r="D45" s="114"/>
       <c r="E45" s="70">
         <f>'Statement of financial position'!E22</f>
         <v>0</v>
@@ -4534,11 +4528,11 @@
     </row>
     <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A46" s="45"/>
-      <c r="B46" s="103" t="s">
+      <c r="B46" s="114" t="s">
         <v>155</v>
       </c>
-      <c r="C46" s="103"/>
-      <c r="D46" s="103"/>
+      <c r="C46" s="114"/>
+      <c r="D46" s="114"/>
       <c r="E46" s="70">
         <f>E45-E44</f>
         <v>0</v>
@@ -4569,10 +4563,10 @@
     </row>
     <row r="50" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A50" s="31"/>
-      <c r="B50" s="116" t="s">
+      <c r="B50" s="122" t="s">
         <v>157</v>
       </c>
-      <c r="C50" s="116"/>
+      <c r="C50" s="122"/>
       <c r="D50" s="94">
         <v>44</v>
       </c>
@@ -4580,10 +4574,10 @@
     </row>
     <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A51" s="31"/>
-      <c r="B51" s="116" t="s">
+      <c r="B51" s="122" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="116"/>
+      <c r="C51" s="122"/>
       <c r="D51" s="94">
         <v>45</v>
       </c>
@@ -4591,10 +4585,10 @@
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="31"/>
-      <c r="B52" s="116" t="s">
+      <c r="B52" s="122" t="s">
         <v>159</v>
       </c>
-      <c r="C52" s="116"/>
+      <c r="C52" s="122"/>
       <c r="D52" s="94">
         <v>46</v>
       </c>
@@ -4602,10 +4596,10 @@
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
-      <c r="B53" s="116" t="s">
+      <c r="B53" s="122" t="s">
         <v>160</v>
       </c>
-      <c r="C53" s="116"/>
+      <c r="C53" s="122"/>
       <c r="D53" s="94">
         <v>47</v>
       </c>
@@ -4613,10 +4607,10 @@
     </row>
     <row r="54" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
-      <c r="B54" s="116" t="s">
+      <c r="B54" s="122" t="s">
         <v>161</v>
       </c>
-      <c r="C54" s="116"/>
+      <c r="C54" s="122"/>
       <c r="D54" s="94">
         <v>48</v>
       </c>
@@ -4638,11 +4632,30 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B18:C18"/>
@@ -4659,30 +4672,11 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
@@ -4708,205 +4702,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="100"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="128" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="122"/>
-      <c r="C9" s="122"/>
-      <c r="D9" s="122"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="119"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
+      <c r="A10" s="127"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="119"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
+      <c r="A11" s="127"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="119"/>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
+      <c r="A12" s="127"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="120"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="120"/>
+      <c r="A13" s="129"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="129"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="120"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
+      <c r="A14" s="129"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="120"/>
-      <c r="B15" s="120"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
+      <c r="A15" s="129"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="129"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="120"/>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
+      <c r="A16" s="129"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="129"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="120"/>
-      <c r="B17" s="120"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
+      <c r="A17" s="129"/>
+      <c r="B17" s="129"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="119"/>
-      <c r="B18" s="119"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
+      <c r="A18" s="127"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="119"/>
-      <c r="B19" s="119"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
+      <c r="A19" s="127"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="127"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="119"/>
-      <c r="B20" s="119"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="119"/>
+      <c r="A20" s="127"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="127"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="119"/>
-      <c r="B21" s="119"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
+      <c r="A21" s="127"/>
+      <c r="B21" s="127"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="127"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
+      <c r="A22" s="127"/>
+      <c r="B22" s="127"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="127"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="119"/>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
+      <c r="A23" s="127"/>
+      <c r="B23" s="127"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="127"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="119"/>
-      <c r="B24" s="119"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
+      <c r="A24" s="127"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="127"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="119"/>
-      <c r="B25" s="119"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
+      <c r="A25" s="127"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="119"/>
-      <c r="B26" s="119"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
+      <c r="A26" s="127"/>
+      <c r="B26" s="127"/>
+      <c r="C26" s="127"/>
+      <c r="D26" s="127"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="119"/>
-      <c r="B27" s="119"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
+      <c r="A27" s="127"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="127"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="119"/>
-      <c r="B28" s="119"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
+      <c r="A28" s="127"/>
+      <c r="B28" s="127"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="127"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="118"/>
-      <c r="B29" s="118"/>
-      <c r="C29" s="118"/>
-      <c r="D29" s="118"/>
+      <c r="A29" s="130"/>
+      <c r="B29" s="130"/>
+      <c r="C29" s="130"/>
+      <c r="D29" s="130"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="75" t="s">
@@ -5524,6 +5518,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5539,18 +5545,6 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5580,77 +5574,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="100"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -5667,7 +5661,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="30" t="s">
         <v>201</v>
       </c>
       <c r="B10" s="38" t="s">
@@ -5679,7 +5673,7 @@
       <c r="D10" s="93"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="140" t="s">
+      <c r="A11" s="30" t="s">
         <v>202</v>
       </c>
       <c r="B11" s="38" t="s">
@@ -5691,7 +5685,7 @@
       <c r="D11" s="93"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="140" t="s">
+      <c r="A12" s="30" t="s">
         <v>203</v>
       </c>
       <c r="B12" s="38" t="s">
@@ -5703,7 +5697,7 @@
       <c r="D12" s="24"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="140" t="s">
+      <c r="A13" s="30" t="s">
         <v>204</v>
       </c>
       <c r="B13" s="38" t="s">
@@ -5715,7 +5709,7 @@
       <c r="D13" s="24"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="30" t="s">
         <v>206</v>
       </c>
       <c r="B14" s="38" t="s">
@@ -5758,7 +5752,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="140" t="s">
+      <c r="A18" s="30" t="s">
         <v>207</v>
       </c>
       <c r="B18" s="38" t="s">
@@ -5770,7 +5764,7 @@
       <c r="D18" s="24"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="140" t="s">
+      <c r="A19" s="30" t="s">
         <v>208</v>
       </c>
       <c r="B19" s="38" t="s">
@@ -5782,7 +5776,7 @@
       <c r="D19" s="24"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="140" t="s">
+      <c r="A20" s="30" t="s">
         <v>209</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -5794,7 +5788,7 @@
       <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="140" t="s">
+      <c r="A21" s="30" t="s">
         <v>210</v>
       </c>
       <c r="B21" s="38" t="s">
@@ -5806,7 +5800,7 @@
       <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="140" t="s">
+      <c r="A22" s="30" t="s">
         <v>211</v>
       </c>
       <c r="B22" s="38" t="s">
@@ -5818,7 +5812,7 @@
       <c r="D22" s="24"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="140" t="s">
+      <c r="A23" s="30" t="s">
         <v>212</v>
       </c>
       <c r="B23" s="38" t="s">
@@ -5830,7 +5824,7 @@
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="140" t="s">
+      <c r="A24" s="30" t="s">
         <v>213</v>
       </c>
       <c r="B24" s="38" t="s">
@@ -5842,7 +5836,7 @@
       <c r="D24" s="24"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="140" t="s">
+      <c r="A25" s="30" t="s">
         <v>214</v>
       </c>
       <c r="B25" s="38" t="s">
@@ -5854,7 +5848,7 @@
       <c r="D25" s="24"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="140" t="s">
+      <c r="A26" s="30" t="s">
         <v>215</v>
       </c>
       <c r="B26" s="38" t="s">
@@ -5866,7 +5860,7 @@
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="140" t="s">
+      <c r="A27" s="30" t="s">
         <v>216</v>
       </c>
       <c r="B27" s="38" t="s">
@@ -5878,7 +5872,7 @@
       <c r="D27" s="24"/>
     </row>
     <row r="28" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="140" t="s">
+      <c r="A28" s="30" t="s">
         <v>217</v>
       </c>
       <c r="B28" s="38" t="s">
@@ -5890,7 +5884,7 @@
       <c r="D28" s="24"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="140" t="s">
+      <c r="A29" s="30" t="s">
         <v>218</v>
       </c>
       <c r="B29" s="38" t="s">
@@ -5902,7 +5896,7 @@
       <c r="D29" s="24"/>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="140" t="s">
+      <c r="A30" s="30" t="s">
         <v>219</v>
       </c>
       <c r="B30" s="38" t="s">
@@ -5914,7 +5908,7 @@
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="140" t="s">
+      <c r="A31" s="30" t="s">
         <v>275</v>
       </c>
       <c r="B31" s="30" t="s">
@@ -5975,140 +5969,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
     </row>
     <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="127" t="str">
+      <c r="B2" s="135" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="127" t="str">
+      <c r="B3" s="135" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="128">
+      <c r="B4" s="136">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="128">
+      <c r="B5" s="136">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="129" t="s">
+      <c r="A6" s="137" t="s">
         <v>269</v>
       </c>
-      <c r="B6" s="129"/>
-      <c r="C6" s="129"/>
-      <c r="D6" s="129"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="129"/>
-      <c r="K6" s="129"/>
-      <c r="L6" s="129"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="137"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="137"/>
+      <c r="K6" s="137"/>
+      <c r="L6" s="137"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="129"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="129"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="129"/>
+      <c r="A7" s="137"/>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="137"/>
+      <c r="H7" s="137"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="129"/>
-      <c r="B8" s="129"/>
-      <c r="C8" s="129"/>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="129"/>
-      <c r="H8" s="129"/>
-      <c r="I8" s="129"/>
-      <c r="J8" s="129"/>
-      <c r="K8" s="129"/>
-      <c r="L8" s="129"/>
+      <c r="A8" s="137"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="137"/>
+      <c r="K8" s="137"/>
+      <c r="L8" s="137"/>
     </row>
     <row r="9" spans="1:12" s="86" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79" t="s">
@@ -6120,74 +6114,74 @@
       <c r="C9" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="D9" s="126" t="s">
+      <c r="D9" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="137"/>
+      <c r="A10" s="104"/>
       <c r="B10" s="30" t="s">
         <v>222</v>
       </c>
       <c r="C10" s="80">
         <v>0</v>
       </c>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="125"/>
-      <c r="K10" s="125"/>
-      <c r="L10" s="125"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
+      <c r="L10" s="132"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="137"/>
+      <c r="A11" s="104"/>
       <c r="B11" s="30" t="s">
         <v>223</v>
       </c>
       <c r="C11" s="80">
         <v>0</v>
       </c>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="125"/>
-      <c r="K11" s="125"/>
-      <c r="L11" s="125"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
+      <c r="L11" s="132"/>
     </row>
     <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="137"/>
+      <c r="A12" s="104"/>
       <c r="B12" s="30" t="s">
         <v>224</v>
       </c>
       <c r="C12" s="80">
         <v>0</v>
       </c>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="125"/>
-      <c r="L12" s="125"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="132"/>
     </row>
     <row r="13" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="135">
+      <c r="A13" s="102">
         <v>43</v>
       </c>
       <c r="B13" s="55" t="s">
@@ -6231,68 +6225,68 @@
       <c r="C15" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="D15" s="126" t="s">
+      <c r="D15" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
-      <c r="K15" s="126"/>
-      <c r="L15" s="126"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="136"/>
+      <c r="A16" s="103"/>
       <c r="B16" s="26"/>
       <c r="C16" s="92">
         <v>0</v>
       </c>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="124"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="138"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="136"/>
+      <c r="A17" s="103"/>
       <c r="B17" s="26"/>
       <c r="C17" s="92">
         <v>0</v>
       </c>
-      <c r="D17" s="124"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="124"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="138"/>
+      <c r="L17" s="138"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="136"/>
+      <c r="A18" s="103"/>
       <c r="B18" s="26"/>
       <c r="C18" s="92">
         <v>0</v>
       </c>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="124"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="138"/>
+      <c r="L18" s="138"/>
     </row>
     <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="138">
+      <c r="A19" s="78">
         <v>48</v>
       </c>
       <c r="B19" s="55" t="s">
@@ -6313,7 +6307,7 @@
       <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="136"/>
+      <c r="A20" s="103"/>
       <c r="B20" s="46"/>
       <c r="C20" s="81"/>
       <c r="D20" s="78"/>
@@ -6336,68 +6330,68 @@
       <c r="C21" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="D21" s="126" t="s">
+      <c r="D21" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="126"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="126"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="134"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="30"/>
       <c r="C22" s="83">
         <v>0</v>
       </c>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="125"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="132"/>
+      <c r="J22" s="132"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="134"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="30"/>
       <c r="C23" s="83">
         <v>0</v>
       </c>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="125"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="132"/>
+      <c r="J23" s="132"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="132"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="134"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="30"/>
       <c r="C24" s="83">
         <v>0</v>
       </c>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="125"/>
-      <c r="L24" s="125"/>
+      <c r="D24" s="132"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="132"/>
+      <c r="I24" s="132"/>
+      <c r="J24" s="132"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="132"/>
     </row>
     <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="138">
+      <c r="A25" s="78">
         <v>44</v>
       </c>
       <c r="B25" s="55" t="s">
@@ -6418,7 +6412,7 @@
       <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="134"/>
+      <c r="A26" s="101"/>
       <c r="B26" s="46"/>
       <c r="C26" s="81"/>
       <c r="D26" s="78"/>
@@ -6441,68 +6435,68 @@
       <c r="C27" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="D27" s="126" t="s">
+      <c r="D27" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="126"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="126"/>
-      <c r="K27" s="126"/>
-      <c r="L27" s="126"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="134"/>
+      <c r="A28" s="101"/>
       <c r="B28" s="30"/>
       <c r="C28" s="83">
         <v>0</v>
       </c>
-      <c r="D28" s="125"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="125"/>
-      <c r="G28" s="125"/>
-      <c r="H28" s="125"/>
-      <c r="I28" s="125"/>
-      <c r="J28" s="125"/>
-      <c r="K28" s="125"/>
-      <c r="L28" s="125"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="132"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="132"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="134"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="30"/>
       <c r="C29" s="83">
         <v>0</v>
       </c>
-      <c r="D29" s="125"/>
-      <c r="E29" s="125"/>
-      <c r="F29" s="125"/>
-      <c r="G29" s="125"/>
-      <c r="H29" s="125"/>
-      <c r="I29" s="125"/>
-      <c r="J29" s="125"/>
-      <c r="K29" s="125"/>
-      <c r="L29" s="125"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="132"/>
+      <c r="J29" s="132"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="132"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="134"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="30"/>
       <c r="C30" s="83">
         <v>0</v>
       </c>
-      <c r="D30" s="125"/>
-      <c r="E30" s="125"/>
-      <c r="F30" s="125"/>
-      <c r="G30" s="125"/>
-      <c r="H30" s="125"/>
-      <c r="I30" s="125"/>
-      <c r="J30" s="125"/>
-      <c r="K30" s="125"/>
-      <c r="L30" s="125"/>
+      <c r="D30" s="132"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="132"/>
+      <c r="H30" s="132"/>
+      <c r="I30" s="132"/>
+      <c r="J30" s="132"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="132"/>
     </row>
     <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="138">
+      <c r="A31" s="78">
         <v>45</v>
       </c>
       <c r="B31" s="55" t="s">
@@ -6523,7 +6517,7 @@
       <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="134"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="46"/>
       <c r="C32" s="81"/>
       <c r="D32" s="78"/>
@@ -6546,68 +6540,68 @@
       <c r="C33" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="D33" s="126" t="s">
+      <c r="D33" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="126"/>
-      <c r="F33" s="126"/>
-      <c r="G33" s="126"/>
-      <c r="H33" s="126"/>
-      <c r="I33" s="126"/>
-      <c r="J33" s="126"/>
-      <c r="K33" s="126"/>
-      <c r="L33" s="126"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="133"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="133"/>
+      <c r="I33" s="133"/>
+      <c r="J33" s="133"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="134"/>
+      <c r="A34" s="101"/>
       <c r="B34" s="30"/>
       <c r="C34" s="83">
         <v>0</v>
       </c>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="125"/>
-      <c r="H34" s="125"/>
-      <c r="I34" s="125"/>
-      <c r="J34" s="125"/>
-      <c r="K34" s="125"/>
-      <c r="L34" s="125"/>
+      <c r="D34" s="132"/>
+      <c r="E34" s="132"/>
+      <c r="F34" s="132"/>
+      <c r="G34" s="132"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="132"/>
+      <c r="J34" s="132"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="132"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="134"/>
+      <c r="A35" s="101"/>
       <c r="B35" s="30"/>
       <c r="C35" s="83">
         <v>0</v>
       </c>
-      <c r="D35" s="125"/>
-      <c r="E35" s="125"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="H35" s="125"/>
-      <c r="I35" s="125"/>
-      <c r="J35" s="125"/>
-      <c r="K35" s="125"/>
-      <c r="L35" s="125"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="132"/>
+      <c r="H35" s="132"/>
+      <c r="I35" s="132"/>
+      <c r="J35" s="132"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="132"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="134"/>
+      <c r="A36" s="101"/>
       <c r="B36" s="30"/>
       <c r="C36" s="83">
         <v>0</v>
       </c>
-      <c r="D36" s="125"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="125"/>
-      <c r="H36" s="125"/>
-      <c r="I36" s="125"/>
-      <c r="J36" s="125"/>
-      <c r="K36" s="125"/>
-      <c r="L36" s="125"/>
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="132"/>
+      <c r="G36" s="132"/>
+      <c r="H36" s="132"/>
+      <c r="I36" s="132"/>
+      <c r="J36" s="132"/>
+      <c r="K36" s="132"/>
+      <c r="L36" s="132"/>
     </row>
     <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="138">
+      <c r="A37" s="78">
         <v>46</v>
       </c>
       <c r="B37" s="55" t="s">
@@ -6628,7 +6622,7 @@
       <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="134"/>
+      <c r="A38" s="101"/>
       <c r="B38" s="46"/>
       <c r="C38" s="81"/>
       <c r="D38" s="78"/>
@@ -6651,68 +6645,68 @@
       <c r="C39" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="D39" s="126" t="s">
+      <c r="D39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="126"/>
-      <c r="F39" s="126"/>
-      <c r="G39" s="126"/>
-      <c r="H39" s="126"/>
-      <c r="I39" s="126"/>
-      <c r="J39" s="126"/>
-      <c r="K39" s="126"/>
-      <c r="L39" s="126"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="133"/>
+      <c r="K39" s="133"/>
+      <c r="L39" s="133"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="134"/>
+      <c r="A40" s="101"/>
       <c r="B40" s="30"/>
       <c r="C40" s="83">
         <v>0</v>
       </c>
-      <c r="D40" s="125"/>
-      <c r="E40" s="125"/>
-      <c r="F40" s="125"/>
-      <c r="G40" s="125"/>
-      <c r="H40" s="125"/>
-      <c r="I40" s="125"/>
-      <c r="J40" s="125"/>
-      <c r="K40" s="125"/>
-      <c r="L40" s="125"/>
+      <c r="D40" s="132"/>
+      <c r="E40" s="132"/>
+      <c r="F40" s="132"/>
+      <c r="G40" s="132"/>
+      <c r="H40" s="132"/>
+      <c r="I40" s="132"/>
+      <c r="J40" s="132"/>
+      <c r="K40" s="132"/>
+      <c r="L40" s="132"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="134"/>
+      <c r="A41" s="101"/>
       <c r="B41" s="30"/>
       <c r="C41" s="83">
         <v>0</v>
       </c>
-      <c r="D41" s="125"/>
-      <c r="E41" s="125"/>
-      <c r="F41" s="125"/>
-      <c r="G41" s="125"/>
-      <c r="H41" s="125"/>
-      <c r="I41" s="125"/>
-      <c r="J41" s="125"/>
-      <c r="K41" s="125"/>
-      <c r="L41" s="125"/>
+      <c r="D41" s="132"/>
+      <c r="E41" s="132"/>
+      <c r="F41" s="132"/>
+      <c r="G41" s="132"/>
+      <c r="H41" s="132"/>
+      <c r="I41" s="132"/>
+      <c r="J41" s="132"/>
+      <c r="K41" s="132"/>
+      <c r="L41" s="132"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="134"/>
+      <c r="A42" s="101"/>
       <c r="B42" s="30"/>
       <c r="C42" s="83">
         <v>0</v>
       </c>
-      <c r="D42" s="125"/>
-      <c r="E42" s="125"/>
-      <c r="F42" s="125"/>
-      <c r="G42" s="125"/>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="125"/>
-      <c r="L42" s="125"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="132"/>
+      <c r="F42" s="132"/>
+      <c r="G42" s="132"/>
+      <c r="H42" s="132"/>
+      <c r="I42" s="132"/>
+      <c r="J42" s="132"/>
+      <c r="K42" s="132"/>
+      <c r="L42" s="132"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="138">
+      <c r="A43" s="78">
         <v>47</v>
       </c>
       <c r="B43" s="55" t="s">
@@ -6733,7 +6727,7 @@
       <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="134"/>
+      <c r="A44" s="101"/>
       <c r="B44" s="46"/>
       <c r="C44" s="81"/>
       <c r="D44" s="78"/>
@@ -6756,68 +6750,68 @@
       <c r="C45" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="D45" s="126" t="s">
+      <c r="D45" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="126"/>
-      <c r="F45" s="126"/>
-      <c r="G45" s="126"/>
-      <c r="H45" s="126"/>
-      <c r="I45" s="126"/>
-      <c r="J45" s="126"/>
-      <c r="K45" s="126"/>
-      <c r="L45" s="126"/>
+      <c r="E45" s="133"/>
+      <c r="F45" s="133"/>
+      <c r="G45" s="133"/>
+      <c r="H45" s="133"/>
+      <c r="I45" s="133"/>
+      <c r="J45" s="133"/>
+      <c r="K45" s="133"/>
+      <c r="L45" s="133"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="134"/>
+      <c r="A46" s="101"/>
       <c r="B46" s="30"/>
       <c r="C46" s="83">
         <v>0</v>
       </c>
-      <c r="D46" s="125"/>
-      <c r="E46" s="125"/>
-      <c r="F46" s="125"/>
-      <c r="G46" s="125"/>
-      <c r="H46" s="125"/>
-      <c r="I46" s="125"/>
-      <c r="J46" s="125"/>
-      <c r="K46" s="125"/>
-      <c r="L46" s="125"/>
+      <c r="D46" s="132"/>
+      <c r="E46" s="132"/>
+      <c r="F46" s="132"/>
+      <c r="G46" s="132"/>
+      <c r="H46" s="132"/>
+      <c r="I46" s="132"/>
+      <c r="J46" s="132"/>
+      <c r="K46" s="132"/>
+      <c r="L46" s="132"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="134"/>
+      <c r="A47" s="101"/>
       <c r="B47" s="30"/>
       <c r="C47" s="83">
         <v>0</v>
       </c>
-      <c r="D47" s="125"/>
-      <c r="E47" s="125"/>
-      <c r="F47" s="125"/>
-      <c r="G47" s="125"/>
-      <c r="H47" s="125"/>
-      <c r="I47" s="125"/>
-      <c r="J47" s="125"/>
-      <c r="K47" s="125"/>
-      <c r="L47" s="125"/>
+      <c r="D47" s="132"/>
+      <c r="E47" s="132"/>
+      <c r="F47" s="132"/>
+      <c r="G47" s="132"/>
+      <c r="H47" s="132"/>
+      <c r="I47" s="132"/>
+      <c r="J47" s="132"/>
+      <c r="K47" s="132"/>
+      <c r="L47" s="132"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="134"/>
+      <c r="A48" s="101"/>
       <c r="B48" s="30"/>
       <c r="C48" s="83">
         <v>0</v>
       </c>
-      <c r="D48" s="125"/>
-      <c r="E48" s="125"/>
-      <c r="F48" s="125"/>
-      <c r="G48" s="125"/>
-      <c r="H48" s="125"/>
-      <c r="I48" s="125"/>
-      <c r="J48" s="125"/>
-      <c r="K48" s="125"/>
-      <c r="L48" s="125"/>
+      <c r="D48" s="132"/>
+      <c r="E48" s="132"/>
+      <c r="F48" s="132"/>
+      <c r="G48" s="132"/>
+      <c r="H48" s="132"/>
+      <c r="I48" s="132"/>
+      <c r="J48" s="132"/>
+      <c r="K48" s="132"/>
+      <c r="L48" s="132"/>
     </row>
     <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="139">
+      <c r="A49" s="99">
         <v>48</v>
       </c>
       <c r="B49" s="55" t="s">
@@ -6827,27 +6821,28 @@
         <f>SUM(C46:C48)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="130"/>
-      <c r="E49" s="130"/>
-      <c r="F49" s="130"/>
-      <c r="G49" s="130"/>
-      <c r="H49" s="130"/>
-      <c r="I49" s="130"/>
-      <c r="J49" s="130"/>
-      <c r="K49" s="130"/>
-      <c r="L49" s="130"/>
+      <c r="D49" s="134"/>
+      <c r="E49" s="134"/>
+      <c r="F49" s="134"/>
+      <c r="G49" s="134"/>
+      <c r="H49" s="134"/>
+      <c r="I49" s="134"/>
+      <c r="J49" s="134"/>
+      <c r="K49" s="134"/>
+      <c r="L49" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="D48:L48"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D40:L40"/>
-    <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D17:L17"/>
+    <mergeCell ref="D18:L18"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="A6:L8"/>
     <mergeCell ref="D49:L49"/>
     <mergeCell ref="D10:L10"/>
     <mergeCell ref="D11:L11"/>
@@ -6861,19 +6856,18 @@
     <mergeCell ref="D21:L21"/>
     <mergeCell ref="D27:L27"/>
     <mergeCell ref="D33:L33"/>
-    <mergeCell ref="D9:L9"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A6:L8"/>
     <mergeCell ref="D16:L16"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="D34:L34"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D17:L17"/>
-    <mergeCell ref="D18:L18"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="D46:L46"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D40:L40"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="D39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>

--- a/noprofit/en/11255/inpag-template.xlsx
+++ b/noprofit/en/11255/inpag-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8CE32C-3852-46A9-9168-4BB40A256DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AA2347-B537-41CE-9C14-1687A0C969D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" firstSheet="1" activeTab="4" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
   <sheets>
     <sheet name="General information" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Notes of cash flow statement" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash flow statement - indirect'!$A$1:$E$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash flow statement - indirect'!$A$1:$E$56</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'General information'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Notes of cash flow statement'!$A$1:$L$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Notes of financial statement'!$A$1:$D$82</definedName>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="297">
   <si>
     <t>Company name and legal form</t>
   </si>
@@ -504,12 +504,6 @@
     <t>Net increase (decrease) in cash and cash equivalents before effect of exchange rate changes</t>
   </si>
   <si>
-    <t>EXRE</t>
-  </si>
-  <si>
-    <t>[+] Effect of exchange rate changes on cash and cash equivalents</t>
-  </si>
-  <si>
     <t>Net increase (decrease) in cash and cash equivalents</t>
   </si>
   <si>
@@ -780,9 +774,6 @@
     <t>IE</t>
   </si>
   <si>
-    <t>OI</t>
-  </si>
-  <si>
     <t>SSA</t>
   </si>
   <si>
@@ -792,42 +783,6 @@
     <t>UGLFED</t>
   </si>
   <si>
-    <t>DBP</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>GDNA</t>
-  </si>
-  <si>
-    <t>SSG</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>EXP1</t>
-  </si>
-  <si>
-    <t>EXP2</t>
-  </si>
-  <si>
-    <t>EXP3</t>
-  </si>
-  <si>
-    <t>OE</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>GDGP</t>
-  </si>
-  <si>
     <t>Bank</t>
   </si>
   <si>
@@ -883,6 +838,111 @@
   </si>
   <si>
     <t>2.1</t>
+  </si>
+  <si>
+    <t>Capital grant</t>
+  </si>
+  <si>
+    <t>[-] Donations of property, plant and equipment (PPE)</t>
+  </si>
+  <si>
+    <t>DPPE</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>IDWIP</t>
+  </si>
+  <si>
+    <t>IDOCA</t>
+  </si>
+  <si>
+    <t>IDOCL</t>
+  </si>
+  <si>
+    <t>IDOC</t>
+  </si>
+  <si>
+    <t>IDA</t>
+  </si>
+  <si>
+    <t>Increase/decrease in inventories</t>
+  </si>
+  <si>
+    <t>Increase/decrease in WIP</t>
+  </si>
+  <si>
+    <t>Increase/decrease in other current assets</t>
+  </si>
+  <si>
+    <t>Increase/decrease in other current liabilities</t>
+  </si>
+  <si>
+    <t>Increase/decrease in operational creditors</t>
+  </si>
+  <si>
+    <t>Increase/decrease in accruals</t>
+  </si>
+  <si>
+    <t>Acquisition of PPE</t>
+  </si>
+  <si>
+    <t>Acquisition of intangible assets</t>
+  </si>
+  <si>
+    <t>Receipt of grants for PPE</t>
+  </si>
+  <si>
+    <t>Disposals</t>
+  </si>
+  <si>
+    <t>APPE</t>
+  </si>
+  <si>
+    <t>AIA</t>
+  </si>
+  <si>
+    <t>RGPPE</t>
+  </si>
+  <si>
+    <t>DISP</t>
+  </si>
+  <si>
+    <t>Repayment of borrowings</t>
+  </si>
+  <si>
+    <t>Member shares redeemed</t>
+  </si>
+  <si>
+    <t>Member shares issued</t>
+  </si>
+  <si>
+    <t>RBOR</t>
+  </si>
+  <si>
+    <t>MSR</t>
+  </si>
+  <si>
+    <t>MSI</t>
+  </si>
+  <si>
+    <t>Opening cash and cash equivalents</t>
+  </si>
+  <si>
+    <t>Movement if cash and cash equivalents</t>
+  </si>
+  <si>
+    <t>Foreign exchange differences</t>
+  </si>
+  <si>
+    <t>FED</t>
+  </si>
+  <si>
+    <t>MCCE</t>
+  </si>
+  <si>
+    <t>OCCE</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1140,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1432,9 +1492,6 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1462,6 +1519,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1470,9 +1530,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1864,7 +1921,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="106" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B1" s="106"/>
       <c r="C1" s="106"/>
@@ -2292,7 +2349,7 @@
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="111" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="B6" s="111"/>
       <c r="C6" s="111"/>
@@ -2459,10 +2516,10 @@
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C19" s="94">
         <v>6</v>
@@ -3099,7 +3156,7 @@
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="111" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="B6" s="111"/>
       <c r="C6" s="111"/>
@@ -3547,7 +3604,7 @@
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="48"/>
       <c r="B35" s="89" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C35" s="89"/>
       <c r="D35" s="90">
@@ -3674,7 +3731,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="111" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B6" s="111"/>
       <c r="C6" s="111"/>
@@ -3754,7 +3811,7 @@
         <v>135</v>
       </c>
       <c r="B13" s="120" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C13" s="120"/>
       <c r="D13" s="120"/>
@@ -3813,7 +3870,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="45" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B18" s="121" t="s">
         <v>54</v>
@@ -3826,7 +3883,7 @@
     </row>
     <row r="19" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B19" s="121" t="s">
         <v>56</v>
@@ -3839,7 +3896,7 @@
     </row>
     <row r="20" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B20" s="121" t="s">
         <v>58</v>
@@ -3852,7 +3909,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B21" s="120" t="s">
         <v>61</v>
@@ -3929,7 +3986,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="2" customWidth="1"/>
@@ -4000,7 +4057,7 @@
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="111" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B6" s="111"/>
       <c r="C6" s="111"/>
@@ -4026,7 +4083,7 @@
         <v>133</v>
       </c>
       <c r="B9" s="124" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C9" s="124"/>
       <c r="D9" s="75" t="s">
@@ -4042,7 +4099,7 @@
         <v>143</v>
       </c>
       <c r="B10" s="114" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C10" s="114"/>
       <c r="D10" s="114"/>
@@ -4075,30 +4132,29 @@
     </row>
     <row r="13" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B13" s="121" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C13" s="121"/>
       <c r="D13" s="94">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E13" s="22">
         <v>0</v>
       </c>
-      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B14" s="121" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C14" s="121"/>
       <c r="D14" s="94">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" s="22">
         <v>0</v>
@@ -4106,14 +4162,14 @@
     </row>
     <row r="15" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B15" s="121" t="s">
-        <v>115</v>
+        <v>263</v>
       </c>
       <c r="C15" s="121"/>
       <c r="D15" s="94">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E15" s="22">
         <v>0</v>
@@ -4121,44 +4177,46 @@
     </row>
     <row r="16" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="45" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B16" s="121" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C16" s="121"/>
       <c r="D16" s="94">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E16" s="22">
         <v>0</v>
       </c>
+      <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45" t="s">
         <v>241</v>
       </c>
       <c r="B17" s="121" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C17" s="121"/>
       <c r="D17" s="94">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E17" s="22">
         <v>0</v>
       </c>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="B18" s="121" t="s">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="C18" s="121"/>
       <c r="D18" s="94">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E18" s="22">
         <v>0</v>
@@ -4167,14 +4225,14 @@
     </row>
     <row r="19" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="B19" s="121" t="s">
-        <v>95</v>
+        <v>271</v>
       </c>
       <c r="C19" s="121"/>
       <c r="D19" s="94">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E19" s="22">
         <v>0</v>
@@ -4183,257 +4241,255 @@
     </row>
     <row r="20" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="B20" s="121" t="s">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="C20" s="121"/>
       <c r="D20" s="94">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E20" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="B21" s="121" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="121"/>
+        <v>267</v>
+      </c>
+      <c r="B21" s="123" t="s">
+        <v>273</v>
+      </c>
+      <c r="C21" s="123"/>
       <c r="D21" s="94">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E21" s="22">
         <v>0</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="B22" s="121" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" s="121"/>
+        <v>268</v>
+      </c>
+      <c r="B22" s="123" t="s">
+        <v>274</v>
+      </c>
+      <c r="C22" s="123"/>
       <c r="D22" s="94">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E22" s="22">
         <v>0</v>
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="B23" s="121" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" s="121"/>
+        <v>269</v>
+      </c>
+      <c r="B23" s="123" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23" s="123"/>
       <c r="D23" s="94">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E23" s="22">
         <v>0</v>
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="B24" s="121" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="121"/>
+        <v>270</v>
+      </c>
+      <c r="B24" s="123" t="s">
+        <v>276</v>
+      </c>
+      <c r="C24" s="123"/>
       <c r="D24" s="94">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E24" s="22">
         <v>0</v>
       </c>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="B25" s="123" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="123"/>
-      <c r="D25" s="94">
-        <v>41</v>
-      </c>
-      <c r="E25" s="22">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="B26" s="123" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" s="123"/>
-      <c r="D26" s="94">
-        <v>42</v>
-      </c>
-      <c r="E26" s="22">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4"/>
+    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="45"/>
+      <c r="B25" s="114" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" s="114"/>
+      <c r="D25" s="114"/>
+      <c r="E25" s="63">
+        <f>E10+SUM(E13:E24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="45"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="29"/>
     </row>
     <row r="27" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="B27" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="121"/>
-      <c r="D27" s="94">
-        <v>25</v>
-      </c>
-      <c r="E27" s="22">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
-      <c r="B28" s="114" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114"/>
-      <c r="E28" s="63">
-        <f>E10+SUM(E13:E27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="29"/>
-    </row>
-    <row r="30" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="75" t="s">
+      <c r="A27" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="124" t="s">
+      <c r="B27" s="124" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="124"/>
-      <c r="D30" s="75" t="s">
+      <c r="C27" s="124"/>
+      <c r="D27" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="75">
+      <c r="E27" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
     </row>
+    <row r="28" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="B28" s="123" t="s">
+        <v>277</v>
+      </c>
+      <c r="C28" s="123"/>
+      <c r="D28" s="94">
+        <v>51</v>
+      </c>
+      <c r="E28" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="B29" s="123" t="s">
+        <v>278</v>
+      </c>
+      <c r="C29" s="123"/>
+      <c r="D29" s="94">
+        <v>52</v>
+      </c>
+      <c r="E29" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="45" t="s">
+        <v>283</v>
+      </c>
+      <c r="B30" s="123" t="s">
+        <v>279</v>
+      </c>
+      <c r="C30" s="123"/>
+      <c r="D30" s="94">
+        <v>53</v>
+      </c>
+      <c r="E30" s="22">
+        <v>0</v>
+      </c>
+    </row>
     <row r="31" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="45" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="B31" s="123" t="s">
-        <v>99</v>
+        <v>280</v>
       </c>
       <c r="C31" s="123"/>
       <c r="D31" s="94">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="E31" s="22">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="B32" s="123" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="123"/>
-      <c r="D32" s="94">
-        <v>30</v>
-      </c>
-      <c r="E32" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="B33" s="123" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="123"/>
-      <c r="D33" s="94">
-        <v>31</v>
-      </c>
-      <c r="E33" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="45"/>
-      <c r="B34" s="114" t="s">
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="45"/>
+      <c r="B32" s="114" t="s">
         <v>146</v>
       </c>
-      <c r="C34" s="114"/>
-      <c r="D34" s="114"/>
-      <c r="E34" s="63">
-        <f>E10+E28+SUM(E31:E33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="45"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="69"/>
-    </row>
-    <row r="36" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="75" t="s">
+      <c r="C32" s="114"/>
+      <c r="D32" s="114"/>
+      <c r="E32" s="63">
+        <f>E10+E25+SUM(E28:E31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="45"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="69"/>
+    </row>
+    <row r="34" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B36" s="124" t="s">
+      <c r="B34" s="124" t="s">
         <v>147</v>
       </c>
-      <c r="C36" s="124"/>
-      <c r="D36" s="75" t="s">
+      <c r="C34" s="124"/>
+      <c r="D34" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E34" s="75">
         <f>$B$5</f>
         <v>45657</v>
       </c>
-      <c r="F36" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="45" t="s">
+        <v>288</v>
+      </c>
+      <c r="B35" s="123" t="s">
+        <v>285</v>
+      </c>
+      <c r="C35" s="123"/>
+      <c r="D35" s="94">
+        <v>55</v>
+      </c>
+      <c r="E35" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="45" t="s">
+        <v>289</v>
+      </c>
+      <c r="B36" s="123" t="s">
+        <v>286</v>
+      </c>
+      <c r="C36" s="123"/>
+      <c r="D36" s="94">
+        <v>56</v>
+      </c>
+      <c r="E36" s="22">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="B37" s="123" t="s">
-        <v>89</v>
+        <v>287</v>
       </c>
       <c r="C37" s="123"/>
       <c r="D37" s="94">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E37" s="22">
         <v>0</v>
@@ -4447,7 +4503,7 @@
       <c r="C38" s="114"/>
       <c r="D38" s="114"/>
       <c r="E38" s="63">
-        <f>E10+E28+E34+SUM(E37:E37)</f>
+        <f>E10+E25+E32+SUM(E35:E35)</f>
         <v>0</v>
       </c>
     </row>
@@ -4466,217 +4522,247 @@
       <c r="C40" s="114"/>
       <c r="D40" s="114"/>
       <c r="E40" s="63">
-        <f>SUM(E28,E34,E38)</f>
+        <f>SUM(E25,E32,E38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="69"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="63"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="B42" s="125" t="s">
-        <v>151</v>
-      </c>
-      <c r="C42" s="125"/>
-      <c r="D42" s="125"/>
-      <c r="E42" s="22"/>
+        <v>296</v>
+      </c>
+      <c r="B42" s="122" t="s">
+        <v>291</v>
+      </c>
+      <c r="C42" s="122"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="22">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="45"/>
-      <c r="B43" s="114" t="s">
-        <v>152</v>
-      </c>
-      <c r="C43" s="114"/>
-      <c r="D43" s="97">
-        <v>43</v>
-      </c>
-      <c r="E43" s="70">
-        <f>E40+E42</f>
+      <c r="A43" s="45" t="s">
+        <v>295</v>
+      </c>
+      <c r="B43" s="122" t="s">
+        <v>292</v>
+      </c>
+      <c r="C43" s="122"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="45"/>
-      <c r="B44" s="114" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="114"/>
-      <c r="D44" s="114"/>
-      <c r="E44" s="70">
-        <f>'Statement of financial position'!D22</f>
+      <c r="A44" s="45" t="s">
+        <v>294</v>
+      </c>
+      <c r="B44" s="122" t="s">
+        <v>293</v>
+      </c>
+      <c r="C44" s="122"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="45"/>
       <c r="B45" s="114" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C45" s="114"/>
-      <c r="D45" s="114"/>
+      <c r="D45" s="97">
+        <v>58</v>
+      </c>
       <c r="E45" s="70">
-        <f>'Statement of financial position'!E22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
+        <f>E40+E42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="45"/>
       <c r="B46" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C46" s="114"/>
       <c r="D46" s="114"/>
       <c r="E46" s="70">
-        <f>E45-E44</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A47" s="31"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
+        <f>'Statement of financial position'!D22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="45"/>
+      <c r="B47" s="114" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" s="114"/>
+      <c r="D47" s="114"/>
+      <c r="E47" s="70">
+        <f>'Statement of financial position'!E22</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A48" s="31"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
+      <c r="A48" s="45"/>
+      <c r="B48" s="114" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" s="114"/>
+      <c r="D48" s="114"/>
+      <c r="E48" s="70">
+        <f>E47-E46</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A49" s="31"/>
-      <c r="B49" s="58" t="s">
-        <v>156</v>
-      </c>
+      <c r="B49" s="31"/>
       <c r="C49" s="31"/>
       <c r="D49" s="31"/>
       <c r="E49" s="31"/>
     </row>
     <row r="50" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A50" s="31"/>
-      <c r="B50" s="122" t="s">
-        <v>157</v>
-      </c>
-      <c r="C50" s="122"/>
-      <c r="D50" s="94">
-        <v>44</v>
-      </c>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
       <c r="E50" s="31"/>
     </row>
     <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A51" s="31"/>
-      <c r="B51" s="122" t="s">
-        <v>158</v>
-      </c>
-      <c r="C51" s="122"/>
-      <c r="D51" s="94">
-        <v>45</v>
-      </c>
+      <c r="B51" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
       <c r="E51" s="31"/>
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="31"/>
       <c r="B52" s="122" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C52" s="122"/>
       <c r="D52" s="94">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E52" s="31"/>
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
       <c r="B53" s="122" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C53" s="122"/>
       <c r="D53" s="94">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E53" s="31"/>
     </row>
-    <row r="54" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
       <c r="B54" s="122" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C54" s="122"/>
       <c r="D54" s="94">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E54" s="31"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="25"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="25"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
+    <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A55" s="31"/>
+      <c r="B55" s="122" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="122"/>
+      <c r="D55" s="94">
+        <v>62</v>
+      </c>
+      <c r="E55" s="31"/>
+    </row>
+    <row r="56" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="31"/>
+      <c r="B56" s="122" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="122"/>
+      <c r="D56" s="94">
+        <v>63</v>
+      </c>
+      <c r="E56" s="31"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="25"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="25"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B17:C17"/>
+  <mergeCells count="47">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
@@ -4702,12 +4788,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -4775,142 +4861,142 @@
       <c r="D8" s="111"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="128" t="s">
-        <v>162</v>
-      </c>
-      <c r="B9" s="128"/>
-      <c r="C9" s="128"/>
-      <c r="D9" s="128"/>
+      <c r="A9" s="127" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="127"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="127"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
+      <c r="A11" s="126"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="126"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="127"/>
-      <c r="B12" s="127"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127"/>
+      <c r="A12" s="126"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="129"/>
-      <c r="B13" s="129"/>
-      <c r="C13" s="129"/>
-      <c r="D13" s="129"/>
+      <c r="A13" s="128"/>
+      <c r="B13" s="128"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="128"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="129"/>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
+      <c r="A14" s="128"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="129"/>
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
+      <c r="A15" s="128"/>
+      <c r="B15" s="128"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="128"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="129"/>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
+      <c r="A16" s="128"/>
+      <c r="B16" s="128"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="129"/>
-      <c r="B17" s="129"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
+      <c r="A17" s="128"/>
+      <c r="B17" s="128"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="128"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="127"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="127"/>
-      <c r="D18" s="127"/>
+      <c r="A18" s="126"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="127"/>
-      <c r="B19" s="127"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="127"/>
+      <c r="A19" s="126"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="127"/>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="127"/>
+      <c r="A20" s="126"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="127"/>
-      <c r="B21" s="127"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="127"/>
+      <c r="A21" s="126"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="127"/>
-      <c r="B22" s="127"/>
-      <c r="C22" s="127"/>
-      <c r="D22" s="127"/>
+      <c r="A22" s="126"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="127"/>
-      <c r="B23" s="127"/>
-      <c r="C23" s="127"/>
-      <c r="D23" s="127"/>
+      <c r="A23" s="126"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="126"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="127"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
+      <c r="A24" s="126"/>
+      <c r="B24" s="126"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="126"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="127"/>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="127"/>
+      <c r="A25" s="126"/>
+      <c r="B25" s="126"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="126"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="127"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="127"/>
-      <c r="D26" s="127"/>
+      <c r="A26" s="126"/>
+      <c r="B26" s="126"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="126"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="127"/>
-      <c r="B27" s="127"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="127"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="126"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="127"/>
-      <c r="B28" s="127"/>
-      <c r="C28" s="127"/>
-      <c r="D28" s="127"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="126"/>
+      <c r="C28" s="126"/>
+      <c r="D28" s="126"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="130"/>
-      <c r="B29" s="130"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="130"/>
+      <c r="A29" s="129"/>
+      <c r="B29" s="129"/>
+      <c r="C29" s="129"/>
+      <c r="D29" s="129"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>163</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>165</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>34</v>
@@ -4940,10 +5026,10 @@
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C33" s="22">
         <v>0</v>
@@ -4955,7 +5041,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C34" s="22">
         <v>0</v>
@@ -4967,7 +5053,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C35" s="23">
         <v>0</v>
@@ -4979,7 +5065,7 @@
         <v>2.4</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C36" s="22">
         <v>0</v>
@@ -4991,7 +5077,7 @@
         <v>2.5</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C37" s="22">
         <v>0</v>
@@ -5003,7 +5089,7 @@
         <v>2.6</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C38" s="22">
         <v>0</v>
@@ -5015,7 +5101,7 @@
         <v>2.7</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C39" s="22">
         <v>0</v>
@@ -5027,7 +5113,7 @@
         <v>2.8</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C40" s="22">
         <v>0</v>
@@ -5039,7 +5125,7 @@
         <v>2.9</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C41" s="22">
         <v>0</v>
@@ -5048,10 +5134,10 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C42" s="22">
         <v>0</v>
@@ -5060,10 +5146,10 @@
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C43" s="22">
         <v>0</v>
@@ -5072,10 +5158,10 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C44" s="22">
         <v>0</v>
@@ -5084,10 +5170,10 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="33" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C45" s="22">
         <v>0</v>
@@ -5096,10 +5182,10 @@
     </row>
     <row r="46" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C46" s="22">
         <v>0</v>
@@ -5108,10 +5194,10 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C47" s="22">
         <v>0</v>
@@ -5121,7 +5207,7 @@
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33"/>
       <c r="B48" s="46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C48" s="63">
         <f>SUM(C33:C47)</f>
@@ -5134,7 +5220,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C49" s="23">
         <v>0</v>
@@ -5172,13 +5258,13 @@
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" s="21" t="s">
         <v>163</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>165</v>
       </c>
       <c r="D53" s="21" t="s">
         <v>34</v>
@@ -5198,10 +5284,10 @@
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="40" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C55" s="23">
         <v>0</v>
@@ -5210,7 +5296,7 @@
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="40" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="B56" s="45" t="s">
         <v>47</v>
@@ -5222,7 +5308,7 @@
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="42" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B57" s="45" t="s">
         <v>48</v>
@@ -5251,13 +5337,13 @@
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C60" s="21" t="s">
         <v>163</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="C60" s="21" t="s">
-        <v>165</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>34</v>
@@ -5265,7 +5351,7 @@
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="40" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B61" s="38" t="s">
         <v>54</v>
@@ -5277,7 +5363,7 @@
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="40" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="B62" s="38" t="s">
         <v>56</v>
@@ -5289,7 +5375,7 @@
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="40" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="B63" s="38" t="s">
         <v>58</v>
@@ -5301,7 +5387,7 @@
     </row>
     <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="40" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="B64" s="38" t="s">
         <v>59</v>
@@ -5313,7 +5399,7 @@
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="40" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="B65" s="38" t="s">
         <v>61</v>
@@ -5326,7 +5412,7 @@
     <row r="66" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A66" s="32"/>
       <c r="B66" s="55" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C66" s="72">
         <f>SUM(C61:C65)</f>
@@ -5342,13 +5428,13 @@
     </row>
     <row r="68" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A68" s="75" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>34</v>
@@ -5356,7 +5442,7 @@
     </row>
     <row r="69" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A69" s="44" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="B69" s="38" t="s">
         <v>64</v>
@@ -5368,7 +5454,7 @@
     </row>
     <row r="70" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A70" s="44" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="B70" s="38" t="s">
         <v>66</v>
@@ -5380,7 +5466,7 @@
     </row>
     <row r="71" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A71" s="44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B71" s="38" t="s">
         <v>68</v>
@@ -5409,13 +5495,13 @@
     </row>
     <row r="74" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A74" s="75" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D74" s="21" t="s">
         <v>34</v>
@@ -5423,7 +5509,7 @@
     </row>
     <row r="75" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A75" s="44" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B75" s="38" t="s">
         <v>72</v>
@@ -5435,7 +5521,7 @@
     </row>
     <row r="76" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A76" s="44" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B76" s="38" t="s">
         <v>73</v>
@@ -5447,7 +5533,7 @@
     </row>
     <row r="77" spans="1:4" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A77" s="44" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>75</v>
@@ -5459,7 +5545,7 @@
     </row>
     <row r="78" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A78" s="44" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B78" s="38" t="s">
         <v>77</v>
@@ -5471,7 +5557,7 @@
     </row>
     <row r="79" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A79" s="44" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B79" s="38" t="s">
         <v>79</v>
@@ -5483,7 +5569,7 @@
     </row>
     <row r="80" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A80" s="44" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B80" s="38" t="s">
         <v>81</v>
@@ -5495,7 +5581,7 @@
     </row>
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A81" s="44" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B81" s="38" t="s">
         <v>83</v>
@@ -5574,12 +5660,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -5648,13 +5734,13 @@
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="88" t="s">
         <v>163</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9" s="88" t="s">
-        <v>165</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>34</v>
@@ -5662,7 +5748,7 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>89</v>
@@ -5674,7 +5760,7 @@
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>91</v>
@@ -5686,7 +5772,7 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>93</v>
@@ -5698,7 +5784,7 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>95</v>
@@ -5710,7 +5796,7 @@
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14" s="38" t="s">
         <v>97</v>
@@ -5723,7 +5809,7 @@
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="41"/>
       <c r="B15" s="55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C15" s="63">
         <f>SUM(C10:C14)</f>
@@ -5739,13 +5825,13 @@
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>106</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>34</v>
@@ -5753,7 +5839,7 @@
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B18" s="38" t="s">
         <v>99</v>
@@ -5765,7 +5851,7 @@
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B19" s="38" t="s">
         <v>101</v>
@@ -5777,7 +5863,7 @@
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>103</v>
@@ -5789,7 +5875,7 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>107</v>
@@ -5801,7 +5887,7 @@
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>109</v>
@@ -5813,7 +5899,7 @@
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>111</v>
@@ -5825,7 +5911,7 @@
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>113</v>
@@ -5837,7 +5923,7 @@
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B25" s="38" t="s">
         <v>115</v>
@@ -5849,7 +5935,7 @@
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>119</v>
@@ -5861,7 +5947,7 @@
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>121</v>
@@ -5873,7 +5959,7 @@
     </row>
     <row r="28" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="30" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B28" s="38" t="s">
         <v>123</v>
@@ -5885,7 +5971,7 @@
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>125</v>
@@ -5897,7 +5983,7 @@
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>127</v>
@@ -5909,7 +5995,7 @@
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="30" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>129</v>
@@ -5922,7 +6008,7 @@
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39"/>
       <c r="B32" s="73" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C32" s="74">
         <f>SUM(C18:C31)</f>
@@ -5969,20 +6055,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
     </row>
     <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
@@ -6062,7 +6148,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="137" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B6" s="137"/>
       <c r="C6" s="137"/>
@@ -6106,86 +6192,86 @@
     </row>
     <row r="9" spans="1:12" s="86" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="D9" s="133" t="s">
+      <c r="D9" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="133"/>
-      <c r="L9" s="133"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="104"/>
       <c r="B10" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C10" s="80">
         <v>0</v>
       </c>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="132"/>
-      <c r="J10" s="132"/>
-      <c r="K10" s="132"/>
-      <c r="L10" s="132"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="104"/>
       <c r="B11" s="30" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C11" s="80">
         <v>0</v>
       </c>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="132"/>
-      <c r="K11" s="132"/>
-      <c r="L11" s="132"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
     </row>
     <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="104"/>
       <c r="B12" s="30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C12" s="80">
         <v>0</v>
       </c>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="132"/>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="132"/>
-      <c r="K12" s="132"/>
-      <c r="L12" s="132"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="131"/>
     </row>
     <row r="13" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="102">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C13" s="84">
         <f>SUM(C10:C12)</f>
@@ -6217,25 +6303,25 @@
     </row>
     <row r="15" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="D15" s="133" t="s">
+      <c r="D15" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="133"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="103"/>
@@ -6243,15 +6329,15 @@
       <c r="C16" s="92">
         <v>0</v>
       </c>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="138"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="138"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="134"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="134"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="103"/>
@@ -6259,15 +6345,15 @@
       <c r="C17" s="92">
         <v>0</v>
       </c>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="138"/>
-      <c r="K17" s="138"/>
-      <c r="L17" s="138"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="134"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="134"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="103"/>
@@ -6275,22 +6361,22 @@
       <c r="C18" s="92">
         <v>0</v>
       </c>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="134"/>
     </row>
     <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="78">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C19" s="84">
         <f>SUM(C16:C18)</f>
@@ -6322,25 +6408,25 @@
     </row>
     <row r="21" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" s="133" t="s">
+      <c r="D21" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="133"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="101"/>
@@ -6348,15 +6434,15 @@
       <c r="C22" s="83">
         <v>0</v>
       </c>
-      <c r="D22" s="132"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="132"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="132"/>
-      <c r="J22" s="132"/>
-      <c r="K22" s="132"/>
-      <c r="L22" s="132"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="131"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="101"/>
@@ -6364,15 +6450,15 @@
       <c r="C23" s="83">
         <v>0</v>
       </c>
-      <c r="D23" s="132"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="132"/>
-      <c r="I23" s="132"/>
-      <c r="J23" s="132"/>
-      <c r="K23" s="132"/>
-      <c r="L23" s="132"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="131"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="131"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="101"/>
@@ -6380,22 +6466,22 @@
       <c r="C24" s="83">
         <v>0</v>
       </c>
-      <c r="D24" s="132"/>
-      <c r="E24" s="132"/>
-      <c r="F24" s="132"/>
-      <c r="G24" s="132"/>
-      <c r="H24" s="132"/>
-      <c r="I24" s="132"/>
-      <c r="J24" s="132"/>
-      <c r="K24" s="132"/>
-      <c r="L24" s="132"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
     </row>
     <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="78">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C25" s="84">
         <f>SUM(C22:C24)</f>
@@ -6427,25 +6513,25 @@
     </row>
     <row r="27" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C27" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C27" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="D27" s="133" t="s">
+      <c r="D27" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="133"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="133"/>
-      <c r="L27" s="133"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="101"/>
@@ -6453,15 +6539,15 @@
       <c r="C28" s="83">
         <v>0</v>
       </c>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="132"/>
-      <c r="I28" s="132"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="132"/>
-      <c r="L28" s="132"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="131"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="101"/>
@@ -6469,15 +6555,15 @@
       <c r="C29" s="83">
         <v>0</v>
       </c>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="132"/>
-      <c r="I29" s="132"/>
-      <c r="J29" s="132"/>
-      <c r="K29" s="132"/>
-      <c r="L29" s="132"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
+      <c r="L29" s="131"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="101"/>
@@ -6485,22 +6571,22 @@
       <c r="C30" s="83">
         <v>0</v>
       </c>
-      <c r="D30" s="132"/>
-      <c r="E30" s="132"/>
-      <c r="F30" s="132"/>
-      <c r="G30" s="132"/>
-      <c r="H30" s="132"/>
-      <c r="I30" s="132"/>
-      <c r="J30" s="132"/>
-      <c r="K30" s="132"/>
-      <c r="L30" s="132"/>
+      <c r="D30" s="131"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="131"/>
     </row>
     <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="78">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B31" s="55" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C31" s="84">
         <f>SUM(C28:C30)</f>
@@ -6532,25 +6618,25 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="82" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="B33" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="C33" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="D33" s="133" t="s">
+      <c r="D33" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="133"/>
-      <c r="H33" s="133"/>
-      <c r="I33" s="133"/>
-      <c r="J33" s="133"/>
-      <c r="K33" s="133"/>
-      <c r="L33" s="133"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132"/>
+      <c r="K33" s="132"/>
+      <c r="L33" s="132"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="101"/>
@@ -6558,15 +6644,15 @@
       <c r="C34" s="83">
         <v>0</v>
       </c>
-      <c r="D34" s="132"/>
-      <c r="E34" s="132"/>
-      <c r="F34" s="132"/>
-      <c r="G34" s="132"/>
-      <c r="H34" s="132"/>
-      <c r="I34" s="132"/>
-      <c r="J34" s="132"/>
-      <c r="K34" s="132"/>
-      <c r="L34" s="132"/>
+      <c r="D34" s="131"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
+      <c r="J34" s="131"/>
+      <c r="K34" s="131"/>
+      <c r="L34" s="131"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="101"/>
@@ -6574,15 +6660,15 @@
       <c r="C35" s="83">
         <v>0</v>
       </c>
-      <c r="D35" s="132"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="132"/>
-      <c r="G35" s="132"/>
-      <c r="H35" s="132"/>
-      <c r="I35" s="132"/>
-      <c r="J35" s="132"/>
-      <c r="K35" s="132"/>
-      <c r="L35" s="132"/>
+      <c r="D35" s="131"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="131"/>
+      <c r="H35" s="131"/>
+      <c r="I35" s="131"/>
+      <c r="J35" s="131"/>
+      <c r="K35" s="131"/>
+      <c r="L35" s="131"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="101"/>
@@ -6590,22 +6676,22 @@
       <c r="C36" s="83">
         <v>0</v>
       </c>
-      <c r="D36" s="132"/>
-      <c r="E36" s="132"/>
-      <c r="F36" s="132"/>
-      <c r="G36" s="132"/>
-      <c r="H36" s="132"/>
-      <c r="I36" s="132"/>
-      <c r="J36" s="132"/>
-      <c r="K36" s="132"/>
-      <c r="L36" s="132"/>
+      <c r="D36" s="131"/>
+      <c r="E36" s="131"/>
+      <c r="F36" s="131"/>
+      <c r="G36" s="131"/>
+      <c r="H36" s="131"/>
+      <c r="I36" s="131"/>
+      <c r="J36" s="131"/>
+      <c r="K36" s="131"/>
+      <c r="L36" s="131"/>
     </row>
     <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="78">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C37" s="84">
         <f>SUM(C34:C36)</f>
@@ -6637,25 +6723,25 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" s="82" t="s">
+        <v>158</v>
+      </c>
+      <c r="C39" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="B39" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="C39" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="D39" s="133" t="s">
+      <c r="D39" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="133"/>
-      <c r="F39" s="133"/>
-      <c r="G39" s="133"/>
-      <c r="H39" s="133"/>
-      <c r="I39" s="133"/>
-      <c r="J39" s="133"/>
-      <c r="K39" s="133"/>
-      <c r="L39" s="133"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="132"/>
+      <c r="H39" s="132"/>
+      <c r="I39" s="132"/>
+      <c r="J39" s="132"/>
+      <c r="K39" s="132"/>
+      <c r="L39" s="132"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="101"/>
@@ -6663,15 +6749,15 @@
       <c r="C40" s="83">
         <v>0</v>
       </c>
-      <c r="D40" s="132"/>
-      <c r="E40" s="132"/>
-      <c r="F40" s="132"/>
-      <c r="G40" s="132"/>
-      <c r="H40" s="132"/>
-      <c r="I40" s="132"/>
-      <c r="J40" s="132"/>
-      <c r="K40" s="132"/>
-      <c r="L40" s="132"/>
+      <c r="D40" s="131"/>
+      <c r="E40" s="131"/>
+      <c r="F40" s="131"/>
+      <c r="G40" s="131"/>
+      <c r="H40" s="131"/>
+      <c r="I40" s="131"/>
+      <c r="J40" s="131"/>
+      <c r="K40" s="131"/>
+      <c r="L40" s="131"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="101"/>
@@ -6679,15 +6765,15 @@
       <c r="C41" s="83">
         <v>0</v>
       </c>
-      <c r="D41" s="132"/>
-      <c r="E41" s="132"/>
-      <c r="F41" s="132"/>
-      <c r="G41" s="132"/>
-      <c r="H41" s="132"/>
-      <c r="I41" s="132"/>
-      <c r="J41" s="132"/>
-      <c r="K41" s="132"/>
-      <c r="L41" s="132"/>
+      <c r="D41" s="131"/>
+      <c r="E41" s="131"/>
+      <c r="F41" s="131"/>
+      <c r="G41" s="131"/>
+      <c r="H41" s="131"/>
+      <c r="I41" s="131"/>
+      <c r="J41" s="131"/>
+      <c r="K41" s="131"/>
+      <c r="L41" s="131"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="101"/>
@@ -6695,22 +6781,22 @@
       <c r="C42" s="83">
         <v>0</v>
       </c>
-      <c r="D42" s="132"/>
-      <c r="E42" s="132"/>
-      <c r="F42" s="132"/>
-      <c r="G42" s="132"/>
-      <c r="H42" s="132"/>
-      <c r="I42" s="132"/>
-      <c r="J42" s="132"/>
-      <c r="K42" s="132"/>
-      <c r="L42" s="132"/>
+      <c r="D42" s="131"/>
+      <c r="E42" s="131"/>
+      <c r="F42" s="131"/>
+      <c r="G42" s="131"/>
+      <c r="H42" s="131"/>
+      <c r="I42" s="131"/>
+      <c r="J42" s="131"/>
+      <c r="K42" s="131"/>
+      <c r="L42" s="131"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="78">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C43" s="84">
         <f>SUM(C40:C42)</f>
@@ -6742,25 +6828,25 @@
     </row>
     <row r="45" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C45" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="D45" s="133" t="s">
+      <c r="D45" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="133"/>
-      <c r="F45" s="133"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="133"/>
-      <c r="I45" s="133"/>
-      <c r="J45" s="133"/>
-      <c r="K45" s="133"/>
-      <c r="L45" s="133"/>
+      <c r="E45" s="132"/>
+      <c r="F45" s="132"/>
+      <c r="G45" s="132"/>
+      <c r="H45" s="132"/>
+      <c r="I45" s="132"/>
+      <c r="J45" s="132"/>
+      <c r="K45" s="132"/>
+      <c r="L45" s="132"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="101"/>
@@ -6768,15 +6854,15 @@
       <c r="C46" s="83">
         <v>0</v>
       </c>
-      <c r="D46" s="132"/>
-      <c r="E46" s="132"/>
-      <c r="F46" s="132"/>
-      <c r="G46" s="132"/>
-      <c r="H46" s="132"/>
-      <c r="I46" s="132"/>
-      <c r="J46" s="132"/>
-      <c r="K46" s="132"/>
-      <c r="L46" s="132"/>
+      <c r="D46" s="131"/>
+      <c r="E46" s="131"/>
+      <c r="F46" s="131"/>
+      <c r="G46" s="131"/>
+      <c r="H46" s="131"/>
+      <c r="I46" s="131"/>
+      <c r="J46" s="131"/>
+      <c r="K46" s="131"/>
+      <c r="L46" s="131"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="101"/>
@@ -6784,15 +6870,15 @@
       <c r="C47" s="83">
         <v>0</v>
       </c>
-      <c r="D47" s="132"/>
-      <c r="E47" s="132"/>
-      <c r="F47" s="132"/>
-      <c r="G47" s="132"/>
-      <c r="H47" s="132"/>
-      <c r="I47" s="132"/>
-      <c r="J47" s="132"/>
-      <c r="K47" s="132"/>
-      <c r="L47" s="132"/>
+      <c r="D47" s="131"/>
+      <c r="E47" s="131"/>
+      <c r="F47" s="131"/>
+      <c r="G47" s="131"/>
+      <c r="H47" s="131"/>
+      <c r="I47" s="131"/>
+      <c r="J47" s="131"/>
+      <c r="K47" s="131"/>
+      <c r="L47" s="131"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="101"/>
@@ -6800,36 +6886,36 @@
       <c r="C48" s="83">
         <v>0</v>
       </c>
-      <c r="D48" s="132"/>
-      <c r="E48" s="132"/>
-      <c r="F48" s="132"/>
-      <c r="G48" s="132"/>
-      <c r="H48" s="132"/>
-      <c r="I48" s="132"/>
-      <c r="J48" s="132"/>
-      <c r="K48" s="132"/>
-      <c r="L48" s="132"/>
+      <c r="D48" s="131"/>
+      <c r="E48" s="131"/>
+      <c r="F48" s="131"/>
+      <c r="G48" s="131"/>
+      <c r="H48" s="131"/>
+      <c r="I48" s="131"/>
+      <c r="J48" s="131"/>
+      <c r="K48" s="131"/>
+      <c r="L48" s="131"/>
     </row>
     <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="99">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B49" s="55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C49" s="84">
         <f>SUM(C46:C48)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="134"/>
-      <c r="E49" s="134"/>
-      <c r="F49" s="134"/>
-      <c r="G49" s="134"/>
-      <c r="H49" s="134"/>
-      <c r="I49" s="134"/>
-      <c r="J49" s="134"/>
-      <c r="K49" s="134"/>
-      <c r="L49" s="134"/>
+      <c r="D49" s="133"/>
+      <c r="E49" s="133"/>
+      <c r="F49" s="133"/>
+      <c r="G49" s="133"/>
+      <c r="H49" s="133"/>
+      <c r="I49" s="133"/>
+      <c r="J49" s="133"/>
+      <c r="K49" s="133"/>
+      <c r="L49" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="35">

--- a/noprofit/en/11255/inpag-template.xlsx
+++ b/noprofit/en/11255/inpag-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AA2347-B537-41CE-9C14-1687A0C969D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6E07B5-0B7F-4605-9276-000F67B53A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" firstSheet="1" activeTab="4" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
   <sheets>
     <sheet name="General information" sheetId="7" r:id="rId1"/>
@@ -843,9 +843,6 @@
     <t>Capital grant</t>
   </si>
   <si>
-    <t>[-] Donations of property, plant and equipment (PPE)</t>
-  </si>
-  <si>
     <t>DPPE</t>
   </si>
   <si>
@@ -943,6 +940,9 @@
   </si>
   <si>
     <t>OCCE</t>
+  </si>
+  <si>
+    <t>Donations of property, plant and equipment (PPE)</t>
   </si>
 </sst>
 </file>
@@ -1441,6 +1441,18 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1450,18 +1462,6 @@
     <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1483,53 +1483,53 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2241,12 +2241,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2263,6 +2257,12 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2291,84 +2291,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="108" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="111"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75" t="s">
@@ -2391,12 +2391,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="45"/>
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
@@ -2490,12 +2490,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45"/>
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45" t="s">
@@ -2623,12 +2623,12 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
-      <c r="B26" s="114" t="s">
+      <c r="B26" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="114"/>
-      <c r="D26" s="114"/>
-      <c r="E26" s="114"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45" t="s">
@@ -2739,12 +2739,12 @@
     </row>
     <row r="34" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45"/>
-      <c r="B34" s="114" t="s">
+      <c r="B34" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="114"/>
-      <c r="D34" s="114"/>
-      <c r="E34" s="114"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45" t="s">
@@ -2821,12 +2821,12 @@
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45"/>
-      <c r="B40" s="114" t="s">
+      <c r="B40" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="114"/>
-      <c r="D40" s="114"/>
-      <c r="E40" s="114"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="111"/>
     </row>
     <row r="41" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45" t="s">
@@ -2949,10 +2949,10 @@
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45"/>
-      <c r="B48" s="114" t="s">
+      <c r="B48" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="114"/>
+      <c r="C48" s="111"/>
       <c r="D48" s="63">
         <f>SUM(D41:D47)</f>
         <v>0</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45"/>
-      <c r="B49" s="114" t="s">
+      <c r="B49" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="114"/>
+      <c r="C49" s="111"/>
       <c r="D49" s="63">
         <f>SUM(D32,D38,D48)</f>
         <v>0</v>
@@ -2995,11 +2995,11 @@
       <c r="A52" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="113" t="str">
+      <c r="B52" s="110" t="str">
         <f>IF((D15+D23+D32=D38+D48),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C52" s="113"/>
+      <c r="C52" s="110"/>
       <c r="D52" s="54">
         <f>D49-D23</f>
         <v>0</v>
@@ -3009,12 +3009,12 @@
       <c r="A53" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="B53" s="112" t="str">
+      <c r="B53" s="109" t="str">
         <f>IF((E15+E23+E32=E38+E48),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="112"/>
-      <c r="D53" s="112"/>
+      <c r="C53" s="109"/>
+      <c r="D53" s="109"/>
       <c r="E53" s="54">
         <f>E49-E23</f>
         <v>0</v>
@@ -3028,6 +3028,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="B52:C52"/>
@@ -3038,11 +3043,6 @@
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B52">
@@ -3155,27 +3155,27 @@
       <c r="E5" s="117"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="108" t="s">
         <v>257</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="111"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="75" t="s">
@@ -3670,13 +3670,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3685,72 +3685,72 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="108" t="s">
         <v>256</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="111"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="111"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="75" t="s">
@@ -3956,6 +3956,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B24:D24"/>
@@ -3967,11 +3972,6 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -3998,85 +3998,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="108" t="s">
         <v>255</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="111"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75" t="s">
@@ -4098,21 +4098,21 @@
       <c r="A10" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="111" t="s">
         <v>233</v>
       </c>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
       <c r="E10" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="123"/>
     </row>
     <row r="12" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="75" t="s">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="15" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B15" s="121" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="C15" s="121"/>
       <c r="D15" s="94">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="18" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B18" s="121" t="s">
         <v>262</v>
@@ -4228,7 +4228,7 @@
         <v>240</v>
       </c>
       <c r="B19" s="121" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C19" s="121"/>
       <c r="D19" s="94">
@@ -4241,10 +4241,10 @@
     </row>
     <row r="20" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B20" s="121" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C20" s="121"/>
       <c r="D20" s="94">
@@ -4257,12 +4257,12 @@
     </row>
     <row r="21" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
-        <v>267</v>
-      </c>
-      <c r="B21" s="123" t="s">
-        <v>273</v>
-      </c>
-      <c r="C21" s="123"/>
+        <v>266</v>
+      </c>
+      <c r="B21" s="122" t="s">
+        <v>272</v>
+      </c>
+      <c r="C21" s="122"/>
       <c r="D21" s="94">
         <v>47</v>
       </c>
@@ -4273,12 +4273,12 @@
     </row>
     <row r="22" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="B22" s="123" t="s">
-        <v>274</v>
-      </c>
-      <c r="C22" s="123"/>
+        <v>267</v>
+      </c>
+      <c r="B22" s="122" t="s">
+        <v>273</v>
+      </c>
+      <c r="C22" s="122"/>
       <c r="D22" s="94">
         <v>48</v>
       </c>
@@ -4289,12 +4289,12 @@
     </row>
     <row r="23" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="B23" s="123" t="s">
-        <v>275</v>
-      </c>
-      <c r="C23" s="123"/>
+        <v>268</v>
+      </c>
+      <c r="B23" s="122" t="s">
+        <v>274</v>
+      </c>
+      <c r="C23" s="122"/>
       <c r="D23" s="94">
         <v>49</v>
       </c>
@@ -4305,12 +4305,12 @@
     </row>
     <row r="24" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="B24" s="123" t="s">
-        <v>276</v>
-      </c>
-      <c r="C24" s="123"/>
+        <v>269</v>
+      </c>
+      <c r="B24" s="122" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24" s="122"/>
       <c r="D24" s="94">
         <v>50</v>
       </c>
@@ -4321,11 +4321,11 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45"/>
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="111" t="s">
         <v>144</v>
       </c>
-      <c r="C25" s="114"/>
-      <c r="D25" s="114"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
       <c r="E25" s="63">
         <f>E10+SUM(E13:E24)</f>
         <v>0</v>
@@ -4356,12 +4356,12 @@
     </row>
     <row r="28" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="B28" s="123" t="s">
-        <v>277</v>
-      </c>
-      <c r="C28" s="123"/>
+        <v>280</v>
+      </c>
+      <c r="B28" s="122" t="s">
+        <v>276</v>
+      </c>
+      <c r="C28" s="122"/>
       <c r="D28" s="94">
         <v>51</v>
       </c>
@@ -4371,12 +4371,12 @@
     </row>
     <row r="29" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B29" s="123" t="s">
-        <v>278</v>
-      </c>
-      <c r="C29" s="123"/>
+        <v>281</v>
+      </c>
+      <c r="B29" s="122" t="s">
+        <v>277</v>
+      </c>
+      <c r="C29" s="122"/>
       <c r="D29" s="94">
         <v>52</v>
       </c>
@@ -4386,12 +4386,12 @@
     </row>
     <row r="30" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="B30" s="123" t="s">
-        <v>279</v>
-      </c>
-      <c r="C30" s="123"/>
+        <v>282</v>
+      </c>
+      <c r="B30" s="122" t="s">
+        <v>278</v>
+      </c>
+      <c r="C30" s="122"/>
       <c r="D30" s="94">
         <v>53</v>
       </c>
@@ -4401,12 +4401,12 @@
     </row>
     <row r="31" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B31" s="123" t="s">
-        <v>280</v>
-      </c>
-      <c r="C31" s="123"/>
+        <v>283</v>
+      </c>
+      <c r="B31" s="122" t="s">
+        <v>279</v>
+      </c>
+      <c r="C31" s="122"/>
       <c r="D31" s="94">
         <v>54</v>
       </c>
@@ -4416,11 +4416,11 @@
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="45"/>
-      <c r="B32" s="114" t="s">
+      <c r="B32" s="111" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="114"/>
-      <c r="D32" s="114"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
       <c r="E32" s="63">
         <f>E10+E25+SUM(E28:E31)</f>
         <v>0</v>
@@ -4452,12 +4452,12 @@
     </row>
     <row r="35" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="45" t="s">
-        <v>288</v>
-      </c>
-      <c r="B35" s="123" t="s">
-        <v>285</v>
-      </c>
-      <c r="C35" s="123"/>
+        <v>287</v>
+      </c>
+      <c r="B35" s="122" t="s">
+        <v>284</v>
+      </c>
+      <c r="C35" s="122"/>
       <c r="D35" s="94">
         <v>55</v>
       </c>
@@ -4467,12 +4467,12 @@
     </row>
     <row r="36" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="45" t="s">
-        <v>289</v>
-      </c>
-      <c r="B36" s="123" t="s">
-        <v>286</v>
-      </c>
-      <c r="C36" s="123"/>
+        <v>288</v>
+      </c>
+      <c r="B36" s="122" t="s">
+        <v>285</v>
+      </c>
+      <c r="C36" s="122"/>
       <c r="D36" s="94">
         <v>56</v>
       </c>
@@ -4482,12 +4482,12 @@
     </row>
     <row r="37" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45" t="s">
-        <v>290</v>
-      </c>
-      <c r="B37" s="123" t="s">
-        <v>287</v>
-      </c>
-      <c r="C37" s="123"/>
+        <v>289</v>
+      </c>
+      <c r="B37" s="122" t="s">
+        <v>286</v>
+      </c>
+      <c r="C37" s="122"/>
       <c r="D37" s="94">
         <v>57</v>
       </c>
@@ -4497,11 +4497,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45"/>
-      <c r="B38" s="114" t="s">
+      <c r="B38" s="111" t="s">
         <v>148</v>
       </c>
-      <c r="C38" s="114"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
       <c r="E38" s="63">
         <f>E10+E25+E32+SUM(E35:E35)</f>
         <v>0</v>
@@ -4516,11 +4516,11 @@
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45"/>
-      <c r="B40" s="114" t="s">
+      <c r="B40" s="111" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="114"/>
-      <c r="D40" s="114"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
       <c r="E40" s="63">
         <f>SUM(E25,E32,E38)</f>
         <v>0</v>
@@ -4535,12 +4535,12 @@
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="45" t="s">
-        <v>296</v>
-      </c>
-      <c r="B42" s="122" t="s">
-        <v>291</v>
-      </c>
-      <c r="C42" s="122"/>
+        <v>295</v>
+      </c>
+      <c r="B42" s="123" t="s">
+        <v>290</v>
+      </c>
+      <c r="C42" s="123"/>
       <c r="D42" s="26"/>
       <c r="E42" s="22">
         <v>0</v>
@@ -4548,12 +4548,12 @@
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="45" t="s">
-        <v>295</v>
-      </c>
-      <c r="B43" s="122" t="s">
-        <v>292</v>
-      </c>
-      <c r="C43" s="122"/>
+        <v>294</v>
+      </c>
+      <c r="B43" s="123" t="s">
+        <v>291</v>
+      </c>
+      <c r="C43" s="123"/>
       <c r="D43" s="26"/>
       <c r="E43" s="22">
         <v>0</v>
@@ -4561,12 +4561,12 @@
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="45" t="s">
-        <v>294</v>
-      </c>
-      <c r="B44" s="122" t="s">
         <v>293</v>
       </c>
-      <c r="C44" s="122"/>
+      <c r="B44" s="123" t="s">
+        <v>292</v>
+      </c>
+      <c r="C44" s="123"/>
       <c r="D44" s="26"/>
       <c r="E44" s="22">
         <v>0</v>
@@ -4574,10 +4574,10 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="45"/>
-      <c r="B45" s="114" t="s">
+      <c r="B45" s="111" t="s">
         <v>150</v>
       </c>
-      <c r="C45" s="114"/>
+      <c r="C45" s="111"/>
       <c r="D45" s="97">
         <v>58</v>
       </c>
@@ -4588,11 +4588,11 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="45"/>
-      <c r="B46" s="114" t="s">
+      <c r="B46" s="111" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="114"/>
-      <c r="D46" s="114"/>
+      <c r="C46" s="111"/>
+      <c r="D46" s="111"/>
       <c r="E46" s="70">
         <f>'Statement of financial position'!D22</f>
         <v>0</v>
@@ -4600,11 +4600,11 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="45"/>
-      <c r="B47" s="114" t="s">
+      <c r="B47" s="111" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="114"/>
-      <c r="D47" s="114"/>
+      <c r="C47" s="111"/>
+      <c r="D47" s="111"/>
       <c r="E47" s="70">
         <f>'Statement of financial position'!E22</f>
         <v>0</v>
@@ -4612,11 +4612,11 @@
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="45"/>
-      <c r="B48" s="114" t="s">
+      <c r="B48" s="111" t="s">
         <v>153</v>
       </c>
-      <c r="C48" s="114"/>
-      <c r="D48" s="114"/>
+      <c r="C48" s="111"/>
+      <c r="D48" s="111"/>
       <c r="E48" s="70">
         <f>E47-E46</f>
         <v>0</v>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="31"/>
-      <c r="B52" s="122" t="s">
+      <c r="B52" s="123" t="s">
         <v>155</v>
       </c>
-      <c r="C52" s="122"/>
+      <c r="C52" s="123"/>
       <c r="D52" s="94">
         <v>59</v>
       </c>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
-      <c r="B53" s="122" t="s">
+      <c r="B53" s="123" t="s">
         <v>156</v>
       </c>
-      <c r="C53" s="122"/>
+      <c r="C53" s="123"/>
       <c r="D53" s="94">
         <v>60</v>
       </c>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
-      <c r="B54" s="122" t="s">
+      <c r="B54" s="123" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="122"/>
+      <c r="C54" s="123"/>
       <c r="D54" s="94">
         <v>61</v>
       </c>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
-      <c r="B55" s="122" t="s">
+      <c r="B55" s="123" t="s">
         <v>158</v>
       </c>
-      <c r="C55" s="122"/>
+      <c r="C55" s="123"/>
       <c r="D55" s="94">
         <v>62</v>
       </c>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="56" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31"/>
-      <c r="B56" s="122" t="s">
+      <c r="B56" s="123" t="s">
         <v>159</v>
       </c>
-      <c r="C56" s="122"/>
+      <c r="C56" s="123"/>
       <c r="D56" s="94">
         <v>63</v>
       </c>
@@ -4716,24 +4716,20 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B32:D32"/>
@@ -4749,20 +4745,24 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
@@ -4788,85 +4788,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="111"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="127" t="s">
+      <c r="A9" s="129" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="127"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="126"/>
@@ -4887,34 +4887,34 @@
       <c r="D12" s="126"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="128"/>
-      <c r="B13" s="128"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="128"/>
+      <c r="A13" s="127"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="128"/>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
+      <c r="A14" s="127"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="128"/>
-      <c r="B15" s="128"/>
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
+      <c r="A15" s="127"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="128"/>
-      <c r="B16" s="128"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
+      <c r="A16" s="127"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="128"/>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
+      <c r="A17" s="127"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="126"/>
@@ -4983,10 +4983,10 @@
       <c r="D28" s="126"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="129"/>
-      <c r="B29" s="129"/>
-      <c r="C29" s="129"/>
-      <c r="D29" s="129"/>
+      <c r="A29" s="125"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="125"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="75" t="s">
@@ -5604,18 +5604,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5631,6 +5619,18 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5672,65 +5672,65 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="114">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="114">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="111"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -6074,121 +6074,121 @@
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="135" t="str">
+      <c r="B2" s="134" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="134"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="135" t="str">
+      <c r="B3" s="134" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="135"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="136">
+      <c r="B4" s="135">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="136"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="136"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="136">
+      <c r="B5" s="135">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="135"/>
+      <c r="J5" s="135"/>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="136" t="s">
         <v>254</v>
       </c>
-      <c r="B6" s="137"/>
-      <c r="C6" s="137"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="137"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="137"/>
-      <c r="K6" s="137"/>
-      <c r="L6" s="137"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137"/>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="137"/>
-      <c r="H7" s="137"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="137"/>
-      <c r="K7" s="137"/>
-      <c r="L7" s="137"/>
+      <c r="A7" s="136"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="137"/>
-      <c r="B8" s="137"/>
-      <c r="C8" s="137"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="137"/>
-      <c r="G8" s="137"/>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="137"/>
-      <c r="K8" s="137"/>
-      <c r="L8" s="137"/>
+      <c r="A8" s="136"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="136"/>
+      <c r="H8" s="136"/>
+      <c r="I8" s="136"/>
+      <c r="J8" s="136"/>
+      <c r="K8" s="136"/>
+      <c r="L8" s="136"/>
     </row>
     <row r="9" spans="1:12" s="86" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79" t="s">
@@ -6200,17 +6200,17 @@
       <c r="C9" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="D9" s="132" t="s">
+      <c r="D9" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="104"/>
@@ -6311,17 +6311,17 @@
       <c r="C15" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="D15" s="132" t="s">
+      <c r="D15" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="103"/>
@@ -6329,15 +6329,15 @@
       <c r="C16" s="92">
         <v>0</v>
       </c>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="134"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="132"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="103"/>
@@ -6345,15 +6345,15 @@
       <c r="C17" s="92">
         <v>0</v>
       </c>
-      <c r="D17" s="134"/>
-      <c r="E17" s="134"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="134"/>
-      <c r="H17" s="134"/>
-      <c r="I17" s="134"/>
-      <c r="J17" s="134"/>
-      <c r="K17" s="134"/>
-      <c r="L17" s="134"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="132"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="103"/>
@@ -6361,15 +6361,15 @@
       <c r="C18" s="92">
         <v>0</v>
       </c>
-      <c r="D18" s="134"/>
-      <c r="E18" s="134"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="134"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="132"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="132"/>
     </row>
     <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="78">
@@ -6416,17 +6416,17 @@
       <c r="C21" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="D21" s="132" t="s">
+      <c r="D21" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="101"/>
@@ -6521,17 +6521,17 @@
       <c r="C27" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="D27" s="132" t="s">
+      <c r="D27" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="132"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="132"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="101"/>
@@ -6626,17 +6626,17 @@
       <c r="C33" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="D33" s="132" t="s">
+      <c r="D33" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="132"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="132"/>
-      <c r="J33" s="132"/>
-      <c r="K33" s="132"/>
-      <c r="L33" s="132"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="133"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="133"/>
+      <c r="I33" s="133"/>
+      <c r="J33" s="133"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="101"/>
@@ -6731,17 +6731,17 @@
       <c r="C39" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="D39" s="132" t="s">
+      <c r="D39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="132"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="132"/>
-      <c r="H39" s="132"/>
-      <c r="I39" s="132"/>
-      <c r="J39" s="132"/>
-      <c r="K39" s="132"/>
-      <c r="L39" s="132"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="133"/>
+      <c r="K39" s="133"/>
+      <c r="L39" s="133"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="101"/>
@@ -6836,17 +6836,17 @@
       <c r="C45" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="D45" s="132" t="s">
+      <c r="D45" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="132"/>
-      <c r="F45" s="132"/>
-      <c r="G45" s="132"/>
-      <c r="H45" s="132"/>
-      <c r="I45" s="132"/>
-      <c r="J45" s="132"/>
-      <c r="K45" s="132"/>
-      <c r="L45" s="132"/>
+      <c r="E45" s="133"/>
+      <c r="F45" s="133"/>
+      <c r="G45" s="133"/>
+      <c r="H45" s="133"/>
+      <c r="I45" s="133"/>
+      <c r="J45" s="133"/>
+      <c r="K45" s="133"/>
+      <c r="L45" s="133"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="101"/>
@@ -6907,28 +6907,27 @@
         <f>SUM(C46:C48)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="133"/>
-      <c r="E49" s="133"/>
-      <c r="F49" s="133"/>
-      <c r="G49" s="133"/>
-      <c r="H49" s="133"/>
-      <c r="I49" s="133"/>
-      <c r="J49" s="133"/>
-      <c r="K49" s="133"/>
-      <c r="L49" s="133"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="137"/>
+      <c r="I49" s="137"/>
+      <c r="J49" s="137"/>
+      <c r="K49" s="137"/>
+      <c r="L49" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D17:L17"/>
-    <mergeCell ref="D18:L18"/>
-    <mergeCell ref="D9:L9"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A6:L8"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="D46:L46"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D40:L40"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="D39:L39"/>
     <mergeCell ref="D49:L49"/>
     <mergeCell ref="D10:L10"/>
     <mergeCell ref="D11:L11"/>
@@ -6945,15 +6944,16 @@
     <mergeCell ref="D16:L16"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="D34:L34"/>
-    <mergeCell ref="D48:L48"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D40:L40"/>
-    <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D17:L17"/>
+    <mergeCell ref="D18:L18"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="A6:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>

--- a/noprofit/en/11255/inpag-template.xlsx
+++ b/noprofit/en/11255/inpag-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A02AFA8-C3DF-4BA9-B283-FD3095575342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFC963B-0A3F-41F2-B0C0-4E6B10D440E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
@@ -1071,7 +1071,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1342,6 +1342,15 @@
     <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1396,12 +1405,12 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1437,21 +1446,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1842,324 +1836,324 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="102" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="100" t="s">
+      <c r="B7" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="98">
+      <c r="B8" s="101">
         <v>45292</v>
       </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="98">
+      <c r="B9" s="101">
         <v>45657</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="96"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="96"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="96"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="96"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="96"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="96"/>
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="101"/>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="98" t="s">
+      <c r="B17" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="101"/>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="96"/>
-      <c r="B18" s="98" t="s">
+      <c r="B18" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="101"/>
+      <c r="G18" s="101"/>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="96"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="101"/>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="96"/>
-      <c r="B20" s="98" t="s">
+      <c r="B20" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="101"/>
+      <c r="G20" s="101"/>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="98" t="s">
+      <c r="B21" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="98"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="101"/>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="98" t="s">
+      <c r="B22" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="101"/>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="96"/>
-      <c r="B23" s="98" t="s">
+      <c r="B23" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="101"/>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="96"/>
-      <c r="B24" s="98" t="s">
+      <c r="B24" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="101"/>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="96"/>
-      <c r="B25" s="98" t="s">
+      <c r="B25" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="98"/>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="98"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="101"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="96"/>
-      <c r="B26" s="98" t="s">
+      <c r="B26" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="98"/>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="98"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="101"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="96"/>
-      <c r="B27" s="98" t="s">
+      <c r="B27" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="98"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="98"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="101"/>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="96"/>
-      <c r="B28" s="98" t="s">
+      <c r="B28" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="98"/>
-      <c r="D28" s="98"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="98"/>
-      <c r="G28" s="98"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2189,7 +2183,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Arial,Normale"© www.banana.ch/it/it</oddFooter>
+    <oddFooter>&amp;C&amp;"Arial,Normale"© www.banana.ch</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2213,84 +2207,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="101" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="101" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="103">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="103">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
@@ -2313,12 +2307,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
@@ -2412,12 +2406,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44"/>
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="110" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
@@ -2545,12 +2539,12 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="107" t="s">
+      <c r="B26" s="110" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
@@ -2678,12 +2672,12 @@
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="44"/>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
+      <c r="C35" s="110"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
     </row>
     <row r="36" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
@@ -2760,12 +2754,12 @@
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="44"/>
-      <c r="B41" s="107" t="s">
+      <c r="B41" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="107"/>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
+      <c r="C41" s="110"/>
+      <c r="D41" s="110"/>
+      <c r="E41" s="110"/>
     </row>
     <row r="42" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
@@ -2888,10 +2882,10 @@
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
-      <c r="B49" s="107" t="s">
+      <c r="B49" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="107"/>
+      <c r="C49" s="110"/>
       <c r="D49" s="62">
         <f>SUM(D42:D48)</f>
         <v>0</v>
@@ -2903,10 +2897,10 @@
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
-      <c r="B50" s="107" t="s">
+      <c r="B50" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="C50" s="107"/>
+      <c r="C50" s="110"/>
       <c r="D50" s="62">
         <f>SUM(D33,D39,D49)</f>
         <v>0</v>
@@ -2934,11 +2928,11 @@
       <c r="A53" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="B53" s="106" t="str">
+      <c r="B53" s="109" t="str">
         <f>IF((D15+D23+D33=D39+D49),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="106"/>
+      <c r="C53" s="109"/>
       <c r="D53" s="53">
         <f>D50-D23</f>
         <v>0</v>
@@ -2948,12 +2942,12 @@
       <c r="A54" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="B54" s="105" t="str">
+      <c r="B54" s="108" t="str">
         <f>IF((E15+E23+E33=E39+E49),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C54" s="105"/>
-      <c r="D54" s="105"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="108"/>
       <c r="E54" s="53">
         <f>E50-E23</f>
         <v>0</v>
@@ -3010,7 +3004,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;C© www.banana.ch/it/it</oddFooter>
+    <oddFooter>&amp;C© www.banana.ch</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3035,13 +3029,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
@@ -3049,72 +3043,72 @@
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="109" t="str">
+      <c r="B2" s="112" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109" t="str">
+      <c r="B3" s="112" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="113">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="113">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>197</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -3673,7 +3667,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;C© www.banana.ch/it/it</oddFooter>
+    <oddFooter>&amp;C© www.banana.ch</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3694,13 +3688,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3709,72 +3703,72 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="101" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="101" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="103">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="103">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -3797,10 +3791,10 @@
       <c r="A10" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="111" t="s">
+      <c r="B10" s="114" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="111"/>
+      <c r="C10" s="114"/>
       <c r="D10" s="14">
         <v>0</v>
       </c>
@@ -3834,11 +3828,11 @@
       <c r="A13" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="113" t="s">
+      <c r="B13" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
       <c r="E13" s="14">
         <v>0</v>
       </c>
@@ -3847,22 +3841,22 @@
       <c r="A14" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="113" t="s">
+      <c r="B14" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
       <c r="E14" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="44"/>
-      <c r="B15" s="112" t="s">
+      <c r="B15" s="115" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="112"/>
-      <c r="D15" s="112"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
       <c r="E15" s="67">
         <f>SUM(E13:E14)</f>
         <v>0</v>
@@ -3896,11 +3890,11 @@
       <c r="A18" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="B18" s="114" t="s">
+      <c r="B18" s="117" t="s">
         <v>254</v>
       </c>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
       <c r="E18" s="14">
         <v>0</v>
       </c>
@@ -3909,11 +3903,11 @@
       <c r="A19" s="44" t="s">
         <v>237</v>
       </c>
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="117" t="s">
         <v>255</v>
       </c>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
       <c r="E19" s="14">
         <v>0</v>
       </c>
@@ -3922,11 +3916,11 @@
       <c r="A20" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="B20" s="114" t="s">
+      <c r="B20" s="117" t="s">
         <v>256</v>
       </c>
-      <c r="C20" s="114"/>
-      <c r="D20" s="114"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
       <c r="E20" s="14">
         <v>0</v>
       </c>
@@ -3935,11 +3929,11 @@
       <c r="A21" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="114" t="s">
+      <c r="B21" s="117" t="s">
         <v>257</v>
       </c>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
       <c r="E21" s="14">
         <v>0</v>
       </c>
@@ -3948,22 +3942,22 @@
       <c r="A22" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="B22" s="113" t="s">
+      <c r="B22" s="116" t="s">
         <v>258</v>
       </c>
-      <c r="C22" s="113"/>
-      <c r="D22" s="113"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
       <c r="E22" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
-      <c r="B23" s="112" t="s">
+      <c r="B23" s="115" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="112"/>
-      <c r="D23" s="112"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="115"/>
       <c r="E23" s="67">
         <f>SUM(E18:E22)</f>
         <v>0</v>
@@ -3981,11 +3975,11 @@
       <c r="A25" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="112" t="s">
+      <c r="B25" s="115" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="112"/>
-      <c r="D25" s="112"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="115"/>
       <c r="E25" s="62">
         <f>SUM(D10,E15,E23)</f>
         <v>0</v>
@@ -4014,7 +4008,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;C© www.banana.ch/it/it</oddFooter>
+    <oddFooter>&amp;C© www.banana.ch</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -4036,94 +4030,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="101" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="101" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="103">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="103">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="119" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="117"/>
+      <c r="C9" s="119"/>
       <c r="D9" s="74" t="s">
         <v>34</v>
       </c>
@@ -4136,30 +4130,30 @@
       <c r="A10" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
       <c r="E10" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="115"/>
-      <c r="B11" s="115"/>
-      <c r="C11" s="115"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
     </row>
     <row r="12" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="117" t="s">
+      <c r="B12" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="117"/>
+      <c r="C12" s="119"/>
       <c r="D12" s="74" t="s">
         <v>34</v>
       </c>
@@ -4172,10 +4166,10 @@
       <c r="A13" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="117" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="114"/>
+      <c r="C13" s="117"/>
       <c r="D13" s="90"/>
       <c r="E13" s="22">
         <v>0</v>
@@ -4185,10 +4179,10 @@
       <c r="A14" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="B14" s="114" t="s">
+      <c r="B14" s="117" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="114"/>
+      <c r="C14" s="117"/>
       <c r="D14" s="90"/>
       <c r="E14" s="22">
         <v>0</v>
@@ -4198,10 +4192,10 @@
       <c r="A15" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="117" t="s">
         <v>270</v>
       </c>
-      <c r="C15" s="114"/>
+      <c r="C15" s="117"/>
       <c r="D15" s="90"/>
       <c r="E15" s="22">
         <v>0</v>
@@ -4211,10 +4205,10 @@
       <c r="A16" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="117" t="s">
         <v>250</v>
       </c>
-      <c r="C16" s="114"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="90"/>
       <c r="E16" s="22">
         <v>0</v>
@@ -4225,10 +4219,10 @@
       <c r="A17" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="117" t="s">
         <v>249</v>
       </c>
-      <c r="C17" s="114"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="90"/>
       <c r="E17" s="22">
         <v>0</v>
@@ -4239,10 +4233,10 @@
       <c r="A18" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="B18" s="114" t="s">
+      <c r="B18" s="117" t="s">
         <v>265</v>
       </c>
-      <c r="C18" s="114"/>
+      <c r="C18" s="117"/>
       <c r="D18" s="90"/>
       <c r="E18" s="22">
         <v>0</v>
@@ -4253,10 +4247,10 @@
       <c r="A19" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="117" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="114"/>
+      <c r="C19" s="117"/>
       <c r="D19" s="90"/>
       <c r="E19" s="22">
         <v>0</v>
@@ -4267,10 +4261,10 @@
       <c r="A20" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="B20" s="114" t="s">
+      <c r="B20" s="117" t="s">
         <v>260</v>
       </c>
-      <c r="C20" s="114"/>
+      <c r="C20" s="117"/>
       <c r="D20" s="90"/>
       <c r="E20" s="22">
         <v>0</v>
@@ -4281,10 +4275,10 @@
       <c r="A21" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="B21" s="116" t="s">
+      <c r="B21" s="120" t="s">
         <v>261</v>
       </c>
-      <c r="C21" s="116"/>
+      <c r="C21" s="120"/>
       <c r="D21" s="90"/>
       <c r="E21" s="22">
         <v>0</v>
@@ -4295,10 +4289,10 @@
       <c r="A22" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="116" t="s">
+      <c r="B22" s="120" t="s">
         <v>262</v>
       </c>
-      <c r="C22" s="116"/>
+      <c r="C22" s="120"/>
       <c r="D22" s="90"/>
       <c r="E22" s="22">
         <v>0</v>
@@ -4309,10 +4303,10 @@
       <c r="A23" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="B23" s="116" t="s">
+      <c r="B23" s="120" t="s">
         <v>263</v>
       </c>
-      <c r="C23" s="116"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="90"/>
       <c r="E23" s="22">
         <v>0</v>
@@ -4323,10 +4317,10 @@
       <c r="A24" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="B24" s="116" t="s">
+      <c r="B24" s="120" t="s">
         <v>264</v>
       </c>
-      <c r="C24" s="116"/>
+      <c r="C24" s="120"/>
       <c r="D24" s="90"/>
       <c r="E24" s="22">
         <v>0</v>
@@ -4335,11 +4329,11 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="107" t="s">
+      <c r="B25" s="110" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
       <c r="E25" s="62">
         <f>E10+SUM(E13:E24)</f>
         <v>0</v>
@@ -4356,10 +4350,10 @@
       <c r="A27" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="117" t="s">
+      <c r="B27" s="119" t="s">
         <v>126</v>
       </c>
-      <c r="C27" s="117"/>
+      <c r="C27" s="119"/>
       <c r="D27" s="74" t="s">
         <v>34</v>
       </c>
@@ -4372,10 +4366,10 @@
       <c r="A28" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="116" t="s">
+      <c r="B28" s="120" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="116"/>
+      <c r="C28" s="120"/>
       <c r="D28" s="90"/>
       <c r="E28" s="22">
         <v>0</v>
@@ -4385,10 +4379,10 @@
       <c r="A29" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="B29" s="116" t="s">
+      <c r="B29" s="120" t="s">
         <v>272</v>
       </c>
-      <c r="C29" s="116"/>
+      <c r="C29" s="120"/>
       <c r="D29" s="90"/>
       <c r="E29" s="22">
         <v>0</v>
@@ -4398,10 +4392,10 @@
       <c r="A30" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="B30" s="116" t="s">
+      <c r="B30" s="120" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="116"/>
+      <c r="C30" s="120"/>
       <c r="D30" s="90"/>
       <c r="E30" s="22">
         <v>0</v>
@@ -4411,10 +4405,10 @@
       <c r="A31" s="44" t="s">
         <v>211</v>
       </c>
-      <c r="B31" s="116" t="s">
+      <c r="B31" s="120" t="s">
         <v>273</v>
       </c>
-      <c r="C31" s="116"/>
+      <c r="C31" s="120"/>
       <c r="D31" s="90"/>
       <c r="E31" s="22">
         <v>0</v>
@@ -4422,11 +4416,11 @@
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="107" t="s">
+      <c r="B32" s="110" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
       <c r="E32" s="62">
         <f>E10+E25+SUM(E28:E31)</f>
         <v>0</v>
@@ -4443,10 +4437,10 @@
       <c r="A34" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="117" t="s">
+      <c r="B34" s="119" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="117"/>
+      <c r="C34" s="119"/>
       <c r="D34" s="74" t="s">
         <v>34</v>
       </c>
@@ -4460,10 +4454,10 @@
       <c r="A35" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="B35" s="116" t="s">
+      <c r="B35" s="120" t="s">
         <v>267</v>
       </c>
-      <c r="C35" s="116"/>
+      <c r="C35" s="120"/>
       <c r="D35" s="90"/>
       <c r="E35" s="22">
         <v>0</v>
@@ -4473,10 +4467,10 @@
       <c r="A36" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="B36" s="116" t="s">
+      <c r="B36" s="120" t="s">
         <v>268</v>
       </c>
-      <c r="C36" s="116"/>
+      <c r="C36" s="120"/>
       <c r="D36" s="90"/>
       <c r="E36" s="22">
         <v>0</v>
@@ -4486,10 +4480,10 @@
       <c r="A37" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="B37" s="116" t="s">
+      <c r="B37" s="120" t="s">
         <v>269</v>
       </c>
-      <c r="C37" s="116"/>
+      <c r="C37" s="120"/>
       <c r="D37" s="90"/>
       <c r="E37" s="22">
         <v>0</v>
@@ -4497,11 +4491,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
-      <c r="B38" s="107" t="s">
+      <c r="B38" s="110" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="107"/>
-      <c r="D38" s="107"/>
+      <c r="C38" s="110"/>
+      <c r="D38" s="110"/>
       <c r="E38" s="62">
         <f>E10+E25+E32+SUM(E35:E37)</f>
         <v>0</v>
@@ -4516,11 +4510,11 @@
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
-      <c r="B40" s="107" t="s">
+      <c r="B40" s="110" t="s">
         <v>130</v>
       </c>
-      <c r="C40" s="107"/>
-      <c r="D40" s="107"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="110"/>
       <c r="E40" s="62">
         <f>SUM(E25,E32,E38)</f>
         <v>0</v>
@@ -4537,10 +4531,10 @@
       <c r="A42" s="44" t="s">
         <v>220</v>
       </c>
-      <c r="B42" s="115" t="s">
+      <c r="B42" s="118" t="s">
         <v>215</v>
       </c>
-      <c r="C42" s="115"/>
+      <c r="C42" s="118"/>
       <c r="D42" s="26"/>
       <c r="E42" s="22">
         <v>0</v>
@@ -4550,10 +4544,10 @@
       <c r="A43" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="B43" s="115" t="s">
+      <c r="B43" s="118" t="s">
         <v>216</v>
       </c>
-      <c r="C43" s="115"/>
+      <c r="C43" s="118"/>
       <c r="D43" s="26"/>
       <c r="E43" s="22">
         <v>0</v>
@@ -4563,10 +4557,10 @@
       <c r="A44" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="115" t="s">
+      <c r="B44" s="118" t="s">
         <v>217</v>
       </c>
-      <c r="C44" s="115"/>
+      <c r="C44" s="118"/>
       <c r="D44" s="26"/>
       <c r="E44" s="22">
         <v>0</v>
@@ -4574,10 +4568,10 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
-      <c r="B45" s="107" t="s">
+      <c r="B45" s="110" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="107"/>
+      <c r="C45" s="110"/>
       <c r="D45" s="93">
         <v>49</v>
       </c>
@@ -4588,11 +4582,11 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
-      <c r="B46" s="107" t="s">
+      <c r="B46" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
+      <c r="C46" s="110"/>
+      <c r="D46" s="110"/>
       <c r="E46" s="69">
         <f>'Statement of financial position'!D22</f>
         <v>0</v>
@@ -4600,11 +4594,11 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
-      <c r="B47" s="107" t="s">
+      <c r="B47" s="110" t="s">
         <v>133</v>
       </c>
-      <c r="C47" s="107"/>
-      <c r="D47" s="107"/>
+      <c r="C47" s="110"/>
+      <c r="D47" s="110"/>
       <c r="E47" s="69">
         <f>'Statement of financial position'!E22</f>
         <v>0</v>
@@ -4612,11 +4606,11 @@
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
-      <c r="B48" s="107" t="s">
+      <c r="B48" s="110" t="s">
         <v>134</v>
       </c>
-      <c r="C48" s="107"/>
-      <c r="D48" s="107"/>
+      <c r="C48" s="110"/>
+      <c r="D48" s="110"/>
       <c r="E48" s="69">
         <f>E47-E46</f>
         <v>0</v>
@@ -4647,10 +4641,10 @@
     </row>
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="31"/>
-      <c r="B52" s="115" t="s">
+      <c r="B52" s="118" t="s">
         <v>136</v>
       </c>
-      <c r="C52" s="115"/>
+      <c r="C52" s="118"/>
       <c r="D52" s="90">
         <v>50</v>
       </c>
@@ -4658,10 +4652,10 @@
     </row>
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
-      <c r="B53" s="115" t="s">
+      <c r="B53" s="118" t="s">
         <v>137</v>
       </c>
-      <c r="C53" s="115"/>
+      <c r="C53" s="118"/>
       <c r="D53" s="90">
         <v>51</v>
       </c>
@@ -4669,10 +4663,10 @@
     </row>
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
-      <c r="B54" s="115" t="s">
+      <c r="B54" s="118" t="s">
         <v>138</v>
       </c>
-      <c r="C54" s="115"/>
+      <c r="C54" s="118"/>
       <c r="D54" s="90">
         <v>52</v>
       </c>
@@ -4680,10 +4674,10 @@
     </row>
     <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
-      <c r="B55" s="115" t="s">
+      <c r="B55" s="118" t="s">
         <v>139</v>
       </c>
-      <c r="C55" s="115"/>
+      <c r="C55" s="118"/>
       <c r="D55" s="90">
         <v>53</v>
       </c>
@@ -4691,10 +4685,10 @@
     </row>
     <row r="56" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31"/>
-      <c r="B56" s="115" t="s">
+      <c r="B56" s="118" t="s">
         <v>140</v>
       </c>
-      <c r="C56" s="115"/>
+      <c r="C56" s="118"/>
       <c r="D56" s="90">
         <v>54</v>
       </c>
@@ -4765,9 +4759,9 @@
     <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;C© www.banana.ch/it/it</oddFooter>
+    <oddFooter>&amp;C© www.banana.ch</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -4788,205 +4782,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="101" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="101" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="103">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="103">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="120" t="s">
+      <c r="A9" s="123" t="s">
         <v>141</v>
       </c>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="119"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
+      <c r="A10" s="122"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="122"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="119"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
+      <c r="A11" s="122"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="119"/>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
+      <c r="A12" s="122"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="121"/>
-      <c r="B13" s="121"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
+      <c r="A13" s="124"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="121"/>
-      <c r="B14" s="121"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
+      <c r="A14" s="124"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="121"/>
-      <c r="B15" s="121"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
+      <c r="A15" s="124"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="121"/>
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
+      <c r="A16" s="124"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
+      <c r="A17" s="124"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="119"/>
-      <c r="B18" s="119"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
+      <c r="A18" s="122"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="119"/>
-      <c r="B19" s="119"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
+      <c r="A19" s="122"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="119"/>
-      <c r="B20" s="119"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="119"/>
+      <c r="A20" s="122"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="119"/>
-      <c r="B21" s="119"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
+      <c r="A21" s="122"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
+      <c r="A22" s="122"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="119"/>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
+      <c r="A23" s="122"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="119"/>
-      <c r="B24" s="119"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
+      <c r="A24" s="122"/>
+      <c r="B24" s="122"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="119"/>
-      <c r="B25" s="119"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
+      <c r="A25" s="122"/>
+      <c r="B25" s="122"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="119"/>
-      <c r="B26" s="119"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
+      <c r="A26" s="122"/>
+      <c r="B26" s="122"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="119"/>
-      <c r="B27" s="119"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
+      <c r="A27" s="122"/>
+      <c r="B27" s="122"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="119"/>
-      <c r="B28" s="119"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
+      <c r="A28" s="122"/>
+      <c r="B28" s="122"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="122"/>
-      <c r="B29" s="122"/>
-      <c r="C29" s="122"/>
-      <c r="D29" s="122"/>
+      <c r="A29" s="125"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="125"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="74" t="s">
@@ -5362,7 +5356,7 @@
       <c r="D61" s="24"/>
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="130">
+      <c r="A62" s="30">
         <v>10</v>
       </c>
       <c r="B62" s="38" t="s">
@@ -5374,7 +5368,7 @@
       <c r="D62" s="24"/>
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="130">
+      <c r="A63" s="30">
         <v>11</v>
       </c>
       <c r="B63" s="38" t="s">
@@ -5386,7 +5380,7 @@
       <c r="D63" s="24"/>
     </row>
     <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="130">
+      <c r="A64" s="30">
         <v>12</v>
       </c>
       <c r="B64" s="38" t="s">
@@ -5398,7 +5392,7 @@
       <c r="D64" s="24"/>
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="130">
+      <c r="A65" s="30">
         <v>13</v>
       </c>
       <c r="B65" s="38" t="s">
@@ -5410,7 +5404,7 @@
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="130">
+      <c r="A66" s="30">
         <v>14</v>
       </c>
       <c r="B66" s="38" t="s">
@@ -5453,7 +5447,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A70" s="131">
+      <c r="A70" s="98">
         <v>15</v>
       </c>
       <c r="B70" s="38" t="s">
@@ -5465,7 +5459,7 @@
       <c r="D70" s="92"/>
     </row>
     <row r="71" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A71" s="131">
+      <c r="A71" s="98">
         <v>16</v>
       </c>
       <c r="B71" s="38" t="s">
@@ -5477,7 +5471,7 @@
       <c r="D71" s="92"/>
     </row>
     <row r="72" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A72" s="131">
+      <c r="A72" s="98">
         <v>17</v>
       </c>
       <c r="B72" s="38" t="s">
@@ -5520,7 +5514,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A76" s="131">
+      <c r="A76" s="98">
         <v>18</v>
       </c>
       <c r="B76" s="38" t="s">
@@ -5532,7 +5526,7 @@
       <c r="D76" s="92"/>
     </row>
     <row r="77" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A77" s="131">
+      <c r="A77" s="98">
         <v>19</v>
       </c>
       <c r="B77" s="38" t="s">
@@ -5544,7 +5538,7 @@
       <c r="D77" s="92"/>
     </row>
     <row r="78" spans="1:4" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A78" s="131">
+      <c r="A78" s="98">
         <v>20</v>
       </c>
       <c r="B78" s="38" t="s">
@@ -5556,7 +5550,7 @@
       <c r="D78" s="92"/>
     </row>
     <row r="79" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A79" s="131">
+      <c r="A79" s="98">
         <v>21</v>
       </c>
       <c r="B79" s="38" t="s">
@@ -5568,7 +5562,7 @@
       <c r="D79" s="92"/>
     </row>
     <row r="80" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A80" s="131">
+      <c r="A80" s="98">
         <v>22</v>
       </c>
       <c r="B80" s="38" t="s">
@@ -5580,7 +5574,7 @@
       <c r="D80" s="92"/>
     </row>
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A81" s="131">
+      <c r="A81" s="98">
         <v>23</v>
       </c>
       <c r="B81" s="38" t="s">
@@ -5592,7 +5586,7 @@
       <c r="D81" s="92"/>
     </row>
     <row r="82" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A82" s="131">
+      <c r="A82" s="98">
         <v>24</v>
       </c>
       <c r="B82" s="38" t="s">
@@ -5648,7 +5642,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;C© www.banana.ch/it/it&amp;R&amp;P</oddFooter>
+    <oddFooter>&amp;C© www.banana.ch&amp;R&amp;P</oddFooter>
   </headerFooter>
   <ignoredErrors>
     <ignoredError sqref="A42:A47 A55:A57 A33 A61" numberStoredAsText="1"/>
@@ -5672,77 +5666,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="101" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="101" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="103">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="103">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -6019,8 +6013,8 @@
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="30"/>
       <c r="B32" s="38"/>
-      <c r="C32" s="133"/>
-      <c r="D32" s="133"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="100"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
@@ -6029,7 +6023,7 @@
       <c r="B33" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="132" t="s">
+      <c r="C33" s="99" t="s">
         <v>144</v>
       </c>
       <c r="D33" s="21" t="s">
@@ -6113,11 +6107,11 @@
       <c r="B40" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="C40" s="134">
+      <c r="C40" s="63">
         <f>SUM(C34:C39)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="133"/>
+      <c r="D40" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6131,7 +6125,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;C© www.banana.ch/it/it&amp;R&amp;P</oddFooter>
+    <oddFooter>&amp;C© www.banana.ch&amp;R&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -6155,140 +6149,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
     </row>
     <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="127" t="str">
+      <c r="B2" s="130" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="127" t="str">
+      <c r="B3" s="130" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="128">
+      <c r="B4" s="131">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="128">
+      <c r="B5" s="131">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="131"/>
+      <c r="J5" s="131"/>
+      <c r="K5" s="131"/>
+      <c r="L5" s="131"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="129" t="s">
+      <c r="A6" s="132" t="s">
         <v>194</v>
       </c>
-      <c r="B6" s="129"/>
-      <c r="C6" s="129"/>
-      <c r="D6" s="129"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="129"/>
-      <c r="K6" s="129"/>
-      <c r="L6" s="129"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
+      <c r="L6" s="132"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="129"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="129"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="129"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="132"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="129"/>
-      <c r="B8" s="129"/>
-      <c r="C8" s="129"/>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="129"/>
-      <c r="H8" s="129"/>
-      <c r="I8" s="129"/>
-      <c r="J8" s="129"/>
-      <c r="K8" s="129"/>
-      <c r="L8" s="129"/>
+      <c r="A8" s="132"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="132"/>
+      <c r="L8" s="132"/>
     </row>
     <row r="9" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="78" t="s">
@@ -6300,17 +6294,17 @@
       <c r="C9" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="125" t="s">
+      <c r="D9" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="125"/>
-      <c r="L9" s="125"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="128"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="97"/>
@@ -6318,15 +6312,15 @@
       <c r="C10" s="81">
         <v>0</v>
       </c>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="124"/>
-      <c r="L10" s="124"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="127"/>
+      <c r="L10" s="127"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="97"/>
@@ -6334,15 +6328,15 @@
       <c r="C11" s="81">
         <v>0</v>
       </c>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="124"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="97"/>
@@ -6350,15 +6344,15 @@
       <c r="C12" s="81">
         <v>0</v>
       </c>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="77">
@@ -6405,17 +6399,17 @@
       <c r="C15" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="D15" s="125" t="s">
+      <c r="D15" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="128"/>
+      <c r="I15" s="128"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="128"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="97"/>
@@ -6423,15 +6417,15 @@
       <c r="C16" s="81">
         <v>0</v>
       </c>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="124"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="127"/>
+      <c r="K16" s="127"/>
+      <c r="L16" s="127"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="97"/>
@@ -6439,15 +6433,15 @@
       <c r="C17" s="81">
         <v>0</v>
       </c>
-      <c r="D17" s="124"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="124"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="127"/>
+      <c r="L17" s="127"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="97"/>
@@ -6455,15 +6449,15 @@
       <c r="C18" s="81">
         <v>0</v>
       </c>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="124"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="127"/>
+      <c r="L18" s="127"/>
     </row>
     <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="77">
@@ -6510,17 +6504,17 @@
       <c r="C21" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="125" t="s">
+      <c r="D21" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="125"/>
-      <c r="F21" s="125"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="125"/>
-      <c r="I21" s="125"/>
-      <c r="J21" s="125"/>
-      <c r="K21" s="125"/>
-      <c r="L21" s="125"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="128"/>
+      <c r="L21" s="128"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="97"/>
@@ -6528,15 +6522,15 @@
       <c r="C22" s="81">
         <v>0</v>
       </c>
-      <c r="D22" s="124"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="124"/>
-      <c r="I22" s="124"/>
-      <c r="J22" s="124"/>
-      <c r="K22" s="124"/>
-      <c r="L22" s="124"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="127"/>
+      <c r="G22" s="127"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="127"/>
+      <c r="J22" s="127"/>
+      <c r="K22" s="127"/>
+      <c r="L22" s="127"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="97"/>
@@ -6544,15 +6538,15 @@
       <c r="C23" s="81">
         <v>0</v>
       </c>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="124"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="127"/>
+      <c r="L23" s="127"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="97"/>
@@ -6560,15 +6554,15 @@
       <c r="C24" s="81">
         <v>0</v>
       </c>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="124"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="127"/>
+      <c r="J24" s="127"/>
+      <c r="K24" s="127"/>
+      <c r="L24" s="127"/>
     </row>
     <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="77">
@@ -6615,17 +6609,17 @@
       <c r="C27" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="125" t="s">
+      <c r="D27" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="125"/>
-      <c r="F27" s="125"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="125"/>
-      <c r="I27" s="125"/>
-      <c r="J27" s="125"/>
-      <c r="K27" s="125"/>
-      <c r="L27" s="125"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="128"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="128"/>
+      <c r="L27" s="128"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="97"/>
@@ -6633,15 +6627,15 @@
       <c r="C28" s="81">
         <v>0</v>
       </c>
-      <c r="D28" s="124"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="124"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="124"/>
-      <c r="J28" s="124"/>
-      <c r="K28" s="124"/>
-      <c r="L28" s="124"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="127"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="127"/>
+      <c r="K28" s="127"/>
+      <c r="L28" s="127"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
@@ -6649,15 +6643,15 @@
       <c r="C29" s="81">
         <v>0</v>
       </c>
-      <c r="D29" s="124"/>
-      <c r="E29" s="124"/>
-      <c r="F29" s="124"/>
-      <c r="G29" s="124"/>
-      <c r="H29" s="124"/>
-      <c r="I29" s="124"/>
-      <c r="J29" s="124"/>
-      <c r="K29" s="124"/>
-      <c r="L29" s="124"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="127"/>
+      <c r="G29" s="127"/>
+      <c r="H29" s="127"/>
+      <c r="I29" s="127"/>
+      <c r="J29" s="127"/>
+      <c r="K29" s="127"/>
+      <c r="L29" s="127"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
@@ -6665,15 +6659,15 @@
       <c r="C30" s="81">
         <v>0</v>
       </c>
-      <c r="D30" s="124"/>
-      <c r="E30" s="124"/>
-      <c r="F30" s="124"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="124"/>
-      <c r="I30" s="124"/>
-      <c r="J30" s="124"/>
-      <c r="K30" s="124"/>
-      <c r="L30" s="124"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="127"/>
+      <c r="F30" s="127"/>
+      <c r="G30" s="127"/>
+      <c r="H30" s="127"/>
+      <c r="I30" s="127"/>
+      <c r="J30" s="127"/>
+      <c r="K30" s="127"/>
+      <c r="L30" s="127"/>
     </row>
     <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="77">
@@ -6720,17 +6714,17 @@
       <c r="C33" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="D33" s="125" t="s">
+      <c r="D33" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="125"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="125"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="125"/>
-      <c r="J33" s="125"/>
-      <c r="K33" s="125"/>
-      <c r="L33" s="125"/>
+      <c r="E33" s="128"/>
+      <c r="F33" s="128"/>
+      <c r="G33" s="128"/>
+      <c r="H33" s="128"/>
+      <c r="I33" s="128"/>
+      <c r="J33" s="128"/>
+      <c r="K33" s="128"/>
+      <c r="L33" s="128"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
@@ -6738,15 +6732,15 @@
       <c r="C34" s="81">
         <v>0</v>
       </c>
-      <c r="D34" s="124"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="124"/>
-      <c r="I34" s="124"/>
-      <c r="J34" s="124"/>
-      <c r="K34" s="124"/>
-      <c r="L34" s="124"/>
+      <c r="D34" s="127"/>
+      <c r="E34" s="127"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="127"/>
+      <c r="I34" s="127"/>
+      <c r="J34" s="127"/>
+      <c r="K34" s="127"/>
+      <c r="L34" s="127"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="97"/>
@@ -6754,15 +6748,15 @@
       <c r="C35" s="81">
         <v>0</v>
       </c>
-      <c r="D35" s="124"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="124"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="124"/>
-      <c r="I35" s="124"/>
-      <c r="J35" s="124"/>
-      <c r="K35" s="124"/>
-      <c r="L35" s="124"/>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="127"/>
+      <c r="J35" s="127"/>
+      <c r="K35" s="127"/>
+      <c r="L35" s="127"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="97"/>
@@ -6770,15 +6764,15 @@
       <c r="C36" s="81">
         <v>0</v>
       </c>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
+      <c r="D36" s="127"/>
+      <c r="E36" s="127"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="127"/>
+      <c r="H36" s="127"/>
+      <c r="I36" s="127"/>
+      <c r="J36" s="127"/>
+      <c r="K36" s="127"/>
+      <c r="L36" s="127"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="77">
@@ -6825,17 +6819,17 @@
       <c r="C39" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="D39" s="125" t="s">
+      <c r="D39" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="125"/>
-      <c r="F39" s="125"/>
-      <c r="G39" s="125"/>
-      <c r="H39" s="125"/>
-      <c r="I39" s="125"/>
-      <c r="J39" s="125"/>
-      <c r="K39" s="125"/>
-      <c r="L39" s="125"/>
+      <c r="E39" s="128"/>
+      <c r="F39" s="128"/>
+      <c r="G39" s="128"/>
+      <c r="H39" s="128"/>
+      <c r="I39" s="128"/>
+      <c r="J39" s="128"/>
+      <c r="K39" s="128"/>
+      <c r="L39" s="128"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="97"/>
@@ -6843,15 +6837,15 @@
       <c r="C40" s="81">
         <v>0</v>
       </c>
-      <c r="D40" s="124"/>
-      <c r="E40" s="124"/>
-      <c r="F40" s="124"/>
-      <c r="G40" s="124"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="124"/>
-      <c r="J40" s="124"/>
-      <c r="K40" s="124"/>
-      <c r="L40" s="124"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="127"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="127"/>
+      <c r="J40" s="127"/>
+      <c r="K40" s="127"/>
+      <c r="L40" s="127"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="97"/>
@@ -6859,15 +6853,15 @@
       <c r="C41" s="81">
         <v>0</v>
       </c>
-      <c r="D41" s="124"/>
-      <c r="E41" s="124"/>
-      <c r="F41" s="124"/>
-      <c r="G41" s="124"/>
-      <c r="H41" s="124"/>
-      <c r="I41" s="124"/>
-      <c r="J41" s="124"/>
-      <c r="K41" s="124"/>
-      <c r="L41" s="124"/>
+      <c r="D41" s="127"/>
+      <c r="E41" s="127"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="127"/>
+      <c r="K41" s="127"/>
+      <c r="L41" s="127"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="97"/>
@@ -6875,15 +6869,15 @@
       <c r="C42" s="81">
         <v>0</v>
       </c>
-      <c r="D42" s="124"/>
-      <c r="E42" s="124"/>
-      <c r="F42" s="124"/>
-      <c r="G42" s="124"/>
-      <c r="H42" s="124"/>
-      <c r="I42" s="124"/>
-      <c r="J42" s="124"/>
-      <c r="K42" s="124"/>
-      <c r="L42" s="124"/>
+      <c r="D42" s="127"/>
+      <c r="E42" s="127"/>
+      <c r="F42" s="127"/>
+      <c r="G42" s="127"/>
+      <c r="H42" s="127"/>
+      <c r="I42" s="127"/>
+      <c r="J42" s="127"/>
+      <c r="K42" s="127"/>
+      <c r="L42" s="127"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="95">
@@ -6896,36 +6890,42 @@
         <f>SUM(C40:C42)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="126"/>
-      <c r="E43" s="126"/>
-      <c r="F43" s="126"/>
-      <c r="G43" s="126"/>
-      <c r="H43" s="126"/>
-      <c r="I43" s="126"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="126"/>
-      <c r="L43" s="126"/>
+      <c r="D43" s="129"/>
+      <c r="E43" s="129"/>
+      <c r="F43" s="129"/>
+      <c r="G43" s="129"/>
+      <c r="H43" s="129"/>
+      <c r="I43" s="129"/>
+      <c r="J43" s="129"/>
+      <c r="K43" s="129"/>
+      <c r="L43" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="A6:L8"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D15:L15"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A6:L8"/>
-    <mergeCell ref="D10:L10"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="D33:L33"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D16:L16"/>
     <mergeCell ref="D17:L17"/>
     <mergeCell ref="D18:L18"/>
     <mergeCell ref="D22:L22"/>
     <mergeCell ref="D23:L23"/>
-    <mergeCell ref="D15:L15"/>
     <mergeCell ref="D21:L21"/>
     <mergeCell ref="D27:L27"/>
     <mergeCell ref="D24:L24"/>
@@ -6933,17 +6933,11 @@
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="D34:L34"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D39:L39"/>
-    <mergeCell ref="D33:L33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;C© www.banana.ch/it/it</oddFooter>
+    <oddFooter>&amp;C© www.banana.ch</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/noprofit/en/11255/inpag-template.xlsx
+++ b/noprofit/en/11255/inpag-template.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFC963B-0A3F-41F2-B0C0-4E6B10D440E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AA23B2-D226-46C1-97C1-0C1CEF0A1F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
   <sheets>
     <sheet name="General information" sheetId="7" r:id="rId1"/>
-    <sheet name="Statement of financial position" sheetId="1" r:id="rId2"/>
-    <sheet name="Income statement" sheetId="3" r:id="rId3"/>
-    <sheet name="Statement of changes in equity" sheetId="6" r:id="rId4"/>
-    <sheet name="Cash flow statement - indirect" sheetId="5" r:id="rId5"/>
-    <sheet name="Notes of financial statement" sheetId="4" r:id="rId6"/>
-    <sheet name="Notes of income statement" sheetId="10" r:id="rId7"/>
-    <sheet name="Notes of cash flow statement" sheetId="9" r:id="rId8"/>
+    <sheet name="Statement of Financial Position" sheetId="1" r:id="rId2"/>
+    <sheet name="Statement of Income &amp; Expenses" sheetId="3" r:id="rId3"/>
+    <sheet name="Statement of Changes NetAssets" sheetId="6" r:id="rId4"/>
+    <sheet name="Cash Flows Statement - indirect" sheetId="5" r:id="rId5"/>
+    <sheet name="Notes of Financial Statement" sheetId="4" r:id="rId6"/>
+    <sheet name="Notes of Income Statement" sheetId="10" r:id="rId7"/>
+    <sheet name="Notes of Cash flows statement" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash flow statement - indirect'!$A$1:$E$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash Flows Statement - indirect'!$A$1:$E$56</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'General information'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Notes of cash flow statement'!$A$1:$L$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Notes of financial statement'!$A$1:$D$83</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Notes of income statement'!$A$1:$D$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Statement of changes in equity'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Statement of financial position'!$A$1:$E$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Notes of Cash flows statement'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Notes of Financial Statement'!$A$1:$D$83</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Notes of Income Statement'!$A$1:$D$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Statement of Changes NetAssets'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Statement of Financial Position'!$A$1:$E$50</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -99,9 +99,6 @@
     <t>Description of nature of entity's operations and principal activities</t>
   </si>
   <si>
-    <t>Description of nature of entit's operation and activities (Activity A, B, C, D)</t>
-  </si>
-  <si>
     <t>During the financial year the principal continuing activities of the company</t>
   </si>
   <si>
@@ -126,27 +123,9 @@
     <t>Contents</t>
   </si>
   <si>
-    <t>Statement of financial position</t>
-  </si>
-  <si>
-    <t>Income statement</t>
-  </si>
-  <si>
-    <t>Statement of changes in equity</t>
-  </si>
-  <si>
-    <t>Cash flow statement - indirect</t>
-  </si>
-  <si>
     <t>Notes of Financial Statement</t>
   </si>
   <si>
-    <t>Notes of Income Statement</t>
-  </si>
-  <si>
-    <t>Notes of Cash Flow Statement</t>
-  </si>
-  <si>
     <t>Identifying information of no-profit</t>
   </si>
   <si>
@@ -393,9 +372,6 @@
     <t>EQB</t>
   </si>
   <si>
-    <t>Equity at beginning of period</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
@@ -414,18 +390,9 @@
     <t>Total comprehensive income</t>
   </si>
   <si>
-    <t>Increase (decrease) in equity</t>
-  </si>
-  <si>
-    <t>Total increase (decrease) in equity</t>
-  </si>
-  <si>
     <t>EQE</t>
   </si>
   <si>
-    <t>Equity at end of period</t>
-  </si>
-  <si>
     <t>PLC</t>
   </si>
   <si>
@@ -582,12 +549,6 @@
     <t>Total Description of acquisition of assets by assuming directly related liabilities or means of finance lease</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Description of acquisition of entity by means of equity issue </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Description of conversion of debt to equity </t>
-  </si>
-  <si>
     <t>Total Commentary by management on significant cash and cash equivalent balances held by entity that are not available for use by group</t>
   </si>
   <si>
@@ -636,21 +597,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Notes to the Cash flow Statement</t>
-  </si>
-  <si>
-    <t>Statement of Cash Flow, indirect method</t>
-  </si>
-  <si>
-    <t>Statement of Changes in Equity</t>
-  </si>
-  <si>
-    <t>Income Statement</t>
-  </si>
-  <si>
-    <t>Statement of Financial position, current/non-current</t>
-  </si>
-  <si>
     <t>General Information</t>
   </si>
   <si>
@@ -874,6 +820,60 @@
   </si>
   <si>
     <t>[-] Disposals</t>
+  </si>
+  <si>
+    <t>Statement of Changes in Net Assets</t>
+  </si>
+  <si>
+    <t>Net Assets at beginning of period</t>
+  </si>
+  <si>
+    <t>Increase (decrease) in Net Assets</t>
+  </si>
+  <si>
+    <t>Total increase (decrease) in Net Assets</t>
+  </si>
+  <si>
+    <t>Net Assets at end of period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of acquisition of entity by means of net assets issue </t>
+  </si>
+  <si>
+    <t>Description of conversion of debt to net assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Description of acquisition of entity by means of net assets issue </t>
+  </si>
+  <si>
+    <t>Total Description of conversion of debt to net assets</t>
+  </si>
+  <si>
+    <t>Notes to the Statement of Cash Flows</t>
+  </si>
+  <si>
+    <t>Notes of Statement of Income and Expenses</t>
+  </si>
+  <si>
+    <t>Statement of Cash Flows, indirect method</t>
+  </si>
+  <si>
+    <t>Statement of Income and Expenses</t>
+  </si>
+  <si>
+    <t>Statement of Financial Position</t>
+  </si>
+  <si>
+    <t>Statement of Cash Flows - indirect</t>
+  </si>
+  <si>
+    <t>Notes of Statement of Financial Position</t>
+  </si>
+  <si>
+    <t>Notes of Statement of Cash Flows</t>
+  </si>
+  <si>
+    <t>Description of nature of entity's operation and activities (Activity A, B, C, D)</t>
   </si>
 </sst>
 </file>
@@ -1360,6 +1360,18 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1369,18 +1381,6 @@
     <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1405,47 +1405,47 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1837,7 +1837,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="102" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="102"/>
@@ -1955,7 +1955,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="101" t="s">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="C10" s="101"/>
       <c r="D10" s="101"/>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="101" t="s">
         <v>16</v>
-      </c>
-      <c r="B17" s="101" t="s">
-        <v>17</v>
       </c>
       <c r="C17" s="101"/>
       <c r="D17" s="101"/>
@@ -2033,7 +2033,7 @@
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="96"/>
       <c r="B18" s="101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="101"/>
       <c r="D18" s="101"/>
@@ -2044,7 +2044,7 @@
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="96"/>
       <c r="B19" s="101" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="101"/>
       <c r="D19" s="101"/>
@@ -2055,7 +2055,7 @@
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="96"/>
       <c r="B20" s="101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="101"/>
       <c r="D20" s="101"/>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="96" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="101" t="s">
         <v>21</v>
-      </c>
-      <c r="B21" s="101" t="s">
-        <v>22</v>
       </c>
       <c r="C21" s="101"/>
       <c r="D21" s="101"/>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="101" t="s">
-        <v>24</v>
+        <v>269</v>
       </c>
       <c r="C22" s="101"/>
       <c r="D22" s="101"/>
@@ -2092,7 +2092,7 @@
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="96"/>
       <c r="B23" s="101" t="s">
-        <v>25</v>
+        <v>268</v>
       </c>
       <c r="C23" s="101"/>
       <c r="D23" s="101"/>
@@ -2103,7 +2103,7 @@
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="96"/>
       <c r="B24" s="101" t="s">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="C24" s="101"/>
       <c r="D24" s="101"/>
@@ -2114,7 +2114,7 @@
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="96"/>
       <c r="B25" s="101" t="s">
-        <v>27</v>
+        <v>270</v>
       </c>
       <c r="C25" s="101"/>
       <c r="D25" s="101"/>
@@ -2125,7 +2125,7 @@
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="96"/>
       <c r="B26" s="101" t="s">
-        <v>28</v>
+        <v>271</v>
       </c>
       <c r="C26" s="101"/>
       <c r="D26" s="101"/>
@@ -2136,7 +2136,7 @@
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="96"/>
       <c r="B27" s="101" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="C27" s="101"/>
       <c r="D27" s="101"/>
@@ -2147,7 +2147,7 @@
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="96"/>
       <c r="B28" s="101" t="s">
-        <v>30</v>
+        <v>272</v>
       </c>
       <c r="C28" s="101"/>
       <c r="D28" s="101"/>
@@ -2157,12 +2157,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2179,6 +2173,12 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2207,94 +2207,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="A1" s="109" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D9" s="74">
         <f>$B$4</f>
@@ -2307,19 +2307,19 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="110" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
+      <c r="B10" s="107" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="107"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C11" s="90">
         <v>1</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="12" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C12" s="90">
         <v>2</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="13" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C13" s="90">
         <v>3</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="14" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C14" s="90">
         <v>4</v>
@@ -2385,7 +2385,7 @@
     <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="44"/>
       <c r="B15" s="54" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C15" s="44"/>
       <c r="D15" s="62">
@@ -2406,19 +2406,19 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44"/>
-      <c r="B17" s="110" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
+      <c r="B17" s="107" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C18" s="90">
         <v>5</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C19" s="90">
         <v>6</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="20" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C20" s="90">
         <v>7</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="21" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C21" s="90">
         <v>8</v>
@@ -2484,7 +2484,7 @@
     <row r="22" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
       <c r="B22" s="54" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C22" s="44"/>
       <c r="D22" s="63">
@@ -2499,7 +2499,7 @@
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
       <c r="B23" s="54" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C23" s="45"/>
       <c r="D23" s="63">
@@ -2520,13 +2520,13 @@
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="74" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D25" s="74">
         <f>$B$4</f>
@@ -2539,19 +2539,19 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="110" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
+      <c r="B26" s="107" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="107"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="C27" s="90">
         <v>9</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C28" s="90">
         <v>10</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="44" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="C29" s="90">
         <v>11</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="30" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="44" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C30" s="90">
         <v>12</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="31" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C31" s="90">
         <v>13</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="32" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C32" s="90">
         <v>14</v>
@@ -2651,7 +2651,7 @@
     <row r="33" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
       <c r="B33" s="54" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C33" s="44"/>
       <c r="D33" s="62">
@@ -2672,19 +2672,19 @@
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="44"/>
-      <c r="B35" s="110" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
+      <c r="B35" s="107" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="107"/>
     </row>
     <row r="36" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C36" s="90">
         <v>15</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="44" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C37" s="90">
         <v>16</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C38" s="90">
         <v>17</v>
@@ -2733,7 +2733,7 @@
     <row r="39" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A39" s="44"/>
       <c r="B39" s="54" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="62">
@@ -2754,19 +2754,19 @@
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="44"/>
-      <c r="B41" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="110"/>
-      <c r="D41" s="110"/>
-      <c r="E41" s="110"/>
+      <c r="B41" s="107" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="107"/>
+      <c r="D41" s="107"/>
+      <c r="E41" s="107"/>
     </row>
     <row r="42" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C42" s="90">
         <v>18</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="43" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C43" s="90">
         <v>19</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C44" s="90">
         <v>20</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="45" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C45" s="90">
         <v>21</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="46" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C46" s="90">
         <v>22</v>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="47" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C47" s="90">
         <v>23</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="48" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C48" s="90">
         <v>24</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
-      <c r="B49" s="110" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" s="110"/>
+      <c r="B49" s="107" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="107"/>
       <c r="D49" s="62">
         <f>SUM(D42:D48)</f>
         <v>0</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
-      <c r="B50" s="110" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="110"/>
+      <c r="B50" s="107" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="107"/>
       <c r="D50" s="62">
         <f>SUM(D33,D39,D49)</f>
         <v>0</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="60" t="s">
-        <v>82</v>
-      </c>
-      <c r="B53" s="109" t="str">
+        <v>75</v>
+      </c>
+      <c r="B53" s="106" t="str">
         <f>IF((D15+D23+D33=D39+D49),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="109"/>
+      <c r="C53" s="106"/>
       <c r="D53" s="53">
         <f>D50-D23</f>
         <v>0</v>
@@ -2940,14 +2940,14 @@
     </row>
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="61" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="108" t="str">
+        <v>75</v>
+      </c>
+      <c r="B54" s="105" t="str">
         <f>IF((E15+E23+E33=E39+E49),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C54" s="108"/>
-      <c r="D54" s="108"/>
+      <c r="C54" s="105"/>
+      <c r="D54" s="105"/>
       <c r="E54" s="53">
         <f>E50-E23</f>
         <v>0</v>
@@ -2961,6 +2961,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B53:C53"/>
@@ -2971,11 +2976,6 @@
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B53">
@@ -3030,7 +3030,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="111" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B1" s="111"/>
       <c r="C1" s="111"/>
@@ -3088,37 +3088,37 @@
       <c r="E5" s="113"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>197</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D9" s="84">
         <f>$B$4</f>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="10" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C10" s="91">
         <v>25</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="11" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C11" s="91">
         <v>26</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="12" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="C12" s="91">
         <v>27</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="13" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C13" s="91">
         <v>28</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="14" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="C14" s="91">
         <v>29</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="15" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="C15" s="91">
         <v>30</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="16" spans="1:7" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C16" s="91">
         <v>31</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="17" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C17" s="91">
         <v>32</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C18" s="91">
         <v>33</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="19" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C19" s="91">
         <v>34</v>
@@ -3302,7 +3302,7 @@
     <row r="20" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="47"/>
       <c r="B20" s="64" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C20" s="64"/>
       <c r="D20" s="65">
@@ -3323,13 +3323,13 @@
     </row>
     <row r="22" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="74" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D22" s="84">
         <f>$B$4</f>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="23" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="C23" s="91">
         <v>35</v>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="24" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C24" s="91">
         <v>36</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="25" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="C25" s="91">
         <v>37</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="26" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="47" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="C26" s="91">
         <v>38</v>
@@ -3410,10 +3410,10 @@
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C27" s="91">
         <v>39</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="47" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C28" s="91">
         <v>40</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C29" s="91">
         <v>41</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="47" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C30" s="91">
         <v>42</v>
@@ -3479,7 +3479,7 @@
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="47"/>
       <c r="B31" s="64" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C31" s="64"/>
       <c r="D31" s="65">
@@ -3500,13 +3500,13 @@
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="74" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D33" s="84">
         <f>$B$4</f>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="47" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="C34" s="91">
         <v>43</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="47" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="C35" s="91">
         <v>44</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="47" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C36" s="91">
         <v>45</v>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="C37" s="91">
         <v>46</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="C38" s="91">
         <v>47</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="C39" s="91">
         <v>48</v>
@@ -3622,7 +3622,7 @@
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="47"/>
       <c r="B40" s="86" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C40" s="86"/>
       <c r="D40" s="87">
@@ -3637,7 +3637,7 @@
     <row r="41" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="64" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C41" s="64"/>
       <c r="D41" s="66">
@@ -3688,13 +3688,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="105" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="A1" s="109" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3703,79 +3703,79 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="107" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B9" s="75" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C9" s="75"/>
       <c r="D9" s="74">
@@ -3789,10 +3789,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="44" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B10" s="114" t="s">
-        <v>113</v>
+        <v>257</v>
       </c>
       <c r="C10" s="114"/>
       <c r="D10" s="14">
@@ -3809,10 +3809,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="74" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B12" s="75" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C12" s="75"/>
       <c r="D12" s="74">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="44" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B13" s="116" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C13" s="116"/>
       <c r="D13" s="116"/>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="44" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B14" s="116" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C14" s="116"/>
       <c r="D14" s="116"/>
@@ -3853,7 +3853,7 @@
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="44"/>
       <c r="B15" s="115" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C15" s="115"/>
       <c r="D15" s="115"/>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="76">
@@ -3888,10 +3888,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="117" t="s">
         <v>236</v>
-      </c>
-      <c r="B18" s="117" t="s">
-        <v>254</v>
       </c>
       <c r="C18" s="117"/>
       <c r="D18" s="117"/>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="117" t="s">
         <v>237</v>
-      </c>
-      <c r="B19" s="117" t="s">
-        <v>255</v>
       </c>
       <c r="C19" s="117"/>
       <c r="D19" s="117"/>
@@ -3914,10 +3914,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" s="117" t="s">
         <v>238</v>
-      </c>
-      <c r="B20" s="117" t="s">
-        <v>256</v>
       </c>
       <c r="C20" s="117"/>
       <c r="D20" s="117"/>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="21" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B21" s="117" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="C21" s="117"/>
       <c r="D21" s="117"/>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B22" s="116" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C22" s="116"/>
       <c r="D22" s="116"/>
@@ -3954,7 +3954,7 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
       <c r="B23" s="115" t="s">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="C23" s="115"/>
       <c r="D23" s="115"/>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>123</v>
+        <v>260</v>
       </c>
       <c r="C25" s="115"/>
       <c r="D25" s="115"/>
@@ -3987,6 +3987,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B25:D25"/>
@@ -3999,11 +4004,6 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -4030,96 +4030,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="105" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
+      <c r="A1" s="109" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>195</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="119" t="s">
-        <v>180</v>
-      </c>
-      <c r="C9" s="119"/>
+        <v>106</v>
+      </c>
+      <c r="B9" s="120" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="120"/>
       <c r="D9" s="74" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E9" s="74">
         <f>$B$5</f>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="110" t="s">
-        <v>181</v>
-      </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
+        <v>113</v>
+      </c>
+      <c r="B10" s="107" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
       <c r="E10" s="22">
         <v>0</v>
       </c>
@@ -4148,14 +4148,14 @@
     </row>
     <row r="12" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="120" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="119" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="120"/>
       <c r="D12" s="74" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E12" s="74">
         <f>$B$5</f>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="13" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B13" s="117" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C13" s="117"/>
       <c r="D13" s="90"/>
@@ -4177,10 +4177,10 @@
     </row>
     <row r="14" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="B14" s="117" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C14" s="117"/>
       <c r="D14" s="90"/>
@@ -4190,10 +4190,10 @@
     </row>
     <row r="15" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="B15" s="117" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C15" s="117"/>
       <c r="D15" s="90"/>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="16" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B16" s="117" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C16" s="117"/>
       <c r="D16" s="90"/>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="17" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B17" s="117" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="C17" s="117"/>
       <c r="D17" s="90"/>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="18" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B18" s="117" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="C18" s="117"/>
       <c r="D18" s="90"/>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="19" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="B19" s="117" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C19" s="117"/>
       <c r="D19" s="90"/>
@@ -4259,10 +4259,10 @@
     </row>
     <row r="20" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B20" s="117" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="C20" s="117"/>
       <c r="D20" s="90"/>
@@ -4273,12 +4273,12 @@
     </row>
     <row r="21" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
-        <v>204</v>
-      </c>
-      <c r="B21" s="120" t="s">
-        <v>261</v>
-      </c>
-      <c r="C21" s="120"/>
+        <v>186</v>
+      </c>
+      <c r="B21" s="119" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" s="119"/>
       <c r="D21" s="90"/>
       <c r="E21" s="22">
         <v>0</v>
@@ -4287,12 +4287,12 @@
     </row>
     <row r="22" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="B22" s="120" t="s">
-        <v>262</v>
-      </c>
-      <c r="C22" s="120"/>
+        <v>187</v>
+      </c>
+      <c r="B22" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="119"/>
       <c r="D22" s="90"/>
       <c r="E22" s="22">
         <v>0</v>
@@ -4301,12 +4301,12 @@
     </row>
     <row r="23" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="B23" s="120" t="s">
-        <v>263</v>
-      </c>
-      <c r="C23" s="120"/>
+        <v>188</v>
+      </c>
+      <c r="B23" s="119" t="s">
+        <v>245</v>
+      </c>
+      <c r="C23" s="119"/>
       <c r="D23" s="90"/>
       <c r="E23" s="22">
         <v>0</v>
@@ -4315,12 +4315,12 @@
     </row>
     <row r="24" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" s="120" t="s">
-        <v>264</v>
-      </c>
-      <c r="C24" s="120"/>
+        <v>189</v>
+      </c>
+      <c r="B24" s="119" t="s">
+        <v>246</v>
+      </c>
+      <c r="C24" s="119"/>
       <c r="D24" s="90"/>
       <c r="E24" s="22">
         <v>0</v>
@@ -4329,11 +4329,11 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="110" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
+      <c r="B25" s="107" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
       <c r="E25" s="62">
         <f>E10+SUM(E13:E24)</f>
         <v>0</v>
@@ -4348,14 +4348,14 @@
     </row>
     <row r="27" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="119" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" s="119"/>
+        <v>106</v>
+      </c>
+      <c r="B27" s="120" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="120"/>
       <c r="D27" s="74" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E27" s="74">
         <f>$B$5</f>
@@ -4364,12 +4364,12 @@
     </row>
     <row r="28" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="B28" s="120" t="s">
-        <v>271</v>
-      </c>
-      <c r="C28" s="120"/>
+        <v>190</v>
+      </c>
+      <c r="B28" s="119" t="s">
+        <v>253</v>
+      </c>
+      <c r="C28" s="119"/>
       <c r="D28" s="90"/>
       <c r="E28" s="22">
         <v>0</v>
@@ -4377,12 +4377,12 @@
     </row>
     <row r="29" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="44" t="s">
-        <v>209</v>
-      </c>
-      <c r="B29" s="120" t="s">
-        <v>272</v>
-      </c>
-      <c r="C29" s="120"/>
+        <v>191</v>
+      </c>
+      <c r="B29" s="119" t="s">
+        <v>254</v>
+      </c>
+      <c r="C29" s="119"/>
       <c r="D29" s="90"/>
       <c r="E29" s="22">
         <v>0</v>
@@ -4390,12 +4390,12 @@
     </row>
     <row r="30" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
-        <v>210</v>
-      </c>
-      <c r="B30" s="120" t="s">
-        <v>266</v>
-      </c>
-      <c r="C30" s="120"/>
+        <v>192</v>
+      </c>
+      <c r="B30" s="119" t="s">
+        <v>248</v>
+      </c>
+      <c r="C30" s="119"/>
       <c r="D30" s="90"/>
       <c r="E30" s="22">
         <v>0</v>
@@ -4403,12 +4403,12 @@
     </row>
     <row r="31" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="44" t="s">
-        <v>211</v>
-      </c>
-      <c r="B31" s="120" t="s">
-        <v>273</v>
-      </c>
-      <c r="C31" s="120"/>
+        <v>193</v>
+      </c>
+      <c r="B31" s="119" t="s">
+        <v>255</v>
+      </c>
+      <c r="C31" s="119"/>
       <c r="D31" s="90"/>
       <c r="E31" s="22">
         <v>0</v>
@@ -4416,11 +4416,11 @@
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="110" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" s="110"/>
-      <c r="D32" s="110"/>
+      <c r="B32" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
       <c r="E32" s="62">
         <f>E10+E25+SUM(E28:E31)</f>
         <v>0</v>
@@ -4435,14 +4435,14 @@
     </row>
     <row r="34" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="119" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="119"/>
+        <v>106</v>
+      </c>
+      <c r="B34" s="120" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="120"/>
       <c r="D34" s="74" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E34" s="74">
         <f>$B$5</f>
@@ -4452,12 +4452,12 @@
     </row>
     <row r="35" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="B35" s="120" t="s">
-        <v>267</v>
-      </c>
-      <c r="C35" s="120"/>
+        <v>194</v>
+      </c>
+      <c r="B35" s="119" t="s">
+        <v>249</v>
+      </c>
+      <c r="C35" s="119"/>
       <c r="D35" s="90"/>
       <c r="E35" s="22">
         <v>0</v>
@@ -4465,12 +4465,12 @@
     </row>
     <row r="36" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="44" t="s">
-        <v>213</v>
-      </c>
-      <c r="B36" s="120" t="s">
-        <v>268</v>
-      </c>
-      <c r="C36" s="120"/>
+        <v>195</v>
+      </c>
+      <c r="B36" s="119" t="s">
+        <v>250</v>
+      </c>
+      <c r="C36" s="119"/>
       <c r="D36" s="90"/>
       <c r="E36" s="22">
         <v>0</v>
@@ -4478,12 +4478,12 @@
     </row>
     <row r="37" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="44" t="s">
-        <v>214</v>
-      </c>
-      <c r="B37" s="120" t="s">
-        <v>269</v>
-      </c>
-      <c r="C37" s="120"/>
+        <v>196</v>
+      </c>
+      <c r="B37" s="119" t="s">
+        <v>251</v>
+      </c>
+      <c r="C37" s="119"/>
       <c r="D37" s="90"/>
       <c r="E37" s="22">
         <v>0</v>
@@ -4491,11 +4491,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
-      <c r="B38" s="110" t="s">
-        <v>129</v>
-      </c>
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
+      <c r="B38" s="107" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
       <c r="E38" s="62">
         <f>E10+E25+E32+SUM(E35:E37)</f>
         <v>0</v>
@@ -4510,11 +4510,11 @@
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
-      <c r="B40" s="110" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="110"/>
-      <c r="D40" s="110"/>
+      <c r="B40" s="107" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="107"/>
+      <c r="D40" s="107"/>
       <c r="E40" s="62">
         <f>SUM(E25,E32,E38)</f>
         <v>0</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B42" s="118" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C42" s="118"/>
       <c r="D42" s="26"/>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="B43" s="118" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="C43" s="118"/>
       <c r="D43" s="26"/>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="B44" s="118" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="C44" s="118"/>
       <c r="D44" s="26"/>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
-      <c r="B45" s="110" t="s">
-        <v>131</v>
-      </c>
-      <c r="C45" s="110"/>
+      <c r="B45" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="107"/>
       <c r="D45" s="93">
         <v>49</v>
       </c>
@@ -4582,35 +4582,35 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
-      <c r="B46" s="110" t="s">
-        <v>132</v>
-      </c>
-      <c r="C46" s="110"/>
-      <c r="D46" s="110"/>
+      <c r="B46" s="107" t="s">
+        <v>121</v>
+      </c>
+      <c r="C46" s="107"/>
+      <c r="D46" s="107"/>
       <c r="E46" s="69">
-        <f>'Statement of financial position'!D22</f>
+        <f>'Statement of Financial Position'!D22</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
-      <c r="B47" s="110" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" s="110"/>
-      <c r="D47" s="110"/>
+      <c r="B47" s="107" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="107"/>
+      <c r="D47" s="107"/>
       <c r="E47" s="69">
-        <f>'Statement of financial position'!E22</f>
+        <f>'Statement of Financial Position'!E22</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
-      <c r="B48" s="110" t="s">
-        <v>134</v>
-      </c>
-      <c r="C48" s="110"/>
-      <c r="D48" s="110"/>
+      <c r="B48" s="107" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="107"/>
+      <c r="D48" s="107"/>
       <c r="E48" s="69">
         <f>E47-E46</f>
         <v>0</v>
@@ -4633,7 +4633,7 @@
     <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A51" s="31"/>
       <c r="B51" s="57" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C51" s="31"/>
       <c r="D51" s="31"/>
@@ -4642,7 +4642,7 @@
     <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="31"/>
       <c r="B52" s="118" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C52" s="118"/>
       <c r="D52" s="90">
@@ -4653,7 +4653,7 @@
     <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A53" s="31"/>
       <c r="B53" s="118" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C53" s="118"/>
       <c r="D53" s="90">
@@ -4664,7 +4664,7 @@
     <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="31"/>
       <c r="B54" s="118" t="s">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="C54" s="118"/>
       <c r="D54" s="90">
@@ -4675,7 +4675,7 @@
     <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
       <c r="B55" s="118" t="s">
-        <v>139</v>
+        <v>262</v>
       </c>
       <c r="C55" s="118"/>
       <c r="D55" s="90">
@@ -4686,7 +4686,7 @@
     <row r="56" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31"/>
       <c r="B56" s="118" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C56" s="118"/>
       <c r="D56" s="90">
@@ -4710,18 +4710,25 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B32:D32"/>
@@ -4738,25 +4745,18 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -4782,85 +4782,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="121" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
+      <c r="A1" s="124" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="123" t="s">
-        <v>141</v>
-      </c>
-      <c r="B9" s="123"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="123"/>
+      <c r="A9" s="125" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="122"/>
@@ -4881,34 +4881,34 @@
       <c r="D12" s="122"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="124"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
+      <c r="A13" s="123"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="123"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="124"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
+      <c r="A14" s="123"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="123"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="124"/>
-      <c r="B15" s="124"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
+      <c r="A15" s="123"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="123"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124"/>
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
+      <c r="A16" s="123"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="124"/>
-      <c r="B17" s="124"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="124"/>
+      <c r="A17" s="123"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="123"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="122"/>
@@ -4977,23 +4977,23 @@
       <c r="D28" s="122"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="125"/>
-      <c r="B29" s="125"/>
-      <c r="C29" s="125"/>
-      <c r="D29" s="125"/>
+      <c r="A29" s="121"/>
+      <c r="B29" s="121"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="121"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="74" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C31" s="22">
         <v>0</v>
@@ -5013,17 +5013,17 @@
         <v>2</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C32" s="70"/>
       <c r="D32" s="89"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C33" s="22">
         <v>0</v>
@@ -5035,7 +5035,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C34" s="22">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C35" s="23">
         <v>0</v>
@@ -5059,7 +5059,7 @@
         <v>2.4</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C36" s="22">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>2.5</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C37" s="22">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>2.6</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C38" s="22">
         <v>0</v>
@@ -5095,7 +5095,7 @@
         <v>2.7</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C39" s="22">
         <v>0</v>
@@ -5107,7 +5107,7 @@
         <v>2.8</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C40" s="22">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>2.9</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C41" s="22">
         <v>0</v>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="C42" s="22">
         <v>0</v>
@@ -5140,10 +5140,10 @@
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C43" s="22">
         <v>0</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C44" s="22">
         <v>0</v>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="33" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C45" s="22">
         <v>0</v>
@@ -5176,10 +5176,10 @@
     </row>
     <row r="46" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C46" s="22">
         <v>0</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C47" s="22">
         <v>0</v>
@@ -5201,7 +5201,7 @@
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33"/>
       <c r="B48" s="45" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="C48" s="62">
         <f>SUM(C33:C47)</f>
@@ -5214,7 +5214,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="44" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C49" s="23">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="44" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C50" s="23">
         <v>0</v>
@@ -5236,7 +5236,7 @@
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="94"/>
       <c r="B51" s="45" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C51" s="62">
         <f>SUM($C31+$C48+$C49+$C50)</f>
@@ -5252,16 +5252,16 @@
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="74" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5269,7 +5269,7 @@
         <v>5</v>
       </c>
       <c r="B54" s="44" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C54" s="23">
         <v>0</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="40" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B55" s="44" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C55" s="23">
         <v>0</v>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="40" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B56" s="44" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C56" s="23">
         <v>0</v>
@@ -5302,10 +5302,10 @@
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="42" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B57" s="44" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C57" s="23">
         <v>0</v>
@@ -5315,7 +5315,7 @@
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="43"/>
       <c r="B58" s="45" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C58" s="62">
         <f>SUM(C54:C57)</f>
@@ -5331,24 +5331,24 @@
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="74" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="40" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="C61" s="23">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>10</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C62" s="23">
         <v>0</v>
@@ -5372,7 +5372,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="C63" s="23">
         <v>0</v>
@@ -5384,7 +5384,7 @@
         <v>12</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C64" s="23">
         <v>0</v>
@@ -5396,7 +5396,7 @@
         <v>13</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C65" s="23">
         <v>0</v>
@@ -5408,7 +5408,7 @@
         <v>14</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C66" s="23">
         <v>0</v>
@@ -5418,7 +5418,7 @@
     <row r="67" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A67" s="32"/>
       <c r="B67" s="54" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C67" s="71">
         <f>SUM(C61:C66)</f>
@@ -5434,16 +5434,16 @@
     </row>
     <row r="69" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A69" s="74" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
@@ -5451,7 +5451,7 @@
         <v>15</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C70" s="88">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="38" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C71" s="88">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>17</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C72" s="14">
         <v>0</v>
@@ -5485,7 +5485,7 @@
     <row r="73" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A73" s="32"/>
       <c r="B73" s="54" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C73" s="63">
         <f>SUM($C70:$C72)</f>
@@ -5501,16 +5501,16 @@
     </row>
     <row r="75" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A75" s="74" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
@@ -5518,7 +5518,7 @@
         <v>18</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C76" s="14">
         <v>0</v>
@@ -5530,7 +5530,7 @@
         <v>19</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C77" s="14">
         <v>0</v>
@@ -5542,7 +5542,7 @@
         <v>20</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C78" s="14">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>21</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C79" s="14">
         <v>0</v>
@@ -5566,7 +5566,7 @@
         <v>22</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C80" s="14">
         <v>0</v>
@@ -5578,7 +5578,7 @@
         <v>23</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C81" s="14">
         <v>0</v>
@@ -5590,7 +5590,7 @@
         <v>24</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C82" s="14">
         <v>0</v>
@@ -5600,7 +5600,7 @@
     <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A83" s="32"/>
       <c r="B83" s="45" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C83" s="63">
         <f>SUM($C76:$C82)</f>
@@ -5610,18 +5610,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5637,6 +5625,18 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5667,7 +5667,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="126" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -5678,78 +5678,78 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="108" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="str">
+      <c r="B3" s="108" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="110">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="110">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
+      <c r="A6" s="104" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C9" s="85" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5757,7 +5757,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C10" s="23">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C11" s="23">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="C12" s="23">
         <v>0</v>
@@ -5793,7 +5793,7 @@
         <v>28</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C13" s="23">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="C14" s="23">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>30</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="C15" s="23">
         <v>0</v>
@@ -5829,7 +5829,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C16" s="23">
         <v>0</v>
@@ -5841,7 +5841,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C17" s="23">
         <v>0</v>
@@ -5853,7 +5853,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C18" s="23">
         <v>0</v>
@@ -5865,7 +5865,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C19" s="23">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41"/>
       <c r="B20" s="54" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C20" s="62">
         <f>SUM(C10:C19)</f>
@@ -5891,16 +5891,16 @@
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C22" s="85" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5908,7 +5908,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="C23" s="23">
         <v>0</v>
@@ -5920,7 +5920,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C24" s="23">
         <v>0</v>
@@ -5932,7 +5932,7 @@
         <v>37</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="C25" s="23">
         <v>0</v>
@@ -5944,7 +5944,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="C26" s="23">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>39</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C27" s="23">
         <v>0</v>
@@ -5968,7 +5968,7 @@
         <v>40</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C28" s="23">
         <v>0</v>
@@ -5980,7 +5980,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C29" s="23">
         <v>0</v>
@@ -5992,7 +5992,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C30" s="23">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="39"/>
       <c r="B31" s="72" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C31" s="73">
         <f>SUM(C11:C28)</f>
@@ -6018,16 +6018,16 @@
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C33" s="99" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6035,7 +6035,7 @@
         <v>43</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="C34" s="23">
         <v>0</v>
@@ -6047,7 +6047,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="C35" s="23">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>45</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C36" s="23">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         <v>46</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="C37" s="23">
         <v>0</v>
@@ -6083,7 +6083,7 @@
         <v>47</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="C38" s="23">
         <v>0</v>
@@ -6095,7 +6095,7 @@
         <v>48</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="C39" s="23">
         <v>0</v>
@@ -6105,7 +6105,7 @@
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="30"/>
       <c r="B40" s="35" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="C40" s="63">
         <f>SUM(C34:C39)</f>
@@ -6150,7 +6150,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="126" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -6241,70 +6241,70 @@
       <c r="L5" s="131"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="132" t="s">
-        <v>194</v>
-      </c>
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132"/>
-      <c r="G6" s="132"/>
-      <c r="H6" s="132"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="132"/>
-      <c r="L6" s="132"/>
+      <c r="A6" s="127" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="127"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="132"/>
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
+      <c r="A7" s="127"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="132"/>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="132"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="127"/>
+      <c r="L8" s="127"/>
     </row>
     <row r="9" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="78" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C9" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="128" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="128"/>
-      <c r="L9" s="128"/>
+        <v>133</v>
+      </c>
+      <c r="D9" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="129"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="129"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="97"/>
@@ -6312,15 +6312,15 @@
       <c r="C10" s="81">
         <v>0</v>
       </c>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
-      <c r="L10" s="127"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="97"/>
@@ -6328,15 +6328,15 @@
       <c r="C11" s="81">
         <v>0</v>
       </c>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="97"/>
@@ -6344,22 +6344,22 @@
       <c r="C12" s="81">
         <v>0</v>
       </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="127"/>
-      <c r="L12" s="127"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="128"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="77">
         <v>49</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C13" s="63">
         <f>SUM(C10:C12)</f>
@@ -6391,25 +6391,25 @@
     </row>
     <row r="15" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="78" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C15" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="D15" s="128" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="128"/>
-      <c r="L15" s="128"/>
+        <v>133</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="129"/>
+      <c r="K15" s="129"/>
+      <c r="L15" s="129"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="97"/>
@@ -6417,15 +6417,15 @@
       <c r="C16" s="81">
         <v>0</v>
       </c>
-      <c r="D16" s="127"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="127"/>
-      <c r="L16" s="127"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="128"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="97"/>
@@ -6433,15 +6433,15 @@
       <c r="C17" s="81">
         <v>0</v>
       </c>
-      <c r="D17" s="127"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="127"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="97"/>
@@ -6449,22 +6449,22 @@
       <c r="C18" s="81">
         <v>0</v>
       </c>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
+      <c r="D18" s="128"/>
+      <c r="E18" s="128"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="128"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="128"/>
+      <c r="L18" s="128"/>
     </row>
     <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="77">
         <v>50</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C19" s="82">
         <f>SUM(C16:C18)</f>
@@ -6496,25 +6496,25 @@
     </row>
     <row r="21" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="78" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C21" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="D21" s="128" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="128"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="128"/>
-      <c r="L21" s="128"/>
+        <v>133</v>
+      </c>
+      <c r="D21" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="129"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="129"/>
+      <c r="K21" s="129"/>
+      <c r="L21" s="129"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="97"/>
@@ -6522,15 +6522,15 @@
       <c r="C22" s="81">
         <v>0</v>
       </c>
-      <c r="D22" s="127"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="127"/>
-      <c r="K22" s="127"/>
-      <c r="L22" s="127"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="128"/>
+      <c r="H22" s="128"/>
+      <c r="I22" s="128"/>
+      <c r="J22" s="128"/>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="97"/>
@@ -6538,15 +6538,15 @@
       <c r="C23" s="81">
         <v>0</v>
       </c>
-      <c r="D23" s="127"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="127"/>
-      <c r="K23" s="127"/>
-      <c r="L23" s="127"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="128"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="97"/>
@@ -6554,22 +6554,22 @@
       <c r="C24" s="81">
         <v>0</v>
       </c>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="127"/>
-      <c r="J24" s="127"/>
-      <c r="K24" s="127"/>
-      <c r="L24" s="127"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
     </row>
     <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="77">
         <v>51</v>
       </c>
       <c r="B25" s="54" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C25" s="82">
         <f>SUM(C22:C24)</f>
@@ -6601,25 +6601,25 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="78" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B27" s="80" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C27" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="D27" s="128" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="128"/>
-      <c r="F27" s="128"/>
-      <c r="G27" s="128"/>
-      <c r="H27" s="128"/>
-      <c r="I27" s="128"/>
-      <c r="J27" s="128"/>
-      <c r="K27" s="128"/>
-      <c r="L27" s="128"/>
+        <v>133</v>
+      </c>
+      <c r="D27" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="129"/>
+      <c r="F27" s="129"/>
+      <c r="G27" s="129"/>
+      <c r="H27" s="129"/>
+      <c r="I27" s="129"/>
+      <c r="J27" s="129"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="129"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="97"/>
@@ -6627,15 +6627,15 @@
       <c r="C28" s="81">
         <v>0</v>
       </c>
-      <c r="D28" s="127"/>
-      <c r="E28" s="127"/>
-      <c r="F28" s="127"/>
-      <c r="G28" s="127"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="127"/>
-      <c r="K28" s="127"/>
-      <c r="L28" s="127"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="128"/>
+      <c r="G28" s="128"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="128"/>
+      <c r="L28" s="128"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
@@ -6643,15 +6643,15 @@
       <c r="C29" s="81">
         <v>0</v>
       </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="127"/>
-      <c r="K29" s="127"/>
-      <c r="L29" s="127"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="128"/>
+      <c r="L29" s="128"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
@@ -6659,22 +6659,22 @@
       <c r="C30" s="81">
         <v>0</v>
       </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="127"/>
-      <c r="G30" s="127"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="127"/>
-      <c r="J30" s="127"/>
-      <c r="K30" s="127"/>
-      <c r="L30" s="127"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="128"/>
+      <c r="I30" s="128"/>
+      <c r="J30" s="128"/>
+      <c r="K30" s="128"/>
+      <c r="L30" s="128"/>
     </row>
     <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="77">
         <v>52</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>176</v>
+        <v>263</v>
       </c>
       <c r="C31" s="82">
         <f>SUM(C28:C30)</f>
@@ -6706,25 +6706,25 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="78" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B33" s="80" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C33" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="128" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="128"/>
-      <c r="F33" s="128"/>
-      <c r="G33" s="128"/>
-      <c r="H33" s="128"/>
-      <c r="I33" s="128"/>
-      <c r="J33" s="128"/>
-      <c r="K33" s="128"/>
-      <c r="L33" s="128"/>
+        <v>133</v>
+      </c>
+      <c r="D33" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="129"/>
+      <c r="F33" s="129"/>
+      <c r="G33" s="129"/>
+      <c r="H33" s="129"/>
+      <c r="I33" s="129"/>
+      <c r="J33" s="129"/>
+      <c r="K33" s="129"/>
+      <c r="L33" s="129"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
@@ -6732,15 +6732,15 @@
       <c r="C34" s="81">
         <v>0</v>
       </c>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="127"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="127"/>
-      <c r="J34" s="127"/>
-      <c r="K34" s="127"/>
-      <c r="L34" s="127"/>
+      <c r="D34" s="128"/>
+      <c r="E34" s="128"/>
+      <c r="F34" s="128"/>
+      <c r="G34" s="128"/>
+      <c r="H34" s="128"/>
+      <c r="I34" s="128"/>
+      <c r="J34" s="128"/>
+      <c r="K34" s="128"/>
+      <c r="L34" s="128"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="97"/>
@@ -6748,15 +6748,15 @@
       <c r="C35" s="81">
         <v>0</v>
       </c>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="127"/>
-      <c r="J35" s="127"/>
-      <c r="K35" s="127"/>
-      <c r="L35" s="127"/>
+      <c r="D35" s="128"/>
+      <c r="E35" s="128"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="128"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="97"/>
@@ -6764,22 +6764,22 @@
       <c r="C36" s="81">
         <v>0</v>
       </c>
-      <c r="D36" s="127"/>
-      <c r="E36" s="127"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="127"/>
-      <c r="H36" s="127"/>
-      <c r="I36" s="127"/>
-      <c r="J36" s="127"/>
-      <c r="K36" s="127"/>
-      <c r="L36" s="127"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="77">
         <v>53</v>
       </c>
       <c r="B37" s="54" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="C37" s="82">
         <f>SUM(C34:C36)</f>
@@ -6811,25 +6811,25 @@
     </row>
     <row r="39" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="78" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C39" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="D39" s="128" t="s">
-        <v>34</v>
-      </c>
-      <c r="E39" s="128"/>
-      <c r="F39" s="128"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="128"/>
-      <c r="I39" s="128"/>
-      <c r="J39" s="128"/>
-      <c r="K39" s="128"/>
-      <c r="L39" s="128"/>
+        <v>133</v>
+      </c>
+      <c r="D39" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="129"/>
+      <c r="F39" s="129"/>
+      <c r="G39" s="129"/>
+      <c r="H39" s="129"/>
+      <c r="I39" s="129"/>
+      <c r="J39" s="129"/>
+      <c r="K39" s="129"/>
+      <c r="L39" s="129"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="97"/>
@@ -6837,15 +6837,15 @@
       <c r="C40" s="81">
         <v>0</v>
       </c>
-      <c r="D40" s="127"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-      <c r="G40" s="127"/>
-      <c r="H40" s="127"/>
-      <c r="I40" s="127"/>
-      <c r="J40" s="127"/>
-      <c r="K40" s="127"/>
-      <c r="L40" s="127"/>
+      <c r="D40" s="128"/>
+      <c r="E40" s="128"/>
+      <c r="F40" s="128"/>
+      <c r="G40" s="128"/>
+      <c r="H40" s="128"/>
+      <c r="I40" s="128"/>
+      <c r="J40" s="128"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="128"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="97"/>
@@ -6853,15 +6853,15 @@
       <c r="C41" s="81">
         <v>0</v>
       </c>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="127"/>
-      <c r="K41" s="127"/>
-      <c r="L41" s="127"/>
+      <c r="D41" s="128"/>
+      <c r="E41" s="128"/>
+      <c r="F41" s="128"/>
+      <c r="G41" s="128"/>
+      <c r="H41" s="128"/>
+      <c r="I41" s="128"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="128"/>
+      <c r="L41" s="128"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="97"/>
@@ -6869,54 +6869,39 @@
       <c r="C42" s="81">
         <v>0</v>
       </c>
-      <c r="D42" s="127"/>
-      <c r="E42" s="127"/>
-      <c r="F42" s="127"/>
-      <c r="G42" s="127"/>
-      <c r="H42" s="127"/>
-      <c r="I42" s="127"/>
-      <c r="J42" s="127"/>
-      <c r="K42" s="127"/>
-      <c r="L42" s="127"/>
+      <c r="D42" s="128"/>
+      <c r="E42" s="128"/>
+      <c r="F42" s="128"/>
+      <c r="G42" s="128"/>
+      <c r="H42" s="128"/>
+      <c r="I42" s="128"/>
+      <c r="J42" s="128"/>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="95">
         <v>54</v>
       </c>
       <c r="B43" s="54" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C43" s="82">
         <f>SUM(C40:C42)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="129"/>
-      <c r="E43" s="129"/>
-      <c r="F43" s="129"/>
-      <c r="G43" s="129"/>
-      <c r="H43" s="129"/>
-      <c r="I43" s="129"/>
-      <c r="J43" s="129"/>
-      <c r="K43" s="129"/>
-      <c r="L43" s="129"/>
+      <c r="D43" s="132"/>
+      <c r="E43" s="132"/>
+      <c r="F43" s="132"/>
+      <c r="G43" s="132"/>
+      <c r="H43" s="132"/>
+      <c r="I43" s="132"/>
+      <c r="J43" s="132"/>
+      <c r="K43" s="132"/>
+      <c r="L43" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A6:L8"/>
-    <mergeCell ref="D10:L10"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D15:L15"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="D34:L34"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D9:L9"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="D33:L33"/>
@@ -6933,6 +6918,21 @@
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D41:L41"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="A6:L8"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D15:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>

--- a/noprofit/en/11255/inpag-template.xlsx
+++ b/noprofit/en/11255/inpag-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patrick.pasquillo\Documents\GitHub\Universal\noprofit\en\11255\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AA23B2-D226-46C1-97C1-0C1CEF0A1F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA20E27-1C79-401B-9F4F-65F1E594FB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{8907ADCE-C3F1-4516-963F-08DDED88069F}"/>
   </bookViews>
@@ -1360,6 +1360,15 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1372,15 +1381,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1405,47 +1405,47 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2157,6 +2157,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B10:G16"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
@@ -2173,12 +2179,6 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B10:G16"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B20:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
@@ -2207,84 +2207,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
     </row>
     <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>269</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
@@ -2307,12 +2307,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="110" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
@@ -2406,12 +2406,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44"/>
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="110" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
     </row>
     <row r="18" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
@@ -2539,12 +2539,12 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="107" t="s">
+      <c r="B26" s="110" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
     </row>
     <row r="27" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="s">
@@ -2672,12 +2672,12 @@
     </row>
     <row r="35" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="44"/>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="110" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
+      <c r="C35" s="110"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
     </row>
     <row r="36" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
@@ -2754,12 +2754,12 @@
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="44"/>
-      <c r="B41" s="107" t="s">
+      <c r="B41" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="107"/>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
+      <c r="C41" s="110"/>
+      <c r="D41" s="110"/>
+      <c r="E41" s="110"/>
     </row>
     <row r="42" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
-      <c r="B49" s="107" t="s">
+      <c r="B49" s="110" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="107"/>
+      <c r="C49" s="110"/>
       <c r="D49" s="62">
         <f>SUM(D42:D48)</f>
         <v>0</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
-      <c r="B50" s="107" t="s">
+      <c r="B50" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="107"/>
+      <c r="C50" s="110"/>
       <c r="D50" s="62">
         <f>SUM(D33,D39,D49)</f>
         <v>0</v>
@@ -2928,11 +2928,11 @@
       <c r="A53" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="B53" s="106" t="str">
+      <c r="B53" s="109" t="str">
         <f>IF((D15+D23+D33=D39+D49),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C53" s="106"/>
+      <c r="C53" s="109"/>
       <c r="D53" s="53">
         <f>D50-D23</f>
         <v>0</v>
@@ -2942,12 +2942,12 @@
       <c r="A54" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="B54" s="105" t="str">
+      <c r="B54" s="108" t="str">
         <f>IF((E15+E23+E33=E39+E49),"Ok","Attention! The total liabilities do not match the total assets!")</f>
         <v>Ok</v>
       </c>
-      <c r="C54" s="105"/>
-      <c r="D54" s="105"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="108"/>
       <c r="E54" s="53">
         <f>E50-E23</f>
         <v>0</v>
@@ -2961,11 +2961,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B53:C53"/>
@@ -2976,6 +2971,11 @@
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B53">
@@ -3088,27 +3088,27 @@
       <c r="E5" s="113"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -3688,13 +3688,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3703,72 +3703,72 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
@@ -3987,11 +3987,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A6:E8"/>
     <mergeCell ref="B25:D25"/>
@@ -4004,6 +3999,11 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -4030,94 +4030,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>267</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="119" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="120"/>
+      <c r="C9" s="119"/>
       <c r="D9" s="74" t="s">
         <v>27</v>
       </c>
@@ -4130,11 +4130,11 @@
       <c r="A10" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="110" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
       <c r="E10" s="22">
         <v>0</v>
       </c>
@@ -4150,10 +4150,10 @@
       <c r="A12" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="120" t="s">
+      <c r="B12" s="119" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="120"/>
+      <c r="C12" s="119"/>
       <c r="D12" s="74" t="s">
         <v>27</v>
       </c>
@@ -4275,10 +4275,10 @@
       <c r="A21" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="120" t="s">
         <v>243</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="120"/>
       <c r="D21" s="90"/>
       <c r="E21" s="22">
         <v>0</v>
@@ -4289,10 +4289,10 @@
       <c r="A22" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="120" t="s">
         <v>244</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="120"/>
       <c r="D22" s="90"/>
       <c r="E22" s="22">
         <v>0</v>
@@ -4303,10 +4303,10 @@
       <c r="A23" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="B23" s="119" t="s">
+      <c r="B23" s="120" t="s">
         <v>245</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="90"/>
       <c r="E23" s="22">
         <v>0</v>
@@ -4317,10 +4317,10 @@
       <c r="A24" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="120" t="s">
         <v>246</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="120"/>
       <c r="D24" s="90"/>
       <c r="E24" s="22">
         <v>0</v>
@@ -4329,11 +4329,11 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="107" t="s">
+      <c r="B25" s="110" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
       <c r="E25" s="62">
         <f>E10+SUM(E13:E24)</f>
         <v>0</v>
@@ -4350,10 +4350,10 @@
       <c r="A27" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="120" t="s">
+      <c r="B27" s="119" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="120"/>
+      <c r="C27" s="119"/>
       <c r="D27" s="74" t="s">
         <v>27</v>
       </c>
@@ -4366,10 +4366,10 @@
       <c r="A28" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="B28" s="119" t="s">
+      <c r="B28" s="120" t="s">
         <v>253</v>
       </c>
-      <c r="C28" s="119"/>
+      <c r="C28" s="120"/>
       <c r="D28" s="90"/>
       <c r="E28" s="22">
         <v>0</v>
@@ -4379,10 +4379,10 @@
       <c r="A29" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="B29" s="119" t="s">
+      <c r="B29" s="120" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="119"/>
+      <c r="C29" s="120"/>
       <c r="D29" s="90"/>
       <c r="E29" s="22">
         <v>0</v>
@@ -4392,10 +4392,10 @@
       <c r="A30" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="B30" s="119" t="s">
+      <c r="B30" s="120" t="s">
         <v>248</v>
       </c>
-      <c r="C30" s="119"/>
+      <c r="C30" s="120"/>
       <c r="D30" s="90"/>
       <c r="E30" s="22">
         <v>0</v>
@@ -4405,10 +4405,10 @@
       <c r="A31" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="B31" s="119" t="s">
+      <c r="B31" s="120" t="s">
         <v>255</v>
       </c>
-      <c r="C31" s="119"/>
+      <c r="C31" s="120"/>
       <c r="D31" s="90"/>
       <c r="E31" s="22">
         <v>0</v>
@@ -4416,11 +4416,11 @@
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="107" t="s">
+      <c r="B32" s="110" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
       <c r="E32" s="62">
         <f>E10+E25+SUM(E28:E31)</f>
         <v>0</v>
@@ -4437,10 +4437,10 @@
       <c r="A34" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="120" t="s">
+      <c r="B34" s="119" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="120"/>
+      <c r="C34" s="119"/>
       <c r="D34" s="74" t="s">
         <v>27</v>
       </c>
@@ -4454,10 +4454,10 @@
       <c r="A35" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="B35" s="119" t="s">
+      <c r="B35" s="120" t="s">
         <v>249</v>
       </c>
-      <c r="C35" s="119"/>
+      <c r="C35" s="120"/>
       <c r="D35" s="90"/>
       <c r="E35" s="22">
         <v>0</v>
@@ -4467,10 +4467,10 @@
       <c r="A36" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="B36" s="119" t="s">
+      <c r="B36" s="120" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="119"/>
+      <c r="C36" s="120"/>
       <c r="D36" s="90"/>
       <c r="E36" s="22">
         <v>0</v>
@@ -4480,10 +4480,10 @@
       <c r="A37" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="B37" s="119" t="s">
+      <c r="B37" s="120" t="s">
         <v>251</v>
       </c>
-      <c r="C37" s="119"/>
+      <c r="C37" s="120"/>
       <c r="D37" s="90"/>
       <c r="E37" s="22">
         <v>0</v>
@@ -4491,11 +4491,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
-      <c r="B38" s="107" t="s">
+      <c r="B38" s="110" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="107"/>
-      <c r="D38" s="107"/>
+      <c r="C38" s="110"/>
+      <c r="D38" s="110"/>
       <c r="E38" s="62">
         <f>E10+E25+E32+SUM(E35:E37)</f>
         <v>0</v>
@@ -4510,11 +4510,11 @@
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
-      <c r="B40" s="107" t="s">
+      <c r="B40" s="110" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="107"/>
-      <c r="D40" s="107"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="110"/>
       <c r="E40" s="62">
         <f>SUM(E25,E32,E38)</f>
         <v>0</v>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
-      <c r="B45" s="107" t="s">
+      <c r="B45" s="110" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="107"/>
+      <c r="C45" s="110"/>
       <c r="D45" s="93">
         <v>49</v>
       </c>
@@ -4582,11 +4582,11 @@
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
-      <c r="B46" s="107" t="s">
+      <c r="B46" s="110" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
+      <c r="C46" s="110"/>
+      <c r="D46" s="110"/>
       <c r="E46" s="69">
         <f>'Statement of Financial Position'!D22</f>
         <v>0</v>
@@ -4594,11 +4594,11 @@
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
-      <c r="B47" s="107" t="s">
+      <c r="B47" s="110" t="s">
         <v>122</v>
       </c>
-      <c r="C47" s="107"/>
-      <c r="D47" s="107"/>
+      <c r="C47" s="110"/>
+      <c r="D47" s="110"/>
       <c r="E47" s="69">
         <f>'Statement of Financial Position'!E22</f>
         <v>0</v>
@@ -4606,11 +4606,11 @@
     </row>
     <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
-      <c r="B48" s="107" t="s">
+      <c r="B48" s="110" t="s">
         <v>123</v>
       </c>
-      <c r="C48" s="107"/>
-      <c r="D48" s="107"/>
+      <c r="C48" s="110"/>
+      <c r="D48" s="110"/>
       <c r="E48" s="69">
         <f>E47-E46</f>
         <v>0</v>
@@ -4710,25 +4710,18 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B32:D32"/>
@@ -4745,18 +4738,25 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -4782,85 +4782,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="121" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="125" t="s">
+      <c r="A9" s="123" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="122"/>
@@ -4881,34 +4881,34 @@
       <c r="D12" s="122"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="123"/>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
+      <c r="A13" s="124"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="123"/>
-      <c r="B14" s="123"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="123"/>
+      <c r="A14" s="124"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="123"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="123"/>
+      <c r="A15" s="124"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="123"/>
-      <c r="B16" s="123"/>
-      <c r="C16" s="123"/>
-      <c r="D16" s="123"/>
+      <c r="A16" s="124"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="123"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="123"/>
+      <c r="A17" s="124"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="122"/>
@@ -4977,10 +4977,10 @@
       <c r="D28" s="122"/>
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="121"/>
-      <c r="B29" s="121"/>
-      <c r="C29" s="121"/>
-      <c r="D29" s="121"/>
+      <c r="A29" s="125"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="125"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="74" t="s">
@@ -5610,6 +5610,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
@@ -5625,18 +5637,6 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5678,65 +5678,65 @@
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108" t="str">
+      <c r="B2" s="104" t="str">
         <f>'General information'!B2</f>
         <v>No-ProfitName LegalForm</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="104" t="str">
         <f>'General information'!B3</f>
         <v>Address 1234, Country</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="106">
         <f>'General information'!B8</f>
         <v>45292</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="106">
         <f>'General information'!B9</f>
         <v>45657</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="107" t="s">
         <v>266</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -6241,48 +6241,48 @@
       <c r="L5" s="131"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="132" t="s">
         <v>265</v>
       </c>
-      <c r="B6" s="127"/>
-      <c r="C6" s="127"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="127"/>
-      <c r="F6" s="127"/>
-      <c r="G6" s="127"/>
-      <c r="H6" s="127"/>
-      <c r="I6" s="127"/>
-      <c r="J6" s="127"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
+      <c r="L6" s="132"/>
     </row>
     <row r="7" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="127"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="132"/>
     </row>
     <row r="8" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="127"/>
-      <c r="K8" s="127"/>
-      <c r="L8" s="127"/>
+      <c r="A8" s="132"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="132"/>
+      <c r="L8" s="132"/>
     </row>
     <row r="9" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="78" t="s">
@@ -6294,17 +6294,17 @@
       <c r="C9" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="129" t="s">
+      <c r="D9" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="129"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="129"/>
-      <c r="K9" s="129"/>
-      <c r="L9" s="129"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="128"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="97"/>
@@ -6312,15 +6312,15 @@
       <c r="C10" s="81">
         <v>0</v>
       </c>
-      <c r="D10" s="128"/>
-      <c r="E10" s="128"/>
-      <c r="F10" s="128"/>
-      <c r="G10" s="128"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="127"/>
+      <c r="L10" s="127"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="97"/>
@@ -6328,15 +6328,15 @@
       <c r="C11" s="81">
         <v>0</v>
       </c>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="128"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="97"/>
@@ -6344,15 +6344,15 @@
       <c r="C12" s="81">
         <v>0</v>
       </c>
-      <c r="D12" s="128"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="128"/>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="77">
@@ -6399,17 +6399,17 @@
       <c r="C15" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="129" t="s">
+      <c r="D15" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="129"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="129"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="128"/>
+      <c r="I15" s="128"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="128"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="97"/>
@@ -6417,15 +6417,15 @@
       <c r="C16" s="81">
         <v>0</v>
       </c>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="128"/>
-      <c r="J16" s="128"/>
-      <c r="K16" s="128"/>
-      <c r="L16" s="128"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="127"/>
+      <c r="K16" s="127"/>
+      <c r="L16" s="127"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="97"/>
@@ -6433,15 +6433,15 @@
       <c r="C17" s="81">
         <v>0</v>
       </c>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="128"/>
-      <c r="J17" s="128"/>
-      <c r="K17" s="128"/>
-      <c r="L17" s="128"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="127"/>
+      <c r="L17" s="127"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="97"/>
@@ -6449,15 +6449,15 @@
       <c r="C18" s="81">
         <v>0</v>
       </c>
-      <c r="D18" s="128"/>
-      <c r="E18" s="128"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="128"/>
-      <c r="H18" s="128"/>
-      <c r="I18" s="128"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="128"/>
-      <c r="L18" s="128"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="127"/>
+      <c r="L18" s="127"/>
     </row>
     <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="77">
@@ -6504,17 +6504,17 @@
       <c r="C21" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="129" t="s">
+      <c r="D21" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="129"/>
-      <c r="K21" s="129"/>
-      <c r="L21" s="129"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="128"/>
+      <c r="L21" s="128"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="97"/>
@@ -6522,15 +6522,15 @@
       <c r="C22" s="81">
         <v>0</v>
       </c>
-      <c r="D22" s="128"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="128"/>
-      <c r="I22" s="128"/>
-      <c r="J22" s="128"/>
-      <c r="K22" s="128"/>
-      <c r="L22" s="128"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="127"/>
+      <c r="G22" s="127"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="127"/>
+      <c r="J22" s="127"/>
+      <c r="K22" s="127"/>
+      <c r="L22" s="127"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="97"/>
@@ -6538,15 +6538,15 @@
       <c r="C23" s="81">
         <v>0</v>
       </c>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="128"/>
-      <c r="J23" s="128"/>
-      <c r="K23" s="128"/>
-      <c r="L23" s="128"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="127"/>
+      <c r="L23" s="127"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="97"/>
@@ -6554,15 +6554,15 @@
       <c r="C24" s="81">
         <v>0</v>
       </c>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="128"/>
-      <c r="I24" s="128"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="128"/>
-      <c r="L24" s="128"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="127"/>
+      <c r="J24" s="127"/>
+      <c r="K24" s="127"/>
+      <c r="L24" s="127"/>
     </row>
     <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="77">
@@ -6609,17 +6609,17 @@
       <c r="C27" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="D27" s="129" t="s">
+      <c r="D27" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="129"/>
-      <c r="F27" s="129"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="129"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="129"/>
-      <c r="K27" s="129"/>
-      <c r="L27" s="129"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="128"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="128"/>
+      <c r="L27" s="128"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="97"/>
@@ -6627,15 +6627,15 @@
       <c r="C28" s="81">
         <v>0</v>
       </c>
-      <c r="D28" s="128"/>
-      <c r="E28" s="128"/>
-      <c r="F28" s="128"/>
-      <c r="G28" s="128"/>
-      <c r="H28" s="128"/>
-      <c r="I28" s="128"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="128"/>
-      <c r="L28" s="128"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="127"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="127"/>
+      <c r="K28" s="127"/>
+      <c r="L28" s="127"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
@@ -6643,15 +6643,15 @@
       <c r="C29" s="81">
         <v>0</v>
       </c>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="128"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="128"/>
-      <c r="K29" s="128"/>
-      <c r="L29" s="128"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="127"/>
+      <c r="G29" s="127"/>
+      <c r="H29" s="127"/>
+      <c r="I29" s="127"/>
+      <c r="J29" s="127"/>
+      <c r="K29" s="127"/>
+      <c r="L29" s="127"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
@@ -6659,15 +6659,15 @@
       <c r="C30" s="81">
         <v>0</v>
       </c>
-      <c r="D30" s="128"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="128"/>
-      <c r="G30" s="128"/>
-      <c r="H30" s="128"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="128"/>
-      <c r="L30" s="128"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="127"/>
+      <c r="F30" s="127"/>
+      <c r="G30" s="127"/>
+      <c r="H30" s="127"/>
+      <c r="I30" s="127"/>
+      <c r="J30" s="127"/>
+      <c r="K30" s="127"/>
+      <c r="L30" s="127"/>
     </row>
     <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="77">
@@ -6714,17 +6714,17 @@
       <c r="C33" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="129" t="s">
+      <c r="D33" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="129"/>
-      <c r="F33" s="129"/>
-      <c r="G33" s="129"/>
-      <c r="H33" s="129"/>
-      <c r="I33" s="129"/>
-      <c r="J33" s="129"/>
-      <c r="K33" s="129"/>
-      <c r="L33" s="129"/>
+      <c r="E33" s="128"/>
+      <c r="F33" s="128"/>
+      <c r="G33" s="128"/>
+      <c r="H33" s="128"/>
+      <c r="I33" s="128"/>
+      <c r="J33" s="128"/>
+      <c r="K33" s="128"/>
+      <c r="L33" s="128"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
@@ -6732,15 +6732,15 @@
       <c r="C34" s="81">
         <v>0</v>
       </c>
-      <c r="D34" s="128"/>
-      <c r="E34" s="128"/>
-      <c r="F34" s="128"/>
-      <c r="G34" s="128"/>
-      <c r="H34" s="128"/>
-      <c r="I34" s="128"/>
-      <c r="J34" s="128"/>
-      <c r="K34" s="128"/>
-      <c r="L34" s="128"/>
+      <c r="D34" s="127"/>
+      <c r="E34" s="127"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="127"/>
+      <c r="I34" s="127"/>
+      <c r="J34" s="127"/>
+      <c r="K34" s="127"/>
+      <c r="L34" s="127"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="97"/>
@@ -6748,15 +6748,15 @@
       <c r="C35" s="81">
         <v>0</v>
       </c>
-      <c r="D35" s="128"/>
-      <c r="E35" s="128"/>
-      <c r="F35" s="128"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="128"/>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="128"/>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="127"/>
+      <c r="J35" s="127"/>
+      <c r="K35" s="127"/>
+      <c r="L35" s="127"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="97"/>
@@ -6764,15 +6764,15 @@
       <c r="C36" s="81">
         <v>0</v>
       </c>
-      <c r="D36" s="128"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="128"/>
-      <c r="G36" s="128"/>
-      <c r="H36" s="128"/>
-      <c r="I36" s="128"/>
-      <c r="J36" s="128"/>
-      <c r="K36" s="128"/>
-      <c r="L36" s="128"/>
+      <c r="D36" s="127"/>
+      <c r="E36" s="127"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="127"/>
+      <c r="H36" s="127"/>
+      <c r="I36" s="127"/>
+      <c r="J36" s="127"/>
+      <c r="K36" s="127"/>
+      <c r="L36" s="127"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="77">
@@ -6819,17 +6819,17 @@
       <c r="C39" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="D39" s="129" t="s">
+      <c r="D39" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="E39" s="129"/>
-      <c r="F39" s="129"/>
-      <c r="G39" s="129"/>
-      <c r="H39" s="129"/>
-      <c r="I39" s="129"/>
-      <c r="J39" s="129"/>
-      <c r="K39" s="129"/>
-      <c r="L39" s="129"/>
+      <c r="E39" s="128"/>
+      <c r="F39" s="128"/>
+      <c r="G39" s="128"/>
+      <c r="H39" s="128"/>
+      <c r="I39" s="128"/>
+      <c r="J39" s="128"/>
+      <c r="K39" s="128"/>
+      <c r="L39" s="128"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="97"/>
@@ -6837,15 +6837,15 @@
       <c r="C40" s="81">
         <v>0</v>
       </c>
-      <c r="D40" s="128"/>
-      <c r="E40" s="128"/>
-      <c r="F40" s="128"/>
-      <c r="G40" s="128"/>
-      <c r="H40" s="128"/>
-      <c r="I40" s="128"/>
-      <c r="J40" s="128"/>
-      <c r="K40" s="128"/>
-      <c r="L40" s="128"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="127"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="127"/>
+      <c r="J40" s="127"/>
+      <c r="K40" s="127"/>
+      <c r="L40" s="127"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="97"/>
@@ -6853,15 +6853,15 @@
       <c r="C41" s="81">
         <v>0</v>
       </c>
-      <c r="D41" s="128"/>
-      <c r="E41" s="128"/>
-      <c r="F41" s="128"/>
-      <c r="G41" s="128"/>
-      <c r="H41" s="128"/>
-      <c r="I41" s="128"/>
-      <c r="J41" s="128"/>
-      <c r="K41" s="128"/>
-      <c r="L41" s="128"/>
+      <c r="D41" s="127"/>
+      <c r="E41" s="127"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="127"/>
+      <c r="K41" s="127"/>
+      <c r="L41" s="127"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="97"/>
@@ -6869,15 +6869,15 @@
       <c r="C42" s="81">
         <v>0</v>
       </c>
-      <c r="D42" s="128"/>
-      <c r="E42" s="128"/>
-      <c r="F42" s="128"/>
-      <c r="G42" s="128"/>
-      <c r="H42" s="128"/>
-      <c r="I42" s="128"/>
-      <c r="J42" s="128"/>
-      <c r="K42" s="128"/>
-      <c r="L42" s="128"/>
+      <c r="D42" s="127"/>
+      <c r="E42" s="127"/>
+      <c r="F42" s="127"/>
+      <c r="G42" s="127"/>
+      <c r="H42" s="127"/>
+      <c r="I42" s="127"/>
+      <c r="J42" s="127"/>
+      <c r="K42" s="127"/>
+      <c r="L42" s="127"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="95">
@@ -6890,18 +6890,33 @@
         <f>SUM(C40:C42)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="132"/>
-      <c r="L43" s="132"/>
+      <c r="D43" s="129"/>
+      <c r="E43" s="129"/>
+      <c r="F43" s="129"/>
+      <c r="G43" s="129"/>
+      <c r="H43" s="129"/>
+      <c r="I43" s="129"/>
+      <c r="J43" s="129"/>
+      <c r="K43" s="129"/>
+      <c r="L43" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A6:L8"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D15:L15"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="D9:L9"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="D33:L33"/>
@@ -6918,21 +6933,6 @@
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D41:L41"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="D34:L34"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D9:L9"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A6:L8"/>
-    <mergeCell ref="D10:L10"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D15:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
